--- a/core/src/main/resources/baseFiles/excel/Reports.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Reports.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="217">
   <si>
     <t>Firm</t>
   </si>
@@ -39,172 +39,646 @@
     <t>Lawyers Registered</t>
   </si>
   <si>
-    <t>Cassels</t>
+    <t>Lee &amp; Ko</t>
+  </si>
+  <si>
+    <t>04min 00s</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>TAN Law</t>
+  </si>
+  <si>
+    <t>Balter, Guth, Aloni &amp; Co</t>
+  </si>
+  <si>
+    <t>Tanner DeWitt</t>
+  </si>
+  <si>
+    <t>03min 52s</t>
+  </si>
+  <si>
+    <t>Gadens</t>
+  </si>
+  <si>
+    <t>03min 36s</t>
+  </si>
+  <si>
+    <t>Yuen Law</t>
+  </si>
+  <si>
+    <t>03min 07s</t>
+  </si>
+  <si>
+    <t>Lipa Meir &amp; Co</t>
+  </si>
+  <si>
+    <t>03min 04s</t>
+  </si>
+  <si>
+    <t>TA Law</t>
+  </si>
+  <si>
+    <t>02min 55s</t>
+  </si>
+  <si>
+    <t>LHAG</t>
+  </si>
+  <si>
+    <t>02min 33s</t>
+  </si>
+  <si>
+    <t>Wrays</t>
+  </si>
+  <si>
+    <t>02min 31s</t>
+  </si>
+  <si>
+    <t>Shoob &amp; Co</t>
+  </si>
+  <si>
+    <t>02min 30s</t>
+  </si>
+  <si>
+    <t>Saga Legal</t>
+  </si>
+  <si>
+    <t>Remfry &amp; Sagar</t>
+  </si>
+  <si>
+    <t>02min 21s</t>
+  </si>
+  <si>
+    <t>Aquinas Law Alliance</t>
+  </si>
+  <si>
+    <t>01min 54s</t>
+  </si>
+  <si>
+    <t>YKVN</t>
+  </si>
+  <si>
+    <t>01min 33s</t>
+  </si>
+  <si>
+    <t>Frasers</t>
+  </si>
+  <si>
+    <t>01min 21s</t>
+  </si>
+  <si>
+    <t>Domnern Somgiat &amp; Boonma</t>
+  </si>
+  <si>
+    <t>01min 18s</t>
+  </si>
+  <si>
+    <t>Kim Chang &amp; Lee</t>
+  </si>
+  <si>
+    <t>01min 15s</t>
+  </si>
+  <si>
+    <t>Wong Partnership</t>
+  </si>
+  <si>
+    <t>01min 11s</t>
+  </si>
+  <si>
+    <t>Mohanadass Partnership</t>
+  </si>
+  <si>
+    <t>01min 08s</t>
+  </si>
+  <si>
+    <t>Harry Elias</t>
+  </si>
+  <si>
+    <t>01min 05s</t>
+  </si>
+  <si>
+    <t>RIAA Barker Gillette</t>
+  </si>
+  <si>
+    <t>01min 02s</t>
+  </si>
+  <si>
+    <t>Axis Law Chambers</t>
+  </si>
+  <si>
+    <t>FGE Ebrahim Hosain</t>
+  </si>
+  <si>
+    <t>01min 00s</t>
+  </si>
+  <si>
+    <t>SG &amp; Co Lawyers</t>
+  </si>
+  <si>
+    <t>59s</t>
+  </si>
+  <si>
+    <t>Sayat Zholshy &amp; Partners</t>
+  </si>
+  <si>
+    <t>Boase Cohen &amp; Collins</t>
+  </si>
+  <si>
+    <t>58s</t>
+  </si>
+  <si>
+    <t>Desai &amp; Diwanji</t>
+  </si>
+  <si>
+    <t>57s</t>
+  </si>
+  <si>
+    <t>LS Horizon</t>
+  </si>
+  <si>
+    <t>56s</t>
+  </si>
+  <si>
+    <t>ALMT Legal</t>
+  </si>
+  <si>
+    <t>55s</t>
+  </si>
+  <si>
+    <t>JTJB International Lawyers</t>
+  </si>
+  <si>
+    <t>54s</t>
+  </si>
+  <si>
+    <t>Yoon &amp; Yang</t>
+  </si>
+  <si>
+    <t>48s</t>
+  </si>
+  <si>
+    <t>SIGNUM</t>
+  </si>
+  <si>
+    <t>46s</t>
+  </si>
+  <si>
+    <t>Kochhar &amp; Co</t>
+  </si>
+  <si>
+    <t>45s</t>
+  </si>
+  <si>
+    <t>Al Alawi &amp; Co</t>
+  </si>
+  <si>
+    <t>Bun &amp; Associates</t>
+  </si>
+  <si>
+    <t>44s</t>
+  </si>
+  <si>
+    <t>Shardul Amarchand Mangaldas &amp; Co</t>
+  </si>
+  <si>
+    <t>43s</t>
+  </si>
+  <si>
+    <t>VILAF</t>
+  </si>
+  <si>
+    <t>38s</t>
+  </si>
+  <si>
+    <t>Asia Liuh IP</t>
+  </si>
+  <si>
+    <t>37s</t>
+  </si>
+  <si>
+    <t>Rajani Associates</t>
+  </si>
+  <si>
+    <t>36s</t>
+  </si>
+  <si>
+    <t>Dhir &amp; Dhir</t>
+  </si>
+  <si>
+    <t>35s</t>
+  </si>
+  <si>
+    <t>H-F &amp; Co</t>
+  </si>
+  <si>
+    <t>34s</t>
+  </si>
+  <si>
+    <t>S&amp;O IP</t>
+  </si>
+  <si>
+    <t>32s</t>
+  </si>
+  <si>
+    <t>LAW Partnership</t>
+  </si>
+  <si>
+    <t>D. L. And F. De Saram</t>
+  </si>
+  <si>
+    <t>31s</t>
+  </si>
+  <si>
+    <t>Haidermota &amp; Co</t>
+  </si>
+  <si>
+    <t>30s</t>
+  </si>
+  <si>
+    <t>Fox And Mandal</t>
+  </si>
+  <si>
+    <t>Stratage Law</t>
+  </si>
+  <si>
+    <t>Bowers</t>
+  </si>
+  <si>
+    <t>29s</t>
+  </si>
+  <si>
+    <t>Zhongzi Law</t>
+  </si>
+  <si>
+    <t>Ramdas &amp; Wong</t>
+  </si>
+  <si>
+    <t>28s</t>
+  </si>
+  <si>
+    <t>S Horowitz &amp; Co</t>
+  </si>
+  <si>
+    <t>Zan Hub</t>
+  </si>
+  <si>
+    <t>SIP Law</t>
+  </si>
+  <si>
+    <t>26s</t>
+  </si>
+  <si>
+    <t>Dhaval Vussonji &amp; Associates</t>
+  </si>
+  <si>
+    <t>Eldan Law</t>
+  </si>
+  <si>
+    <t>Manuela António</t>
+  </si>
+  <si>
+    <t>25s</t>
+  </si>
+  <si>
+    <t>Vision &amp; Associates</t>
+  </si>
+  <si>
+    <t>Bross And Partners</t>
+  </si>
+  <si>
+    <t>24s</t>
+  </si>
+  <si>
+    <t>RCL Chambers Law</t>
+  </si>
+  <si>
+    <t>Gross &amp; Co</t>
+  </si>
+  <si>
+    <t>Cornelius Lane &amp; Mufti</t>
+  </si>
+  <si>
+    <t>23s</t>
+  </si>
+  <si>
+    <t>Deacons</t>
+  </si>
+  <si>
+    <t>22s</t>
+  </si>
+  <si>
+    <t>Vanguard Lawyers Tokyo</t>
+  </si>
+  <si>
+    <t>Nurmansyah &amp; Muzdalifah</t>
+  </si>
+  <si>
+    <t>Makes &amp; Partners Law</t>
+  </si>
+  <si>
+    <t>21s</t>
+  </si>
+  <si>
+    <t>SGLA Law</t>
+  </si>
+  <si>
+    <t>FCLaw</t>
+  </si>
+  <si>
+    <t>20s</t>
+  </si>
+  <si>
+    <t>ABS And Co</t>
+  </si>
+  <si>
+    <t>Bhandari Naqvi Riaz</t>
+  </si>
+  <si>
+    <t>YYC Legal</t>
+  </si>
+  <si>
+    <t>M&amp;D LAW</t>
+  </si>
+  <si>
+    <t>19s</t>
+  </si>
+  <si>
+    <t>Sierra Legal</t>
+  </si>
+  <si>
+    <t>Mohsin Tayebaly &amp; Co</t>
+  </si>
+  <si>
+    <t>18s</t>
+  </si>
+  <si>
+    <t>Russell McVeagh</t>
+  </si>
+  <si>
+    <t>MBIP</t>
+  </si>
+  <si>
+    <t>Tian Yuan</t>
+  </si>
+  <si>
+    <t>17s</t>
+  </si>
+  <si>
+    <t>GKC Partners</t>
+  </si>
+  <si>
+    <t>Barnea And Co</t>
+  </si>
+  <si>
+    <t>16s</t>
+  </si>
+  <si>
+    <t>Helmsman</t>
+  </si>
+  <si>
+    <t>15s</t>
+  </si>
+  <si>
+    <t>Global Vietnam Lawyers</t>
+  </si>
+  <si>
+    <t>Chadha &amp; Co</t>
+  </si>
+  <si>
+    <t>DSKLegal</t>
+  </si>
+  <si>
+    <t>Baohua Law</t>
+  </si>
+  <si>
+    <t>Doogue + George</t>
+  </si>
+  <si>
+    <t>Moroğlu Arseven</t>
+  </si>
+  <si>
+    <t>14s</t>
+  </si>
+  <si>
+    <t>HY Leung &amp; Co</t>
+  </si>
+  <si>
+    <t>Beijing East IP</t>
+  </si>
+  <si>
+    <t>13s</t>
+  </si>
+  <si>
+    <t>Tommy Thomas</t>
+  </si>
+  <si>
+    <t>Al Busaidy, Mansoor Jamal &amp; Co</t>
+  </si>
+  <si>
+    <t>Deheheng Law</t>
+  </si>
+  <si>
+    <t>Hugill &amp; Ip</t>
+  </si>
+  <si>
+    <t>Hiways</t>
+  </si>
+  <si>
+    <t>12s</t>
+  </si>
+  <si>
+    <t>Malley And Co</t>
+  </si>
+  <si>
+    <t>Maheshwari &amp; Co</t>
+  </si>
+  <si>
+    <t>11s</t>
+  </si>
+  <si>
+    <t>Collyer Law</t>
+  </si>
+  <si>
+    <t>Lektou</t>
+  </si>
+  <si>
+    <t>Tiruchelvam Associates</t>
+  </si>
+  <si>
+    <t>Anhad Law</t>
+  </si>
+  <si>
+    <t>10s</t>
+  </si>
+  <si>
+    <t>Economic Laws Practice</t>
+  </si>
+  <si>
+    <t>MAS Law</t>
+  </si>
+  <si>
+    <t>09s</t>
+  </si>
+  <si>
+    <t>Arnold Bloch Leibler</t>
+  </si>
+  <si>
+    <t>Vellani &amp; Vellani</t>
+  </si>
+  <si>
+    <t>07s</t>
+  </si>
+  <si>
+    <t>LNT</t>
+  </si>
+  <si>
+    <t>Sok Siphana &amp; Associates</t>
+  </si>
+  <si>
+    <t>Dashnyam</t>
+  </si>
+  <si>
+    <t>05s</t>
+  </si>
+  <si>
+    <t>K1 Chamber</t>
+  </si>
+  <si>
+    <t>Aequitas</t>
+  </si>
+  <si>
+    <t>04s</t>
+  </si>
+  <si>
+    <t>BTG Advaya</t>
+  </si>
+  <si>
+    <t>03s</t>
+  </si>
+  <si>
+    <t>Samvad Partners</t>
+  </si>
+  <si>
+    <t>AOil</t>
+  </si>
+  <si>
+    <t>01s</t>
+  </si>
+  <si>
+    <t>Corrs</t>
+  </si>
+  <si>
+    <t>01min 37s</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Simpson Grierson</t>
+  </si>
+  <si>
+    <t>01min 19s</t>
+  </si>
+  <si>
+    <t>Wenger Vieli AG</t>
+  </si>
+  <si>
+    <t>Minter Ellison RuddWatts</t>
+  </si>
+  <si>
+    <t>Gilbert + Tobin</t>
+  </si>
+  <si>
+    <t>Hicksons</t>
   </si>
   <si>
     <t>01min 04s</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Schoenherr</t>
-  </si>
-  <si>
-    <t>Houthoof</t>
-  </si>
-  <si>
-    <t>01min 06s</t>
-  </si>
-  <si>
-    <t>Young List</t>
-  </si>
-  <si>
-    <t>01min 09s</t>
-  </si>
-  <si>
-    <t>Hakun Law</t>
-  </si>
-  <si>
-    <t>01min 43s</t>
-  </si>
-  <si>
-    <t>Nauta Dutilh</t>
-  </si>
-  <si>
-    <t>02min 10s</t>
-  </si>
-  <si>
-    <t>Latham And Watkins</t>
-  </si>
-  <si>
-    <t>02min 29s</t>
-  </si>
-  <si>
-    <t>Guantao Law</t>
-  </si>
-  <si>
-    <t>03min 48s</t>
-  </si>
-  <si>
-    <t>Tahota Law</t>
-  </si>
-  <si>
-    <t>04min 00s</t>
-  </si>
-  <si>
-    <t>Davies Ward Phillips And Vineberg</t>
-  </si>
-  <si>
-    <t>Huiye Law</t>
-  </si>
-  <si>
-    <t>Ashurst</t>
-  </si>
-  <si>
-    <t>Gadens</t>
-  </si>
-  <si>
-    <t>Ronan Daly Jermyn</t>
-  </si>
-  <si>
-    <t>05s</t>
-  </si>
-  <si>
-    <t>Werksmans</t>
-  </si>
-  <si>
-    <t>08s</t>
-  </si>
-  <si>
-    <t>Banki Haddock Fiora</t>
-  </si>
-  <si>
-    <t>Schindler Attorneys</t>
-  </si>
-  <si>
-    <t>10s</t>
-  </si>
-  <si>
-    <t>StewartMcKelvey</t>
-  </si>
-  <si>
-    <t>13s</t>
-  </si>
-  <si>
-    <t>Bennett Jones</t>
-  </si>
-  <si>
-    <t>14s</t>
-  </si>
-  <si>
-    <t>Helmsman</t>
-  </si>
-  <si>
-    <t>17s</t>
-  </si>
-  <si>
-    <t>MBIP</t>
-  </si>
-  <si>
-    <t>18s</t>
-  </si>
-  <si>
-    <t>Hammarskiöld And Co</t>
-  </si>
-  <si>
-    <t>Krogerus</t>
-  </si>
-  <si>
-    <t>Reliance Corporate Advisors</t>
-  </si>
-  <si>
-    <t>21s</t>
-  </si>
-  <si>
-    <t>Paksoy</t>
-  </si>
-  <si>
-    <t>Dillon Eustace</t>
+    <t>Buddle Findlay</t>
+  </si>
+  <si>
+    <t>Moray &amp; Agnew</t>
+  </si>
+  <si>
+    <t>HWL Ebsworth</t>
+  </si>
+  <si>
+    <t>53s</t>
+  </si>
+  <si>
+    <t>Norman Waterhouse</t>
+  </si>
+  <si>
+    <t>52s</t>
+  </si>
+  <si>
+    <t>Tompkins Wake</t>
+  </si>
+  <si>
+    <t>49s</t>
+  </si>
+  <si>
+    <t>Zhong Lun</t>
+  </si>
+  <si>
+    <t>39s</t>
+  </si>
+  <si>
+    <t>Hesketh Henry</t>
+  </si>
+  <si>
+    <t>Baumgartners</t>
+  </si>
+  <si>
+    <t>Mellor Olsson</t>
+  </si>
+  <si>
+    <t>Carter Newell</t>
+  </si>
+  <si>
+    <t>DW Fox Tucker</t>
+  </si>
+  <si>
+    <t>FPA Patent</t>
+  </si>
+  <si>
+    <t>wilson ryan grose</t>
+  </si>
+  <si>
+    <t>Johnson Winter Slattery</t>
+  </si>
+  <si>
+    <t>McCullough Robertson</t>
+  </si>
+  <si>
+    <t>Wilson Harle</t>
+  </si>
+  <si>
+    <t>Anderson Lloyd</t>
+  </si>
+  <si>
+    <t>Greenwood Roche</t>
   </si>
   <si>
     <t>DBHLaw</t>
   </si>
   <si>
-    <t>25s</t>
-  </si>
-  <si>
-    <t>James And Wells</t>
-  </si>
-  <si>
-    <t>Ramdas And Wong</t>
-  </si>
-  <si>
-    <t>MSP</t>
-  </si>
-  <si>
-    <t>28s</t>
-  </si>
-  <si>
-    <t>Carey Olsen</t>
-  </si>
-  <si>
-    <t>Dahl Law</t>
-  </si>
-  <si>
-    <t>29s</t>
-  </si>
-  <si>
-    <t>Santamarina And Steta</t>
-  </si>
-  <si>
-    <t>34s</t>
-  </si>
-  <si>
-    <t>Saba And Co</t>
-  </si>
-  <si>
-    <t>55s</t>
+    <t>Lane Neave</t>
+  </si>
+  <si>
+    <t>Macpherson Kelley</t>
+  </si>
+  <si>
+    <t>Docvit</t>
+  </si>
+  <si>
+    <t>Finlaysons</t>
+  </si>
+  <si>
+    <t>Corcoran</t>
   </si>
 </sst>
 </file>
@@ -1192,13 +1666,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="27.6634615384615"/>
-    <col min="2" max="2" customWidth="true" style="1" width="33.3461538461538"/>
-    <col min="3" max="3" customWidth="true" style="1" width="51.1442307692308"/>
-    <col min="4" max="8" customWidth="true" width="8.88461538461539"/>
+    <col min="1" max="1" width="27.6634615384615" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3461538461538" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.1442307692308" style="1" customWidth="1"/>
+    <col min="4" max="8" width="8.88461538461539" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.2" spans="1:3">
@@ -1212,9 +1686,1560 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:C35">
-    <sortCondition ref="B2"/>
+  <sortState ref="A2:C350">
+    <sortCondition ref="C2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1227,8 +3252,8 @@
   <dimension ref="D2:F35"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="4" max="4" customWidth="true" width="36.0769230769231"/>
-    <col min="5" max="6" customWidth="true" width="15.875"/>
+    <col min="4" max="4" width="36.0769230769231" customWidth="1"/>
+    <col min="5" max="6" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="4:6">

--- a/core/src/main/resources/baseFiles/excel/Reports.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Reports.xlsx
@@ -1666,13 +1666,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="27.6634615384615" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3461538461538" style="1" customWidth="1"/>
-    <col min="3" max="3" width="51.1442307692308" style="1" customWidth="1"/>
-    <col min="4" max="8" width="8.88461538461539" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="27.6634615384615"/>
+    <col min="2" max="2" customWidth="true" style="1" width="33.3461538461538"/>
+    <col min="3" max="3" customWidth="true" style="1" width="51.1442307692308"/>
+    <col min="4" max="8" customWidth="true" width="8.88461538461539"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.2" spans="1:3">
@@ -1684,1557 +1684,6 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3252,8 +1701,8 @@
   <dimension ref="D2:F35"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="4" max="4" width="36.0769230769231" customWidth="1"/>
-    <col min="5" max="6" width="15.875" customWidth="1"/>
+    <col min="4" max="4" customWidth="true" width="36.0769230769231"/>
+    <col min="5" max="6" customWidth="true" width="15.875"/>
   </cols>
   <sheetData>
     <row r="2" spans="4:6">

--- a/core/src/main/resources/baseFiles/excel/Reports.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Reports.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="589">
   <si>
     <t>Firm</t>
   </si>
@@ -679,6 +679,1122 @@
   </si>
   <si>
     <t>Corcoran</t>
+  </si>
+  <si>
+    <t>Hylands</t>
+  </si>
+  <si>
+    <t>1min 16</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Juslaws &amp; Consult</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1min 33</t>
+  </si>
+  <si>
+    <t>Halim Hong &amp; Quek</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Singhania &amp; Partners</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Chuo Sogo LPC</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Hui Zhong</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Firon Law</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>CFN Law</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Al-Hamad Legal</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>JunZeJun Law</t>
+  </si>
+  <si>
+    <t>AZB</t>
+  </si>
+  <si>
+    <t>1min 44</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Capital Equity Legal Group</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Anli</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Hiswara Bunjamin &amp; Tandjung</t>
+  </si>
+  <si>
+    <t>UMBRA</t>
+  </si>
+  <si>
+    <t>Soemadipradja &amp; Taher</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>1min 23</t>
+  </si>
+  <si>
+    <t>CNP Law</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Mourant</t>
+  </si>
+  <si>
+    <t>1min 50</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Vaish</t>
+  </si>
+  <si>
+    <t>1min 47</t>
+  </si>
+  <si>
+    <t>1min 53</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Zaid Ibrahim &amp; Co</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>K Law</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>3min 0</t>
+  </si>
+  <si>
+    <t>Shin &amp; Kim</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>AYMP</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Trilegal</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Rahmat Lim &amp; Partners</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>AJU Kim Chang &amp; Lee</t>
+  </si>
+  <si>
+    <t>4min 0</t>
+  </si>
+  <si>
+    <t>Tsar &amp; Tsai</t>
+  </si>
+  <si>
+    <t>Providence Law</t>
+  </si>
+  <si>
+    <t>1min 9</t>
+  </si>
+  <si>
+    <t>Phoenix Legal</t>
+  </si>
+  <si>
+    <t>1min 27</t>
+  </si>
+  <si>
+    <t>Lee &amp; Lee</t>
+  </si>
+  <si>
+    <t>1min 3</t>
+  </si>
+  <si>
+    <t>Veritas Legal</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Wang Jing &amp; Co</t>
+  </si>
+  <si>
+    <t>Kai Rong Law</t>
+  </si>
+  <si>
+    <t>Shandong Deheng Law</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Aron Tadmor Levy</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Bae Kim &amp; Lee</t>
+  </si>
+  <si>
+    <t>1min 20</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Bharucha &amp; Partners</t>
+  </si>
+  <si>
+    <t>FKNK Law</t>
+  </si>
+  <si>
+    <t>Virtus</t>
+  </si>
+  <si>
+    <t>Solomon &amp; Co</t>
+  </si>
+  <si>
+    <t>1min 6</t>
+  </si>
+  <si>
+    <t>C&amp;T Partners</t>
+  </si>
+  <si>
+    <t>2min 49</t>
+  </si>
+  <si>
+    <t>The Capital Law</t>
+  </si>
+  <si>
+    <t>Archeus Law</t>
+  </si>
+  <si>
+    <t>Jingtian &amp; Gongcheng</t>
+  </si>
+  <si>
+    <t>1min 15</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>R&amp;P</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Mori Hamada &amp; Matsumoto</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Zhong Lun Law</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Global Law Office</t>
+  </si>
+  <si>
+    <t>Al Yaqout &amp; Al Fouzan Legal</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Anand &amp; Anand</t>
+  </si>
+  <si>
+    <t>Platon Martinez Flores San Pedro &amp; Leaño</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>TSMP</t>
+  </si>
+  <si>
+    <t>Co-effort Law</t>
+  </si>
+  <si>
+    <t>1min 13</t>
+  </si>
+  <si>
+    <t>MAQ Legal</t>
+  </si>
+  <si>
+    <t>Shook Lin &amp; Bok</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Shanghai Pacific Legal</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>HHR Lawyers</t>
+  </si>
+  <si>
+    <t>ELIG Gürkaynak</t>
+  </si>
+  <si>
+    <t>MZM Legal</t>
+  </si>
+  <si>
+    <t>Paksoy</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>King Stubb &amp; Kasiva</t>
+  </si>
+  <si>
+    <t>1min 8</t>
+  </si>
+  <si>
+    <t>City-Yuwa Partners</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Azman Davidson &amp; Co</t>
+  </si>
+  <si>
+    <t>Chien Yeh Law</t>
+  </si>
+  <si>
+    <t>2min 1</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>DFDL</t>
+  </si>
+  <si>
+    <t>2min 21</t>
+  </si>
+  <si>
+    <t>Skrine</t>
+  </si>
+  <si>
+    <t>2min 26</t>
+  </si>
+  <si>
+    <t>1min 40</t>
+  </si>
+  <si>
+    <t>1min 1</t>
+  </si>
+  <si>
+    <t>F. J. And G. De Saram</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>GLA &amp; Company</t>
+  </si>
+  <si>
+    <t>2min 54</t>
+  </si>
+  <si>
+    <t>Tongshang</t>
+  </si>
+  <si>
+    <t>TMI Associates</t>
+  </si>
+  <si>
+    <t>Jeff Leong Poon &amp; Wong</t>
+  </si>
+  <si>
+    <t>Khaitan &amp; Co</t>
+  </si>
+  <si>
+    <t>1min 5</t>
+  </si>
+  <si>
+    <t>MVGS</t>
+  </si>
+  <si>
+    <t>Duan &amp; Duan</t>
+  </si>
+  <si>
+    <t>Chang Tsi &amp; Partners</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>AMT Law</t>
+  </si>
+  <si>
+    <t>Nuno Simões &amp; Associados</t>
+  </si>
+  <si>
+    <t>Chance Bridge</t>
+  </si>
+  <si>
+    <t>1min 14</t>
+  </si>
+  <si>
+    <t>3min 59</t>
+  </si>
+  <si>
+    <t>Boss &amp; Young</t>
+  </si>
+  <si>
+    <t>V&amp;A Law</t>
+  </si>
+  <si>
+    <t>Davidson &amp; Co Legal</t>
+  </si>
+  <si>
+    <t>River Delta Law</t>
+  </si>
+  <si>
+    <t>EJE Law</t>
+  </si>
+  <si>
+    <t>1min 19</t>
+  </si>
+  <si>
+    <t>Dowway &amp; Partners</t>
+  </si>
+  <si>
+    <t>Meysan</t>
+  </si>
+  <si>
+    <t>2min 3</t>
+  </si>
+  <si>
+    <t>S&amp;R Associates</t>
+  </si>
+  <si>
+    <t>KECO Legal</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Stevenson Wong &amp; Co</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>ERM</t>
+  </si>
+  <si>
+    <t>Braun Partners</t>
+  </si>
+  <si>
+    <t>FirstLaw PC</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Hai Run</t>
+  </si>
+  <si>
+    <t>1min 28</t>
+  </si>
+  <si>
+    <t>Adnan Sundra &amp; Low</t>
+  </si>
+  <si>
+    <t>William Hendrik &amp; Siregar Djojonegoro</t>
+  </si>
+  <si>
+    <t>Gornitzky &amp; Co</t>
+  </si>
+  <si>
+    <t>1min 21</t>
+  </si>
+  <si>
+    <t>Jia Yuan Law</t>
+  </si>
+  <si>
+    <t>Ascendant Legal</t>
+  </si>
+  <si>
+    <t>3min 4</t>
+  </si>
+  <si>
+    <t>ABNR</t>
+  </si>
+  <si>
+    <t>EBN</t>
+  </si>
+  <si>
+    <t>1min 48</t>
+  </si>
+  <si>
+    <t>Al Markaz Law</t>
+  </si>
+  <si>
+    <t>Longan Law</t>
+  </si>
+  <si>
+    <t>Kan &amp; Krishme</t>
+  </si>
+  <si>
+    <t>Agmon with Tulchinsky</t>
+  </si>
+  <si>
+    <t>TTT &amp; Partners</t>
+  </si>
+  <si>
+    <t>Steinmetz Haring Gurman</t>
+  </si>
+  <si>
+    <t>Premier Chambers</t>
+  </si>
+  <si>
+    <t>1min 7</t>
+  </si>
+  <si>
+    <t>East &amp; Concord</t>
+  </si>
+  <si>
+    <t>TCLaw</t>
+  </si>
+  <si>
+    <t>2min 16</t>
+  </si>
+  <si>
+    <t>Guoyao Qindao Law</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>AnJie Broad</t>
+  </si>
+  <si>
+    <t>Cyril Amarchand Mangaldas</t>
+  </si>
+  <si>
+    <t>RSM</t>
+  </si>
+  <si>
+    <t>DeHeng</t>
+  </si>
+  <si>
+    <t>Donaldson &amp; Burkinshaw</t>
+  </si>
+  <si>
+    <t>JPM Law</t>
+  </si>
+  <si>
+    <t>1min 0</t>
+  </si>
+  <si>
+    <t>Shibolet &amp; Co</t>
+  </si>
+  <si>
+    <t>Grandway Law</t>
+  </si>
+  <si>
+    <t>Meitar Law</t>
+  </si>
+  <si>
+    <t>Poovayya</t>
+  </si>
+  <si>
+    <t>1min 18</t>
+  </si>
+  <si>
+    <t>ACIP</t>
+  </si>
+  <si>
+    <t>Luthra &amp; Luthra</t>
+  </si>
+  <si>
+    <t>Oh-Ebashi LPC &amp; Partners</t>
+  </si>
+  <si>
+    <t>Mishcon Karas</t>
+  </si>
+  <si>
+    <t>ONC</t>
+  </si>
+  <si>
+    <t>SASLO</t>
+  </si>
+  <si>
+    <t>AECO</t>
+  </si>
+  <si>
+    <t>1min 45</t>
+  </si>
+  <si>
+    <t>Llinks</t>
+  </si>
+  <si>
+    <t>Yossi Levy &amp; Co</t>
+  </si>
+  <si>
+    <t>Abe Ikubo &amp; Katayama</t>
+  </si>
+  <si>
+    <t>Aretha Legal</t>
+  </si>
+  <si>
+    <t>Ocampo &amp; Suralvo</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Amicus</t>
+  </si>
+  <si>
+    <t>Jincheng Tongda &amp; Neal</t>
+  </si>
+  <si>
+    <t>Horn &amp; Co</t>
+  </si>
+  <si>
+    <t>Stellex</t>
+  </si>
+  <si>
+    <t>Tilleke &amp; Gibbins</t>
+  </si>
+  <si>
+    <t>1min 43</t>
+  </si>
+  <si>
+    <t>Numen Law</t>
+  </si>
+  <si>
+    <t>Chandler MHM</t>
+  </si>
+  <si>
+    <t>MDP &amp; Partners</t>
+  </si>
+  <si>
+    <t>Covenant Chambers</t>
+  </si>
+  <si>
+    <t>Gallant</t>
+  </si>
+  <si>
+    <t>Oldham Li &amp; Nie</t>
+  </si>
+  <si>
+    <t>AS&amp;H Clifford Chance</t>
+  </si>
+  <si>
+    <t>Momo-o Matsuo &amp; Namba</t>
+  </si>
+  <si>
+    <t>Yulchon</t>
+  </si>
+  <si>
+    <t>1min 32</t>
+  </si>
+  <si>
+    <t>Atlas Law</t>
+  </si>
+  <si>
+    <t>AllBright Law</t>
+  </si>
+  <si>
+    <t>Lee Tsai &amp; Partners</t>
+  </si>
+  <si>
+    <t>Haiwen</t>
+  </si>
+  <si>
+    <t>Kojima Law</t>
+  </si>
+  <si>
+    <t>Woo Kwan Lee &amp; Lo</t>
+  </si>
+  <si>
+    <t>ADCO Law</t>
+  </si>
+  <si>
+    <t>BLC &amp; ASSOCIATES</t>
+  </si>
+  <si>
+    <t>Assegaf Hamzah &amp; Partners</t>
+  </si>
+  <si>
+    <t>PK Wong &amp; Nair</t>
+  </si>
+  <si>
+    <t>One Asia Lawyers</t>
+  </si>
+  <si>
+    <t>Legacy Law</t>
+  </si>
+  <si>
+    <t>Hauzen</t>
+  </si>
+  <si>
+    <t>TT&amp;A</t>
+  </si>
+  <si>
+    <t>1min 37</t>
+  </si>
+  <si>
+    <t>ASAR</t>
+  </si>
+  <si>
+    <t>Sudath Perera</t>
+  </si>
+  <si>
+    <t>KRBLaw</t>
+  </si>
+  <si>
+    <t>Saraf &amp; Partners</t>
+  </si>
+  <si>
+    <t>PSL</t>
+  </si>
+  <si>
+    <t>Allen &amp; Gledhill</t>
+  </si>
+  <si>
+    <t>Oon &amp; Bazul</t>
+  </si>
+  <si>
+    <t>Lanbai Law</t>
+  </si>
+  <si>
+    <t>GRUBA LAW</t>
+  </si>
+  <si>
+    <t>Gan Lee &amp; Tan</t>
+  </si>
+  <si>
+    <t>1min 11</t>
+  </si>
+  <si>
+    <t>SCPT</t>
+  </si>
+  <si>
+    <t>C&amp;G</t>
+  </si>
+  <si>
+    <t>ANSS</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Atsumi &amp; Sakai</t>
+  </si>
+  <si>
+    <t>Machas &amp; Partners</t>
+  </si>
+  <si>
+    <t>RHT Law</t>
+  </si>
+  <si>
+    <t>1min 30</t>
+  </si>
+  <si>
+    <t>Lee International</t>
+  </si>
+  <si>
+    <t>Robertsons Solicitors</t>
+  </si>
+  <si>
+    <t>JIPYONG</t>
+  </si>
+  <si>
+    <t>3min 3</t>
+  </si>
+  <si>
+    <t>Quiason Makalintal</t>
+  </si>
+  <si>
+    <t>2min 30</t>
+  </si>
+  <si>
+    <t>Romulo Law Firm</t>
+  </si>
+  <si>
+    <t>Miura &amp; Partners</t>
+  </si>
+  <si>
+    <t>1min 2</t>
+  </si>
+  <si>
+    <t>DR &amp; AJU</t>
+  </si>
+  <si>
+    <t>C&amp;C</t>
+  </si>
+  <si>
+    <t>1min 4</t>
+  </si>
+  <si>
+    <t>You Me</t>
+  </si>
+  <si>
+    <t>ACCRALAW</t>
+  </si>
+  <si>
+    <t>Quahe Woo &amp; Palmer</t>
+  </si>
+  <si>
+    <t>1min 46</t>
+  </si>
+  <si>
+    <t>Nagashima Ohno &amp; Tsunematsu</t>
+  </si>
+  <si>
+    <t>2min 11</t>
+  </si>
+  <si>
+    <t>TMP Intellectual Property</t>
+  </si>
+  <si>
+    <t>BSA Law</t>
+  </si>
+  <si>
+    <t>2min 40</t>
+  </si>
+  <si>
+    <t>SEUM</t>
+  </si>
+  <si>
+    <t>Tokyo International Law</t>
+  </si>
+  <si>
+    <t>1min 59</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Ushijima &amp; Partners</t>
+  </si>
+  <si>
+    <t>Matry Meiri &amp; Co</t>
+  </si>
+  <si>
+    <t>Puno Law</t>
+  </si>
+  <si>
+    <t>Argus</t>
+  </si>
+  <si>
+    <t>India Law Offices</t>
+  </si>
+  <si>
+    <t>Drew &amp; Napier</t>
+  </si>
+  <si>
+    <t>Gulapa Law</t>
+  </si>
+  <si>
+    <t>Hastings &amp; Co</t>
+  </si>
+  <si>
+    <t>Joint-Win</t>
+  </si>
+  <si>
+    <t>3min 53</t>
+  </si>
+  <si>
+    <t>Daiichi Fuyo</t>
+  </si>
+  <si>
+    <t>Erdem &amp; Erdem</t>
+  </si>
+  <si>
+    <t>Ergün Avukatlik Bürosu</t>
+  </si>
+  <si>
+    <t>Mosveldtt Law</t>
+  </si>
+  <si>
+    <t>Mochtar Karuwin Komar</t>
+  </si>
+  <si>
+    <t>2min 29</t>
+  </si>
+  <si>
+    <t>Huiye Law</t>
+  </si>
+  <si>
+    <t>Gall</t>
+  </si>
+  <si>
+    <t>SFKS Law</t>
+  </si>
+  <si>
+    <t>3min 22</t>
+  </si>
+  <si>
+    <t>Clasis Law</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>2min 36</t>
+  </si>
+  <si>
+    <t>Aitken Partners</t>
+  </si>
+  <si>
+    <t>1min 22</t>
+  </si>
+  <si>
+    <t>2min 2</t>
+  </si>
+  <si>
+    <t>Piper Alderman</t>
+  </si>
+  <si>
+    <t>Matthews Folbigg</t>
+  </si>
+  <si>
+    <t>1min 38</t>
+  </si>
+  <si>
+    <t>Chamberlains</t>
+  </si>
+  <si>
+    <t>Duncan Cotterill</t>
+  </si>
+  <si>
+    <t>Holding Redlich</t>
+  </si>
+  <si>
+    <t>Young List</t>
+  </si>
+  <si>
+    <t>1min 12</t>
+  </si>
+  <si>
+    <t>Banki Haddock Fiora</t>
+  </si>
+  <si>
+    <t>Harmos Horton Lusk</t>
+  </si>
+  <si>
+    <t>Anthony Harper</t>
+  </si>
+  <si>
+    <t>Madderns</t>
+  </si>
+  <si>
+    <t>Simmons Wolfhagen</t>
+  </si>
+  <si>
+    <t>Clayton Utz</t>
+  </si>
+  <si>
+    <t>Grette</t>
+  </si>
+  <si>
+    <t>Ai Group</t>
+  </si>
+  <si>
+    <t>Connolly Suthers</t>
+  </si>
+  <si>
+    <t>Gordon Legal</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Hamilton Locke</t>
+  </si>
+  <si>
+    <t>A J LawAndCo</t>
+  </si>
+  <si>
+    <t>Wynn Williams</t>
+  </si>
+  <si>
+    <t>1min 10</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Mayne Wetherell</t>
+  </si>
+  <si>
+    <t>Deutsch Miller</t>
+  </si>
+  <si>
+    <t>Thomson Geer</t>
+  </si>
+  <si>
+    <t>James &amp; Wells</t>
+  </si>
+  <si>
+    <t>Dahl Law</t>
+  </si>
+  <si>
+    <t>AF Mpanga</t>
+  </si>
+  <si>
+    <t>ENR Advisory</t>
+  </si>
+  <si>
+    <t>August Debouzy</t>
+  </si>
+  <si>
+    <t>FPS Law</t>
+  </si>
+  <si>
+    <t>Adams &amp; Adams</t>
+  </si>
+  <si>
+    <t>Bonelli Erede</t>
+  </si>
+  <si>
+    <t>Niederer Kraft Frey</t>
+  </si>
+  <si>
+    <t>AC&amp;R</t>
+  </si>
+  <si>
+    <t>AVM</t>
+  </si>
+  <si>
+    <t>Mccann Fitz Gerald</t>
+  </si>
+  <si>
+    <t>Filip &amp; Company</t>
+  </si>
+  <si>
+    <t>Rutgers &amp; Posch</t>
+  </si>
+  <si>
+    <t>G.Elías &amp; Muñoz</t>
+  </si>
+  <si>
+    <t>Giliberti Triscornia e Associati</t>
+  </si>
+  <si>
+    <t>Dimitrov Petrov &amp; Co</t>
+  </si>
+  <si>
+    <t>Bookbinder</t>
+  </si>
+  <si>
+    <t>WIDEN</t>
+  </si>
+  <si>
+    <t>Dottir</t>
+  </si>
+  <si>
+    <t>Niedermüller</t>
+  </si>
+  <si>
+    <t>SGP Schneider Geiwitz &amp; Partner</t>
   </si>
 </sst>
 </file>
@@ -1666,7 +2782,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C406"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.6634615384615"/>
@@ -1684,6 +2800,4461 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="1">
+        <v>279</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C2" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C3" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="1">
+        <v>318</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C4" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="1">
+        <v>362</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C5" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C6" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C7" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="1">
+        <v>429</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C8" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="1">
+        <v>308</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C9" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="1">
+        <v>367</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C10" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="1">
+        <v>458</v>
+      </c>
+      <c r="B11" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C11" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>369</v>
+      </c>
+      <c r="C12" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="1">
+        <v>388</v>
+      </c>
+      <c r="B13" t="s" s="1">
+        <v>523</v>
+      </c>
+      <c r="C13" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s" s="1">
+        <v>396</v>
+      </c>
+      <c r="C14" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="1">
+        <v>491</v>
+      </c>
+      <c r="B15" t="s" s="1">
+        <v>492</v>
+      </c>
+      <c r="C15" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s" s="1">
+        <v>270</v>
+      </c>
+      <c r="C16" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1">
+        <v>477</v>
+      </c>
+      <c r="B17" t="s" s="1">
+        <v>270</v>
+      </c>
+      <c r="C17" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s" s="1">
+        <v>355</v>
+      </c>
+      <c r="C18" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s" s="1">
+        <v>355</v>
+      </c>
+      <c r="C19" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1">
+        <v>304</v>
+      </c>
+      <c r="B20" t="s" s="1">
+        <v>305</v>
+      </c>
+      <c r="C20" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s" s="1">
+        <v>494</v>
+      </c>
+      <c r="C21" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="B22" t="s" s="1">
+        <v>410</v>
+      </c>
+      <c r="C22" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>179</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>539</v>
+      </c>
+      <c r="C23" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s" s="1">
+        <v>344</v>
+      </c>
+      <c r="C24" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="1">
+        <v>232</v>
+      </c>
+      <c r="B25" t="s" s="1">
+        <v>512</v>
+      </c>
+      <c r="C25" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="B26" t="s" s="1">
+        <v>264</v>
+      </c>
+      <c r="C26" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="1">
+        <v>328</v>
+      </c>
+      <c r="B27" t="s" s="1">
+        <v>263</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s" s="1">
+        <v>263</v>
+      </c>
+      <c r="C28" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>431</v>
+      </c>
+      <c r="B29" t="s" s="1">
+        <v>432</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s" s="1">
+        <v>242</v>
+      </c>
+      <c r="C30" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s" s="1">
+        <v>350</v>
+      </c>
+      <c r="C31" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s" s="1">
+        <v>469</v>
+      </c>
+      <c r="C32" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1">
+        <v>390</v>
+      </c>
+      <c r="B33" t="s" s="1">
+        <v>469</v>
+      </c>
+      <c r="C33" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="B34" t="s" s="1">
+        <v>469</v>
+      </c>
+      <c r="C34" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s" s="1">
+        <v>223</v>
+      </c>
+      <c r="C35" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s" s="1">
+        <v>255</v>
+      </c>
+      <c r="C36" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="1">
+        <v>321</v>
+      </c>
+      <c r="B37" t="s" s="1">
+        <v>255</v>
+      </c>
+      <c r="C37" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s" s="1">
+        <v>424</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="B39" t="s" s="1">
+        <v>326</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>479</v>
+      </c>
+      <c r="B40" t="s" s="1">
+        <v>480</v>
+      </c>
+      <c r="C40" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s" s="1">
+        <v>283</v>
+      </c>
+      <c r="C41" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B42" t="s" s="1">
+        <v>407</v>
+      </c>
+      <c r="C42" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s" s="1">
+        <v>500</v>
+      </c>
+      <c r="C43" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="1">
+        <v>391</v>
+      </c>
+      <c r="B44" t="s" s="1">
+        <v>287</v>
+      </c>
+      <c r="C44" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="B45" t="s" s="1">
+        <v>351</v>
+      </c>
+      <c r="C45" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s" s="1">
+        <v>353</v>
+      </c>
+      <c r="C46" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1">
+        <v>149</v>
+      </c>
+      <c r="B47" t="s" s="1">
+        <v>513</v>
+      </c>
+      <c r="C47" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
+        <v>319</v>
+      </c>
+      <c r="B48" t="s" s="1">
+        <v>320</v>
+      </c>
+      <c r="C48" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s" s="1">
+        <v>257</v>
+      </c>
+      <c r="C49" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="B50" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="C50" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="B51" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="C51" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="1">
+        <v>68</v>
+      </c>
+      <c r="B52" t="s" s="1">
+        <v>387</v>
+      </c>
+      <c r="C52" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="1">
+        <v>70</v>
+      </c>
+      <c r="B53" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="C53" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="B54" t="s" s="1">
+        <v>345</v>
+      </c>
+      <c r="C54" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s" s="1">
+        <v>345</v>
+      </c>
+      <c r="C55" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="B56" t="s" s="1">
+        <v>345</v>
+      </c>
+      <c r="C56" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s" s="1">
+        <v>341</v>
+      </c>
+      <c r="C57" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="1">
+        <v>90</v>
+      </c>
+      <c r="B58" t="s" s="1">
+        <v>341</v>
+      </c>
+      <c r="C58" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="B59" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="C59" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="1">
+        <v>100</v>
+      </c>
+      <c r="B60" t="s" s="1">
+        <v>226</v>
+      </c>
+      <c r="C60" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="1">
+        <v>109</v>
+      </c>
+      <c r="B61" t="s" s="1">
+        <v>226</v>
+      </c>
+      <c r="C61" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1">
+        <v>493</v>
+      </c>
+      <c r="B62" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="C62" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="B63" t="s" s="1">
+        <v>243</v>
+      </c>
+      <c r="C63" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="1">
+        <v>102</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>310</v>
+      </c>
+      <c r="C64" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="B65" t="s" s="1">
+        <v>310</v>
+      </c>
+      <c r="C65" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="1">
+        <v>151</v>
+      </c>
+      <c r="B66" t="s" s="1">
+        <v>438</v>
+      </c>
+      <c r="C66" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="1">
+        <v>85</v>
+      </c>
+      <c r="B67" t="s" s="1">
+        <v>438</v>
+      </c>
+      <c r="C67" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="B68" t="s" s="1">
+        <v>317</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="1">
+        <v>462</v>
+      </c>
+      <c r="B69" t="s" s="1">
+        <v>383</v>
+      </c>
+      <c r="C69" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>87</v>
+      </c>
+      <c r="B70" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C70" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="1">
+        <v>89</v>
+      </c>
+      <c r="B71" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C71" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="1">
+        <v>461</v>
+      </c>
+      <c r="B72" t="s" s="1">
+        <v>225</v>
+      </c>
+      <c r="C72" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="1">
+        <v>20</v>
+      </c>
+      <c r="B73" t="s" s="1">
+        <v>225</v>
+      </c>
+      <c r="C73" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="1">
+        <v>132</v>
+      </c>
+      <c r="B74" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C74" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="B75" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C75" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="B76" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C76" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="1">
+        <v>93</v>
+      </c>
+      <c r="B77" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C77" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="B78" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C78" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="B79" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C79" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="B80" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C80" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="1">
+        <v>97</v>
+      </c>
+      <c r="B81" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C81" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="1">
+        <v>481</v>
+      </c>
+      <c r="B82" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C82" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
+        <v>107</v>
+      </c>
+      <c r="B83" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C83" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="1">
+        <v>104</v>
+      </c>
+      <c r="B84" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C84" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="1">
+        <v>96</v>
+      </c>
+      <c r="B85" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C85" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="1">
+        <v>105</v>
+      </c>
+      <c r="B86" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C86" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="1">
+        <v>526</v>
+      </c>
+      <c r="B87" t="s" s="1">
+        <v>269</v>
+      </c>
+      <c r="C87" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="B88" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="C88" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="1">
+        <v>76</v>
+      </c>
+      <c r="B89" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="C89" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="1">
+        <v>327</v>
+      </c>
+      <c r="B90" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C90" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="B91" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C91" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="1">
+        <v>111</v>
+      </c>
+      <c r="B92" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C92" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="1">
+        <v>459</v>
+      </c>
+      <c r="B93" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C93" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="1">
+        <v>328</v>
+      </c>
+      <c r="B94" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C94" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="1">
+        <v>569</v>
+      </c>
+      <c r="B95" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C95" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="1">
+        <v>574</v>
+      </c>
+      <c r="B96" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C96" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="1">
+        <v>159</v>
+      </c>
+      <c r="B97" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C97" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="1">
+        <v>115</v>
+      </c>
+      <c r="B98" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C98" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="1">
+        <v>120</v>
+      </c>
+      <c r="B99" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C99" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="1">
+        <v>252</v>
+      </c>
+      <c r="B100" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C100" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="1">
+        <v>121</v>
+      </c>
+      <c r="B101" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C101" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="B102" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C102" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="1">
+        <v>123</v>
+      </c>
+      <c r="B103" t="s" s="1">
+        <v>298</v>
+      </c>
+      <c r="C103" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="B104" t="s" s="1">
+        <v>298</v>
+      </c>
+      <c r="C104" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="B105" t="s" s="1">
+        <v>298</v>
+      </c>
+      <c r="C105" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="1">
+        <v>126</v>
+      </c>
+      <c r="B106" t="s" s="1">
+        <v>298</v>
+      </c>
+      <c r="C106" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="B107" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="C107" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="1">
+        <v>139</v>
+      </c>
+      <c r="B108" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="C108" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="1">
+        <v>114</v>
+      </c>
+      <c r="B109" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C109" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="B110" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C110" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="1">
+        <v>133</v>
+      </c>
+      <c r="B111" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C111" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="1">
+        <v>129</v>
+      </c>
+      <c r="B112" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C112" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="1">
+        <v>128</v>
+      </c>
+      <c r="B113" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C113" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="1">
+        <v>565</v>
+      </c>
+      <c r="B114" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C114" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="B115" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C115" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="1">
+        <v>137</v>
+      </c>
+      <c r="B116" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C116" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="1">
+        <v>135</v>
+      </c>
+      <c r="B117" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C117" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="1">
+        <v>142</v>
+      </c>
+      <c r="B118" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C118" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="1">
+        <v>140</v>
+      </c>
+      <c r="B119" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C119" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="1">
+        <v>141</v>
+      </c>
+      <c r="B120" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C120" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="1">
+        <v>147</v>
+      </c>
+      <c r="B121" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="C121" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="1">
+        <v>162</v>
+      </c>
+      <c r="B122" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C122" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="1">
+        <v>161</v>
+      </c>
+      <c r="B123" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C123" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="1">
+        <v>165</v>
+      </c>
+      <c r="B124" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C124" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="B125" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C125" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="B126" t="s" s="1">
+        <v>412</v>
+      </c>
+      <c r="C126" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="1">
+        <v>587</v>
+      </c>
+      <c r="B127" t="s" s="1">
+        <v>412</v>
+      </c>
+      <c r="C127" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="1">
+        <v>167</v>
+      </c>
+      <c r="B128" t="s" s="1">
+        <v>289</v>
+      </c>
+      <c r="C128" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="B129" t="s" s="1">
+        <v>289</v>
+      </c>
+      <c r="C129" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="B130" t="s" s="1">
+        <v>227</v>
+      </c>
+      <c r="C130" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="1">
+        <v>168</v>
+      </c>
+      <c r="B131" t="s" s="1">
+        <v>227</v>
+      </c>
+      <c r="C131" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="1">
+        <v>576</v>
+      </c>
+      <c r="B132" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C132" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="B133" t="s" s="1">
+        <v>231</v>
+      </c>
+      <c r="C133" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="1">
+        <v>171</v>
+      </c>
+      <c r="B134" t="s" s="1">
+        <v>231</v>
+      </c>
+      <c r="C134" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="1">
+        <v>380</v>
+      </c>
+      <c r="B135" t="s" s="1">
+        <v>381</v>
+      </c>
+      <c r="C135" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="1">
+        <v>439</v>
+      </c>
+      <c r="B136" t="s" s="1">
+        <v>381</v>
+      </c>
+      <c r="C136" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="1">
+        <v>174</v>
+      </c>
+      <c r="B137" t="s" s="1">
+        <v>484</v>
+      </c>
+      <c r="C137" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="B138" t="s" s="1">
+        <v>244</v>
+      </c>
+      <c r="C138" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="1">
+        <v>177</v>
+      </c>
+      <c r="B139" t="s" s="1">
+        <v>181</v>
+      </c>
+      <c r="C139" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="1">
+        <v>532</v>
+      </c>
+      <c r="B140" t="s" s="1">
+        <v>533</v>
+      </c>
+      <c r="C140" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="1">
+        <v>508</v>
+      </c>
+      <c r="B141" t="s" s="1">
+        <v>509</v>
+      </c>
+      <c r="C141" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="1">
+        <v>535</v>
+      </c>
+      <c r="B142" t="s" s="1">
+        <v>536</v>
+      </c>
+      <c r="C142" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="1">
+        <v>528</v>
+      </c>
+      <c r="B143" t="s" s="1">
+        <v>529</v>
+      </c>
+      <c r="C143" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="1">
+        <v>348</v>
+      </c>
+      <c r="B144" t="s" s="1">
+        <v>349</v>
+      </c>
+      <c r="C144" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="1">
+        <v>346</v>
+      </c>
+      <c r="B145" t="s" s="1">
+        <v>347</v>
+      </c>
+      <c r="C145" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="1">
+        <v>505</v>
+      </c>
+      <c r="B146" t="s" s="1">
+        <v>506</v>
+      </c>
+      <c r="C146" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="1">
+        <v>377</v>
+      </c>
+      <c r="B147" t="s" s="1">
+        <v>378</v>
+      </c>
+      <c r="C147" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="1">
+        <v>501</v>
+      </c>
+      <c r="B148" t="s" s="1">
+        <v>378</v>
+      </c>
+      <c r="C148" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B149" t="s" s="1">
+        <v>264</v>
+      </c>
+      <c r="C149" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="1">
+        <v>414</v>
+      </c>
+      <c r="B150" t="s" s="1">
+        <v>264</v>
+      </c>
+      <c r="C150" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="1">
+        <v>417</v>
+      </c>
+      <c r="B151" t="s" s="1">
+        <v>264</v>
+      </c>
+      <c r="C151" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="1">
+        <v>398</v>
+      </c>
+      <c r="B152" t="s" s="1">
+        <v>399</v>
+      </c>
+      <c r="C152" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="1">
+        <v>262</v>
+      </c>
+      <c r="B153" t="s" s="1">
+        <v>263</v>
+      </c>
+      <c r="C153" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="1">
+        <v>503</v>
+      </c>
+      <c r="B154" t="s" s="1">
+        <v>504</v>
+      </c>
+      <c r="C154" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="1">
+        <v>241</v>
+      </c>
+      <c r="B155" t="s" s="1">
+        <v>242</v>
+      </c>
+      <c r="C155" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="1">
+        <v>251</v>
+      </c>
+      <c r="B156" t="s" s="1">
+        <v>242</v>
+      </c>
+      <c r="C156" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="1">
+        <v>443</v>
+      </c>
+      <c r="B157" t="s" s="1">
+        <v>444</v>
+      </c>
+      <c r="C157" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="1">
+        <v>541</v>
+      </c>
+      <c r="B158" t="s" s="1">
+        <v>542</v>
+      </c>
+      <c r="C158" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="1">
+        <v>453</v>
+      </c>
+      <c r="B159" t="s" s="1">
+        <v>454</v>
+      </c>
+      <c r="C159" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="1">
+        <v>487</v>
+      </c>
+      <c r="B160" t="s" s="1">
+        <v>488</v>
+      </c>
+      <c r="C160" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="1">
+        <v>388</v>
+      </c>
+      <c r="B161" t="s" s="1">
+        <v>389</v>
+      </c>
+      <c r="C161" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="1">
+        <v>284</v>
+      </c>
+      <c r="B162" t="s" s="1">
+        <v>285</v>
+      </c>
+      <c r="C162" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="1">
+        <v>190</v>
+      </c>
+      <c r="B163" t="s" s="1">
+        <v>538</v>
+      </c>
+      <c r="C163" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="1">
+        <v>392</v>
+      </c>
+      <c r="B164" t="s" s="1">
+        <v>393</v>
+      </c>
+      <c r="C164" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="1">
+        <v>296</v>
+      </c>
+      <c r="B165" t="s" s="1">
+        <v>297</v>
+      </c>
+      <c r="C165" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="1">
+        <v>374</v>
+      </c>
+      <c r="B166" t="s" s="1">
+        <v>375</v>
+      </c>
+      <c r="C166" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="1">
+        <v>423</v>
+      </c>
+      <c r="B167" t="s" s="1">
+        <v>424</v>
+      </c>
+      <c r="C167" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="B168" t="s" s="1">
+        <v>218</v>
+      </c>
+      <c r="C168" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="1">
+        <v>397</v>
+      </c>
+      <c r="B169" t="s" s="1">
+        <v>218</v>
+      </c>
+      <c r="C169" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="1">
+        <v>552</v>
+      </c>
+      <c r="B170" t="s" s="1">
+        <v>218</v>
+      </c>
+      <c r="C170" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="1">
+        <v>182</v>
+      </c>
+      <c r="B171" t="s" s="1">
+        <v>218</v>
+      </c>
+      <c r="C171" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="1">
+        <v>308</v>
+      </c>
+      <c r="B172" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C172" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="1">
+        <v>334</v>
+      </c>
+      <c r="B173" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C173" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="1">
+        <v>559</v>
+      </c>
+      <c r="B174" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C174" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="1">
+        <v>367</v>
+      </c>
+      <c r="B175" t="s" s="1">
+        <v>368</v>
+      </c>
+      <c r="C175" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="1">
+        <v>325</v>
+      </c>
+      <c r="B176" t="s" s="1">
+        <v>326</v>
+      </c>
+      <c r="C176" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="1">
+        <v>394</v>
+      </c>
+      <c r="B177" t="s" s="1">
+        <v>326</v>
+      </c>
+      <c r="C177" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="1">
+        <v>186</v>
+      </c>
+      <c r="B178" t="s" s="1">
+        <v>547</v>
+      </c>
+      <c r="C178" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="1">
+        <v>561</v>
+      </c>
+      <c r="B179" t="s" s="1">
+        <v>562</v>
+      </c>
+      <c r="C179" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="1">
+        <v>282</v>
+      </c>
+      <c r="B180" t="s" s="1">
+        <v>283</v>
+      </c>
+      <c r="C180" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="1">
+        <v>338</v>
+      </c>
+      <c r="B181" t="s" s="1">
+        <v>339</v>
+      </c>
+      <c r="C181" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="1">
+        <v>185</v>
+      </c>
+      <c r="B182" t="s" s="1">
+        <v>407</v>
+      </c>
+      <c r="C182" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="1">
+        <v>585</v>
+      </c>
+      <c r="B183" t="s" s="1">
+        <v>407</v>
+      </c>
+      <c r="C183" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="1">
+        <v>302</v>
+      </c>
+      <c r="B184" t="s" s="1">
+        <v>303</v>
+      </c>
+      <c r="C184" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="B185" t="s" s="1">
+        <v>303</v>
+      </c>
+      <c r="C185" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="1">
+        <v>359</v>
+      </c>
+      <c r="B186" t="s" s="1">
+        <v>360</v>
+      </c>
+      <c r="C186" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="1">
+        <v>499</v>
+      </c>
+      <c r="B187" t="s" s="1">
+        <v>500</v>
+      </c>
+      <c r="C187" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="1">
+        <v>583</v>
+      </c>
+      <c r="B188" t="s" s="1">
+        <v>500</v>
+      </c>
+      <c r="C188" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="1">
+        <v>286</v>
+      </c>
+      <c r="B189" t="s" s="1">
+        <v>287</v>
+      </c>
+      <c r="C189" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="1">
+        <v>252</v>
+      </c>
+      <c r="B190" t="s" s="1">
+        <v>287</v>
+      </c>
+      <c r="C190" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="1">
+        <v>584</v>
+      </c>
+      <c r="B191" t="s" s="1">
+        <v>287</v>
+      </c>
+      <c r="C191" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="1">
+        <v>496</v>
+      </c>
+      <c r="B192" t="s" s="1">
+        <v>497</v>
+      </c>
+      <c r="C192" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="1">
+        <v>195</v>
+      </c>
+      <c r="B193" t="s" s="1">
+        <v>497</v>
+      </c>
+      <c r="C193" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="1">
+        <v>517</v>
+      </c>
+      <c r="B194" t="s" s="1">
+        <v>351</v>
+      </c>
+      <c r="C194" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="1">
+        <v>193</v>
+      </c>
+      <c r="B195" t="s" s="1">
+        <v>351</v>
+      </c>
+      <c r="C195" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="1">
+        <v>184</v>
+      </c>
+      <c r="B196" t="s" s="1">
+        <v>351</v>
+      </c>
+      <c r="C196" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="1">
+        <v>572</v>
+      </c>
+      <c r="B197" t="s" s="1">
+        <v>351</v>
+      </c>
+      <c r="C197" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="1">
+        <v>586</v>
+      </c>
+      <c r="B198" t="s" s="1">
+        <v>351</v>
+      </c>
+      <c r="C198" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="B199" t="s" s="1">
+        <v>419</v>
+      </c>
+      <c r="C199" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="1">
+        <v>551</v>
+      </c>
+      <c r="B200" t="s" s="1">
+        <v>419</v>
+      </c>
+      <c r="C200" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="1">
+        <v>273</v>
+      </c>
+      <c r="B201" t="s" s="1">
+        <v>274</v>
+      </c>
+      <c r="C201" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="1">
+        <v>324</v>
+      </c>
+      <c r="B202" t="s" s="1">
+        <v>274</v>
+      </c>
+      <c r="C202" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="1">
+        <v>373</v>
+      </c>
+      <c r="B203" t="s" s="1">
+        <v>274</v>
+      </c>
+      <c r="C203" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="1">
+        <v>457</v>
+      </c>
+      <c r="B204" t="s" s="1">
+        <v>274</v>
+      </c>
+      <c r="C204" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="1">
+        <v>515</v>
+      </c>
+      <c r="B205" t="s" s="1">
+        <v>274</v>
+      </c>
+      <c r="C205" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="1">
+        <v>370</v>
+      </c>
+      <c r="B206" t="s" s="1">
+        <v>353</v>
+      </c>
+      <c r="C206" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="1">
+        <v>433</v>
+      </c>
+      <c r="B207" t="s" s="1">
+        <v>353</v>
+      </c>
+      <c r="C207" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="1">
+        <v>228</v>
+      </c>
+      <c r="B208" t="s" s="1">
+        <v>229</v>
+      </c>
+      <c r="C208" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="1">
+        <v>540</v>
+      </c>
+      <c r="B209" t="s" s="1">
+        <v>229</v>
+      </c>
+      <c r="C209" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="1">
+        <v>401</v>
+      </c>
+      <c r="B210" t="s" s="1">
+        <v>320</v>
+      </c>
+      <c r="C210" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="1">
+        <v>482</v>
+      </c>
+      <c r="B211" t="s" s="1">
+        <v>320</v>
+      </c>
+      <c r="C211" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="1">
+        <v>502</v>
+      </c>
+      <c r="B212" t="s" s="1">
+        <v>320</v>
+      </c>
+      <c r="C212" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="1">
+        <v>191</v>
+      </c>
+      <c r="B213" t="s" s="1">
+        <v>563</v>
+      </c>
+      <c r="C213" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="1">
+        <v>567</v>
+      </c>
+      <c r="B214" t="s" s="1">
+        <v>563</v>
+      </c>
+      <c r="C214" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="1">
+        <v>577</v>
+      </c>
+      <c r="B215" t="s" s="1">
+        <v>563</v>
+      </c>
+      <c r="C215" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="1">
+        <v>256</v>
+      </c>
+      <c r="B216" t="s" s="1">
+        <v>257</v>
+      </c>
+      <c r="C216" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="1">
+        <v>546</v>
+      </c>
+      <c r="B217" t="s" s="1">
+        <v>257</v>
+      </c>
+      <c r="C217" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="1">
+        <v>336</v>
+      </c>
+      <c r="B218" t="s" s="1">
+        <v>337</v>
+      </c>
+      <c r="C218" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="B219" t="s" s="1">
+        <v>337</v>
+      </c>
+      <c r="C219" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="1">
+        <v>578</v>
+      </c>
+      <c r="B220" t="s" s="1">
+        <v>337</v>
+      </c>
+      <c r="C220" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="1">
+        <v>306</v>
+      </c>
+      <c r="B221" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="C221" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="1">
+        <v>395</v>
+      </c>
+      <c r="B222" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="C222" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="1">
+        <v>402</v>
+      </c>
+      <c r="B223" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="C223" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="1">
+        <v>328</v>
+      </c>
+      <c r="B224" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="C224" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="1">
+        <v>352</v>
+      </c>
+      <c r="B225" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="C225" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="1">
+        <v>468</v>
+      </c>
+      <c r="B226" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="C226" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="1">
+        <v>470</v>
+      </c>
+      <c r="B227" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="C227" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="1">
+        <v>386</v>
+      </c>
+      <c r="B228" t="s" s="1">
+        <v>387</v>
+      </c>
+      <c r="C228" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="1">
+        <v>440</v>
+      </c>
+      <c r="B229" t="s" s="1">
+        <v>387</v>
+      </c>
+      <c r="C229" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="1">
+        <v>456</v>
+      </c>
+      <c r="B230" t="s" s="1">
+        <v>387</v>
+      </c>
+      <c r="C230" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="1">
+        <v>467</v>
+      </c>
+      <c r="B231" t="s" s="1">
+        <v>387</v>
+      </c>
+      <c r="C231" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="1">
+        <v>489</v>
+      </c>
+      <c r="B232" t="s" s="1">
+        <v>387</v>
+      </c>
+      <c r="C232" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="1">
+        <v>277</v>
+      </c>
+      <c r="B233" t="s" s="1">
+        <v>278</v>
+      </c>
+      <c r="C233" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="1">
+        <v>290</v>
+      </c>
+      <c r="B234" t="s" s="1">
+        <v>278</v>
+      </c>
+      <c r="C234" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="1">
+        <v>362</v>
+      </c>
+      <c r="B235" t="s" s="1">
+        <v>278</v>
+      </c>
+      <c r="C235" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="1">
+        <v>366</v>
+      </c>
+      <c r="B236" t="s" s="1">
+        <v>278</v>
+      </c>
+      <c r="C236" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="1">
+        <v>340</v>
+      </c>
+      <c r="B237" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="C237" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="1">
+        <v>356</v>
+      </c>
+      <c r="B238" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="C238" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="1">
+        <v>420</v>
+      </c>
+      <c r="B239" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="C239" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="1">
+        <v>476</v>
+      </c>
+      <c r="B240" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="C240" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="1">
+        <v>543</v>
+      </c>
+      <c r="B241" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="C241" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="1">
+        <v>573</v>
+      </c>
+      <c r="B242" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="C242" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="B243" t="s" s="1">
+        <v>332</v>
+      </c>
+      <c r="C243" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="1">
+        <v>342</v>
+      </c>
+      <c r="B244" t="s" s="1">
+        <v>332</v>
+      </c>
+      <c r="C244" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="1">
+        <v>371</v>
+      </c>
+      <c r="B245" t="s" s="1">
+        <v>332</v>
+      </c>
+      <c r="C245" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="1">
+        <v>426</v>
+      </c>
+      <c r="B246" t="s" s="1">
+        <v>332</v>
+      </c>
+      <c r="C246" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="1">
+        <v>361</v>
+      </c>
+      <c r="B247" t="s" s="1">
+        <v>345</v>
+      </c>
+      <c r="C247" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="1">
+        <v>408</v>
+      </c>
+      <c r="B248" t="s" s="1">
+        <v>345</v>
+      </c>
+      <c r="C248" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="1">
+        <v>510</v>
+      </c>
+      <c r="B249" t="s" s="1">
+        <v>345</v>
+      </c>
+      <c r="C249" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="1">
+        <v>376</v>
+      </c>
+      <c r="B250" t="s" s="1">
+        <v>341</v>
+      </c>
+      <c r="C250" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="1">
+        <v>416</v>
+      </c>
+      <c r="B251" t="s" s="1">
+        <v>341</v>
+      </c>
+      <c r="C251" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="1">
+        <v>199</v>
+      </c>
+      <c r="B252" t="s" s="1">
+        <v>558</v>
+      </c>
+      <c r="C252" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="1">
+        <v>568</v>
+      </c>
+      <c r="B253" t="s" s="1">
+        <v>558</v>
+      </c>
+      <c r="C253" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="B254" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="C254" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="1">
+        <v>372</v>
+      </c>
+      <c r="B255" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="C255" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="1">
+        <v>442</v>
+      </c>
+      <c r="B256" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="C256" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="1">
+        <v>448</v>
+      </c>
+      <c r="B257" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="C257" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="1">
+        <v>450</v>
+      </c>
+      <c r="B258" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="C258" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="1">
+        <v>471</v>
+      </c>
+      <c r="B259" t="s" s="1">
+        <v>226</v>
+      </c>
+      <c r="C259" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="1">
+        <v>525</v>
+      </c>
+      <c r="B260" t="s" s="1">
+        <v>226</v>
+      </c>
+      <c r="C260" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="1">
+        <v>245</v>
+      </c>
+      <c r="B261" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="C261" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="1">
+        <v>343</v>
+      </c>
+      <c r="B262" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="C262" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="1">
+        <v>436</v>
+      </c>
+      <c r="B263" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="C263" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="1">
+        <v>511</v>
+      </c>
+      <c r="B264" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="C264" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="1">
+        <v>519</v>
+      </c>
+      <c r="B265" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="C265" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="B266" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="C266" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="1">
+        <v>333</v>
+      </c>
+      <c r="B267" t="s" s="1">
+        <v>243</v>
+      </c>
+      <c r="C267" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="1">
+        <v>335</v>
+      </c>
+      <c r="B268" t="s" s="1">
+        <v>243</v>
+      </c>
+      <c r="C268" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="1">
+        <v>544</v>
+      </c>
+      <c r="B269" t="s" s="1">
+        <v>243</v>
+      </c>
+      <c r="C269" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="1">
+        <v>441</v>
+      </c>
+      <c r="B270" t="s" s="1">
+        <v>310</v>
+      </c>
+      <c r="C270" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="B271" t="s" s="1">
+        <v>310</v>
+      </c>
+      <c r="C271" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="1">
+        <v>530</v>
+      </c>
+      <c r="B272" t="s" s="1">
+        <v>438</v>
+      </c>
+      <c r="C272" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="1">
+        <v>486</v>
+      </c>
+      <c r="B273" t="s" s="1">
+        <v>317</v>
+      </c>
+      <c r="C273" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="1">
+        <v>550</v>
+      </c>
+      <c r="B274" t="s" s="1">
+        <v>317</v>
+      </c>
+      <c r="C274" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="B275" t="s" s="1">
+        <v>317</v>
+      </c>
+      <c r="C275" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="1">
+        <v>330</v>
+      </c>
+      <c r="B276" t="s" s="1">
+        <v>331</v>
+      </c>
+      <c r="C276" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="1">
+        <v>365</v>
+      </c>
+      <c r="B277" t="s" s="1">
+        <v>331</v>
+      </c>
+      <c r="C277" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="B278" t="s" s="1">
+        <v>331</v>
+      </c>
+      <c r="C278" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="1">
+        <v>382</v>
+      </c>
+      <c r="B279" t="s" s="1">
+        <v>383</v>
+      </c>
+      <c r="C279" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="1">
+        <v>322</v>
+      </c>
+      <c r="B280" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C280" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="1">
+        <v>522</v>
+      </c>
+      <c r="B281" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C281" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="1">
+        <v>224</v>
+      </c>
+      <c r="B282" t="s" s="1">
+        <v>225</v>
+      </c>
+      <c r="C282" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="1">
+        <v>428</v>
+      </c>
+      <c r="B283" t="s" s="1">
+        <v>225</v>
+      </c>
+      <c r="C283" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="1">
+        <v>435</v>
+      </c>
+      <c r="B284" t="s" s="1">
+        <v>225</v>
+      </c>
+      <c r="C284" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="1">
+        <v>311</v>
+      </c>
+      <c r="B285" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C285" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="1">
+        <v>418</v>
+      </c>
+      <c r="B286" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C286" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="1">
+        <v>537</v>
+      </c>
+      <c r="B287" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C287" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="1">
+        <v>201</v>
+      </c>
+      <c r="B288" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C288" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="1">
+        <v>575</v>
+      </c>
+      <c r="B289" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C289" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="1">
+        <v>288</v>
+      </c>
+      <c r="B290" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C290" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="1">
+        <v>483</v>
+      </c>
+      <c r="B291" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C291" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="1">
+        <v>516</v>
+      </c>
+      <c r="B292" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C292" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="1">
+        <v>554</v>
+      </c>
+      <c r="B293" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C293" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="1">
+        <v>579</v>
+      </c>
+      <c r="B294" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C294" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="1">
+        <v>271</v>
+      </c>
+      <c r="B295" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C295" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="1">
+        <v>430</v>
+      </c>
+      <c r="B296" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C296" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="1">
+        <v>473</v>
+      </c>
+      <c r="B297" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C297" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="1">
+        <v>474</v>
+      </c>
+      <c r="B298" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C298" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="1">
+        <v>507</v>
+      </c>
+      <c r="B299" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C299" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="1">
+        <v>210</v>
+      </c>
+      <c r="B300" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="C300" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="1">
+        <v>275</v>
+      </c>
+      <c r="B301" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C301" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="1">
+        <v>291</v>
+      </c>
+      <c r="B302" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C302" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="1">
+        <v>385</v>
+      </c>
+      <c r="B303" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C303" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="1">
+        <v>464</v>
+      </c>
+      <c r="B304" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C304" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="1">
+        <v>485</v>
+      </c>
+      <c r="B305" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C305" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="1">
+        <v>556</v>
+      </c>
+      <c r="B306" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="C306" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="1">
+        <v>268</v>
+      </c>
+      <c r="B307" t="s" s="1">
+        <v>269</v>
+      </c>
+      <c r="C307" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="B308" t="s" s="1">
+        <v>269</v>
+      </c>
+      <c r="C308" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="1">
+        <v>354</v>
+      </c>
+      <c r="B309" t="s" s="1">
+        <v>269</v>
+      </c>
+      <c r="C309" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="1">
+        <v>294</v>
+      </c>
+      <c r="B310" t="s" s="1">
+        <v>295</v>
+      </c>
+      <c r="C310" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="1">
+        <v>403</v>
+      </c>
+      <c r="B311" t="s" s="1">
+        <v>295</v>
+      </c>
+      <c r="C311" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="1">
+        <v>409</v>
+      </c>
+      <c r="B312" t="s" s="1">
+        <v>295</v>
+      </c>
+      <c r="C312" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="1">
+        <v>434</v>
+      </c>
+      <c r="B313" t="s" s="1">
+        <v>295</v>
+      </c>
+      <c r="C313" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="1">
+        <v>520</v>
+      </c>
+      <c r="B314" t="s" s="1">
+        <v>295</v>
+      </c>
+      <c r="C314" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="1">
+        <v>384</v>
+      </c>
+      <c r="B315" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="C315" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="1">
+        <v>421</v>
+      </c>
+      <c r="B316" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="C316" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="1">
+        <v>478</v>
+      </c>
+      <c r="B317" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="C317" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="1">
+        <v>514</v>
+      </c>
+      <c r="B318" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="C318" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="1">
+        <v>564</v>
+      </c>
+      <c r="B319" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="C319" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="1">
+        <v>232</v>
+      </c>
+      <c r="B320" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C320" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="1">
+        <v>266</v>
+      </c>
+      <c r="B321" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C321" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="1">
+        <v>117</v>
+      </c>
+      <c r="B322" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C322" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="B323" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C323" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="1">
+        <v>390</v>
+      </c>
+      <c r="B324" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C324" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="1">
+        <v>449</v>
+      </c>
+      <c r="B325" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C325" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="1">
+        <v>534</v>
+      </c>
+      <c r="B326" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C326" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="1">
+        <v>207</v>
+      </c>
+      <c r="B327" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C327" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="1">
+        <v>204</v>
+      </c>
+      <c r="B328" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="C328" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="1">
+        <v>292</v>
+      </c>
+      <c r="B329" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C329" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="1">
+        <v>299</v>
+      </c>
+      <c r="B330" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C330" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="1">
+        <v>406</v>
+      </c>
+      <c r="B331" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C331" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="1">
+        <v>452</v>
+      </c>
+      <c r="B332" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C332" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="1">
+        <v>527</v>
+      </c>
+      <c r="B333" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C333" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="1">
+        <v>202</v>
+      </c>
+      <c r="B334" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C334" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="1">
+        <v>548</v>
+      </c>
+      <c r="B335" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C335" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="B336" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="C336" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="1">
+        <v>234</v>
+      </c>
+      <c r="B337" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C337" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="1">
+        <v>240</v>
+      </c>
+      <c r="B338" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C338" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="1">
+        <v>358</v>
+      </c>
+      <c r="B339" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C339" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="1">
+        <v>413</v>
+      </c>
+      <c r="B340" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C340" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="1">
+        <v>531</v>
+      </c>
+      <c r="B341" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C341" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="1">
+        <v>212</v>
+      </c>
+      <c r="B342" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C342" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="1">
+        <v>566</v>
+      </c>
+      <c r="B343" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="C343" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="1">
+        <v>446</v>
+      </c>
+      <c r="B344" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C344" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="1">
+        <v>447</v>
+      </c>
+      <c r="B345" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C345" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="1">
+        <v>455</v>
+      </c>
+      <c r="B346" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C346" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="1">
+        <v>472</v>
+      </c>
+      <c r="B347" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C347" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s" s="1">
+        <v>490</v>
+      </c>
+      <c r="B348" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C348" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="1">
+        <v>524</v>
+      </c>
+      <c r="B349" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C349" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s" s="1">
+        <v>209</v>
+      </c>
+      <c r="B350" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="C350" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s" s="1">
+        <v>400</v>
+      </c>
+      <c r="B351" t="s" s="1">
+        <v>298</v>
+      </c>
+      <c r="C351" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s" s="1">
+        <v>415</v>
+      </c>
+      <c r="B352" t="s" s="1">
+        <v>298</v>
+      </c>
+      <c r="C352" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="1">
+        <v>545</v>
+      </c>
+      <c r="B353" t="s" s="1">
+        <v>298</v>
+      </c>
+      <c r="C353" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="1">
+        <v>315</v>
+      </c>
+      <c r="B354" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="C354" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s" s="1">
+        <v>463</v>
+      </c>
+      <c r="B355" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="C355" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s" s="1">
+        <v>495</v>
+      </c>
+      <c r="B356" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="C356" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s" s="1">
+        <v>213</v>
+      </c>
+      <c r="B357" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="C357" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s" s="1">
+        <v>557</v>
+      </c>
+      <c r="B358" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="C358" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="1">
+        <v>581</v>
+      </c>
+      <c r="B359" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="C359" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="B360" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C360" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="B361" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C361" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="1">
+        <v>560</v>
+      </c>
+      <c r="B362" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C362" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="1">
+        <v>582</v>
+      </c>
+      <c r="B363" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="C363" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="1">
+        <v>236</v>
+      </c>
+      <c r="B364" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C364" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="1">
+        <v>250</v>
+      </c>
+      <c r="B365" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C365" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s" s="1">
+        <v>281</v>
+      </c>
+      <c r="B366" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C366" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s" s="1">
+        <v>422</v>
+      </c>
+      <c r="B367" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C367" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s" s="1">
+        <v>458</v>
+      </c>
+      <c r="B368" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C368" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s" s="1">
+        <v>465</v>
+      </c>
+      <c r="B369" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C369" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="B370" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C370" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="1">
+        <v>215</v>
+      </c>
+      <c r="B371" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="C371" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="1">
+        <v>238</v>
+      </c>
+      <c r="B372" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C372" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="1">
+        <v>300</v>
+      </c>
+      <c r="B373" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C373" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="1">
+        <v>405</v>
+      </c>
+      <c r="B374" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C374" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="1">
+        <v>518</v>
+      </c>
+      <c r="B375" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C375" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="1">
+        <v>549</v>
+      </c>
+      <c r="B376" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C376" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="1">
+        <v>216</v>
+      </c>
+      <c r="B377" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C377" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="1">
+        <v>588</v>
+      </c>
+      <c r="B378" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="C378" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="1">
+        <v>425</v>
+      </c>
+      <c r="B379" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="C379" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="1">
+        <v>437</v>
+      </c>
+      <c r="B380" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="C380" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="1">
+        <v>466</v>
+      </c>
+      <c r="B381" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="C381" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="1">
+        <v>521</v>
+      </c>
+      <c r="B382" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="C382" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="B383" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="C383" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="1">
+        <v>580</v>
+      </c>
+      <c r="B384" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="C384" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="1">
+        <v>214</v>
+      </c>
+      <c r="B385" t="s" s="1">
+        <v>220</v>
+      </c>
+      <c r="C385" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="1">
+        <v>460</v>
+      </c>
+      <c r="B386" t="s" s="1">
+        <v>220</v>
+      </c>
+      <c r="C386" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="1">
+        <v>248</v>
+      </c>
+      <c r="B387" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C387" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="1">
+        <v>357</v>
+      </c>
+      <c r="B388" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C388" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="1">
+        <v>379</v>
+      </c>
+      <c r="B389" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C389" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="1">
+        <v>427</v>
+      </c>
+      <c r="B390" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C390" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="1">
+        <v>411</v>
+      </c>
+      <c r="B391" t="s" s="1">
+        <v>412</v>
+      </c>
+      <c r="C391" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="1">
+        <v>498</v>
+      </c>
+      <c r="B392" t="s" s="1">
+        <v>412</v>
+      </c>
+      <c r="C392" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="1">
+        <v>555</v>
+      </c>
+      <c r="B393" t="s" s="1">
+        <v>412</v>
+      </c>
+      <c r="C393" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="1">
+        <v>301</v>
+      </c>
+      <c r="B394" t="s" s="1">
+        <v>289</v>
+      </c>
+      <c r="C394" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="1">
+        <v>445</v>
+      </c>
+      <c r="B395" t="s" s="1">
+        <v>227</v>
+      </c>
+      <c r="C395" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="1">
+        <v>570</v>
+      </c>
+      <c r="B396" t="s" s="1">
+        <v>227</v>
+      </c>
+      <c r="C396" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="1">
+        <v>221</v>
+      </c>
+      <c r="B397" t="s" s="1">
+        <v>222</v>
+      </c>
+      <c r="C397" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="1">
+        <v>553</v>
+      </c>
+      <c r="B398" t="s" s="1">
+        <v>222</v>
+      </c>
+      <c r="C398" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B399" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C399" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="1">
+        <v>404</v>
+      </c>
+      <c r="B400" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C400" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="1">
+        <v>571</v>
+      </c>
+      <c r="B401" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C401" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s" s="1">
+        <v>230</v>
+      </c>
+      <c r="B402" t="s" s="1">
+        <v>231</v>
+      </c>
+      <c r="C402" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s" s="1">
+        <v>451</v>
+      </c>
+      <c r="B403" t="s" s="1">
+        <v>381</v>
+      </c>
+      <c r="C403" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="B404" t="s" s="1">
+        <v>260</v>
+      </c>
+      <c r="C404" t="s" s="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s" s="1">
+        <v>475</v>
+      </c>
+      <c r="B405" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="C405" t="s" s="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="1">
+        <v>313</v>
+      </c>
+      <c r="B406" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="C406" t="s" s="1">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/core/src/main/resources/baseFiles/excel/Reports.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Reports.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="559">
   <si>
     <t>Firm</t>
   </si>
@@ -676,6 +676,1035 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>William Freire Advogados</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Santamarina And Steta</t>
+  </si>
+  <si>
+    <t>Brigrard Urrutia</t>
+  </si>
+  <si>
+    <t>Rosselló Abogados</t>
+  </si>
+  <si>
+    <t>Mello Torres</t>
+  </si>
+  <si>
+    <t>Nassar</t>
+  </si>
+  <si>
+    <t>Benson Buffett</t>
+  </si>
+  <si>
+    <t>Rossi, Maffini, Milman &amp; Grando</t>
+  </si>
+  <si>
+    <t>GNB Law</t>
+  </si>
+  <si>
+    <t>Felsberg</t>
+  </si>
+  <si>
+    <t>Lawson Lundell</t>
+  </si>
+  <si>
+    <t>Leaf</t>
+  </si>
+  <si>
+    <t>BWB LLP</t>
+  </si>
+  <si>
+    <t>L&amp;E Global</t>
+  </si>
+  <si>
+    <t>1min 52</t>
+  </si>
+  <si>
+    <t>OlarteMoure</t>
+  </si>
+  <si>
+    <t>Vazquez Tercero And Zepeda</t>
+  </si>
+  <si>
+    <t>Pietrantoni Méndez &amp; Alvarez LLC</t>
+  </si>
+  <si>
+    <t>Perez Correa Gonzalez</t>
+  </si>
+  <si>
+    <t>Velloza</t>
+  </si>
+  <si>
+    <t>Spingarn</t>
+  </si>
+  <si>
+    <t>Rodríguez Angobaldo</t>
+  </si>
+  <si>
+    <t>Icaza González-Ruiz &amp; Alemán</t>
+  </si>
+  <si>
+    <t>Mijares Angoitia Cortés And Fuentes</t>
+  </si>
+  <si>
+    <t>1min 15</t>
+  </si>
+  <si>
+    <t>Deeth Williams Wall</t>
+  </si>
+  <si>
+    <t>Goodmans</t>
+  </si>
+  <si>
+    <t>Stikeman Elliott</t>
+  </si>
+  <si>
+    <t>1min 31</t>
+  </si>
+  <si>
+    <t>Dias De Souza</t>
+  </si>
+  <si>
+    <t>BBGS</t>
+  </si>
+  <si>
+    <t>2min 8</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Myers Fletcher And Gordon</t>
+  </si>
+  <si>
+    <t>Ernesto Borges</t>
+  </si>
+  <si>
+    <t>Machado Meyer</t>
+  </si>
+  <si>
+    <t>Ibañez Parkman</t>
+  </si>
+  <si>
+    <t>1min 16</t>
+  </si>
+  <si>
+    <t>Morgan &amp; Morgan</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Sangra</t>
+  </si>
+  <si>
+    <t>Galindo, Arias &amp; López</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Tumnet</t>
+  </si>
+  <si>
+    <t>ZBV</t>
+  </si>
+  <si>
+    <t>Miranda &amp; Amado</t>
+  </si>
+  <si>
+    <t>CAR Advogados</t>
+  </si>
+  <si>
+    <t>Lerners</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Guerrero Olivos</t>
+  </si>
+  <si>
+    <t>BCF Law</t>
+  </si>
+  <si>
+    <t>GSA Legal</t>
+  </si>
+  <si>
+    <t>BULLRICH FLANZBAUM</t>
+  </si>
+  <si>
+    <t>NHM</t>
+  </si>
+  <si>
+    <t>Cozen O’Connor</t>
+  </si>
+  <si>
+    <t>AGM Abogados</t>
+  </si>
+  <si>
+    <t>Robles Miaja</t>
+  </si>
+  <si>
+    <t>Morales &amp; Besa</t>
+  </si>
+  <si>
+    <t>Mundie e Advogados</t>
+  </si>
+  <si>
+    <t>Nelligan Law</t>
+  </si>
+  <si>
+    <t>Mitrani Caballero &amp; Ruiz Moreno</t>
+  </si>
+  <si>
+    <t>Kanuka Thuringer</t>
+  </si>
+  <si>
+    <t>Farroco Abreu Guarnieri Zotelli</t>
+  </si>
+  <si>
+    <t>Curtis Dawe</t>
+  </si>
+  <si>
+    <t>VBD Advogados</t>
+  </si>
+  <si>
+    <t>BRZ</t>
+  </si>
+  <si>
+    <t>Brasil Salomao e Matthes</t>
+  </si>
+  <si>
+    <t>1min 35</t>
+  </si>
+  <si>
+    <t>Abe</t>
+  </si>
+  <si>
+    <t>Chevez Ruiz Zamarripa</t>
+  </si>
+  <si>
+    <t>RGRH</t>
+  </si>
+  <si>
+    <t>Mattos Engelberg Echenique</t>
+  </si>
+  <si>
+    <t>Zuzunaga &amp; Assereto</t>
+  </si>
+  <si>
+    <t>CTP Advogados</t>
+  </si>
+  <si>
+    <t>Siqueira Castro</t>
+  </si>
+  <si>
+    <t>Lavín Abogados &amp; Consultores</t>
+  </si>
+  <si>
+    <t>Burnet Duckworth &amp; Palmer</t>
+  </si>
+  <si>
+    <t>Madruga BTW</t>
+  </si>
+  <si>
+    <t>PHR Legal</t>
+  </si>
+  <si>
+    <t>MGGL</t>
+  </si>
+  <si>
+    <t>Ferrada Nehme</t>
+  </si>
+  <si>
+    <t>Andersen</t>
+  </si>
+  <si>
+    <t>Bocater</t>
+  </si>
+  <si>
+    <t>Prasad And Company</t>
+  </si>
+  <si>
+    <t>Barrios And Fuentes</t>
+  </si>
+  <si>
+    <t>Estudio Olaechea</t>
+  </si>
+  <si>
+    <t>Tauil And Chequer</t>
+  </si>
+  <si>
+    <t>Balmaceda, Cox &amp; Piña</t>
+  </si>
+  <si>
+    <t>Dillon Eustace</t>
+  </si>
+  <si>
+    <t>DunnCox</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Carey</t>
+  </si>
+  <si>
+    <t>2min 59</t>
+  </si>
+  <si>
+    <t>Alvarez Abogados</t>
+  </si>
+  <si>
+    <t>J. Armando Batista</t>
+  </si>
+  <si>
+    <t>CASSAGNE</t>
+  </si>
+  <si>
+    <t>Patterson</t>
+  </si>
+  <si>
+    <t>Boyne Clarke</t>
+  </si>
+  <si>
+    <t>BAQSN</t>
+  </si>
+  <si>
+    <t>Duarte Garcia, Serra Netto e Terra</t>
+  </si>
+  <si>
+    <t>Sacha Calmon</t>
+  </si>
+  <si>
+    <t>KVLAW</t>
+  </si>
+  <si>
+    <t>Beccar Varela</t>
+  </si>
+  <si>
+    <t>Fabrega Molino &amp; Mulino</t>
+  </si>
+  <si>
+    <t>HD Legal</t>
+  </si>
+  <si>
+    <t>Dale And Lessmann</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>De La Vega &amp; Martínez Rojas</t>
+  </si>
+  <si>
+    <t>Bustamante Fabara</t>
+  </si>
+  <si>
+    <t>IW Melcheds</t>
+  </si>
+  <si>
+    <t>Villarreal VGF</t>
+  </si>
+  <si>
+    <t>Prado Vidigal</t>
+  </si>
+  <si>
+    <t>Aninat</t>
+  </si>
+  <si>
+    <t>MQMGLD</t>
+  </si>
+  <si>
+    <t>Headrick Rizik Alvarez And Fernandez</t>
+  </si>
+  <si>
+    <t>Pitblado</t>
+  </si>
+  <si>
+    <t>Payet Rey Cauvi Pérez</t>
+  </si>
+  <si>
+    <t>Robortella e Peres</t>
+  </si>
+  <si>
+    <t>Alcogal</t>
+  </si>
+  <si>
+    <t>CEPD Abogados</t>
+  </si>
+  <si>
+    <t>Oyen Wiggs</t>
+  </si>
+  <si>
+    <t>Vouga</t>
+  </si>
+  <si>
+    <t>Langlois</t>
+  </si>
+  <si>
+    <t>Amprimo</t>
+  </si>
+  <si>
+    <t>Hernández And Cía</t>
+  </si>
+  <si>
+    <t>Wald Antunes Vita e Blattner</t>
+  </si>
+  <si>
+    <t>MUC</t>
+  </si>
+  <si>
+    <t>Alburquerque Abogados Consultores</t>
+  </si>
+  <si>
+    <t>FM Derraik</t>
+  </si>
+  <si>
+    <t>Galicia</t>
+  </si>
+  <si>
+    <t>Bichara e Motta</t>
+  </si>
+  <si>
+    <t>Ramos, Ripoll &amp; Schuster</t>
+  </si>
+  <si>
+    <t>NFA</t>
+  </si>
+  <si>
+    <t>Allende And Brea</t>
+  </si>
+  <si>
+    <t>McConnell Valdés</t>
+  </si>
+  <si>
+    <t>Puga Ortiz</t>
+  </si>
+  <si>
+    <t>Justen Pereira</t>
+  </si>
+  <si>
+    <t>2min 18</t>
+  </si>
+  <si>
+    <t>Santivanez</t>
+  </si>
+  <si>
+    <t>PPO Abogados</t>
+  </si>
+  <si>
+    <t>Alessandri Lawyers</t>
+  </si>
+  <si>
+    <t>Malpica, Iturbe, Buj &amp; Paredes</t>
+  </si>
+  <si>
+    <t>Cox &amp; Palmer</t>
+  </si>
+  <si>
+    <t>OMG</t>
+  </si>
+  <si>
+    <t>Chrupo Evans</t>
+  </si>
+  <si>
+    <t>Nunes Scholefield DeLeon &amp; Co</t>
+  </si>
+  <si>
+    <t>Olaechea</t>
+  </si>
+  <si>
+    <t>Bofill Mir</t>
+  </si>
+  <si>
+    <t>Cervantes Abogados</t>
+  </si>
+  <si>
+    <t>Lex Atlas</t>
+  </si>
+  <si>
+    <t>Ferrere</t>
+  </si>
+  <si>
+    <t>2min 27</t>
+  </si>
+  <si>
+    <t>McKinney Bancroft &amp; Hughes</t>
+  </si>
+  <si>
+    <t>Romeu Amaral Advogados</t>
+  </si>
+  <si>
+    <t>Osterling</t>
+  </si>
+  <si>
+    <t>O'Neill &amp; Borges</t>
+  </si>
+  <si>
+    <t>Aguayo Ecclefield And Martinez</t>
+  </si>
+  <si>
+    <t>Silva</t>
+  </si>
+  <si>
+    <t>1min 14</t>
+  </si>
+  <si>
+    <t>Peixoto &amp; Cury</t>
+  </si>
+  <si>
+    <t>Schneider Pugliese</t>
+  </si>
+  <si>
+    <t>Novotny Advogados</t>
+  </si>
+  <si>
+    <t>Coronel &amp; Pérez</t>
+  </si>
+  <si>
+    <t>Trench Rossi Watanabe</t>
+  </si>
+  <si>
+    <t>Ritch Mueller And Nicolau</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>O'Farrell</t>
+  </si>
+  <si>
+    <t>Damma</t>
+  </si>
+  <si>
+    <t>Urenda Rencoret Orrego y Dörr</t>
+  </si>
+  <si>
+    <t>Muniz Law</t>
+  </si>
+  <si>
+    <t>Molina Ríos</t>
+  </si>
+  <si>
+    <t>MLT Aikins</t>
+  </si>
+  <si>
+    <t>Creel</t>
+  </si>
+  <si>
+    <t>Filion Wakely Thorup Angeletti</t>
+  </si>
+  <si>
+    <t>Vieira Rezende Advogados</t>
+  </si>
+  <si>
+    <t>Barriston Law</t>
+  </si>
+  <si>
+    <t>CBLM</t>
+  </si>
+  <si>
+    <t>Farris</t>
+  </si>
+  <si>
+    <t>BSVV</t>
+  </si>
+  <si>
+    <t>Serrano Martinez CMA</t>
+  </si>
+  <si>
+    <t>LRI Law</t>
+  </si>
+  <si>
+    <t>Basch &amp; Rameh</t>
+  </si>
+  <si>
+    <t>MENPA</t>
+  </si>
+  <si>
+    <t>Bomchil</t>
+  </si>
+  <si>
+    <t>Clark Wilson</t>
+  </si>
+  <si>
+    <t>Fitzwilliam Stone Furness &amp; Smith &amp; Morgan</t>
+  </si>
+  <si>
+    <t>Lobo de Rizzo</t>
+  </si>
+  <si>
+    <t>1min 6</t>
+  </si>
+  <si>
+    <t>Thompson Dorfman Sweatman</t>
+  </si>
+  <si>
+    <t>Prieto</t>
+  </si>
+  <si>
+    <t>PG Law</t>
+  </si>
+  <si>
+    <t>Madrona</t>
+  </si>
+  <si>
+    <t>Esguerra JHR</t>
+  </si>
+  <si>
+    <t>Santos Bevilaqua Advogados</t>
+  </si>
+  <si>
+    <t>MPA Trade Law</t>
+  </si>
+  <si>
+    <t>Wildeboer Dellelce</t>
+  </si>
+  <si>
+    <t>Baptista Luz</t>
+  </si>
+  <si>
+    <t>VBSO Advogados</t>
+  </si>
+  <si>
+    <t>Barcellos Tucunduva</t>
+  </si>
+  <si>
+    <t>Ulises Cabrera</t>
+  </si>
+  <si>
+    <t>Fillmore Riley</t>
+  </si>
+  <si>
+    <t>Fischer &amp; Cia</t>
+  </si>
+  <si>
+    <t>Lavery</t>
+  </si>
+  <si>
+    <t>Labbe Abogados</t>
+  </si>
+  <si>
+    <t>Harris</t>
+  </si>
+  <si>
+    <t>Livingston Alexander &amp; Levy</t>
+  </si>
+  <si>
+    <t>LEFOSSE</t>
+  </si>
+  <si>
+    <t>2min 29</t>
+  </si>
+  <si>
+    <t>Osler Hoskin &amp; Harcourt</t>
+  </si>
+  <si>
+    <t>Cariola Diez Perez-Cotapos</t>
+  </si>
+  <si>
+    <t>PSTBN</t>
+  </si>
+  <si>
+    <t>Guzmán Ariza</t>
+  </si>
+  <si>
+    <t>Latin Alliance</t>
+  </si>
+  <si>
+    <t>1min 22</t>
+  </si>
+  <si>
+    <t>Gumucio &amp; Abogados</t>
+  </si>
+  <si>
+    <t>BLG Law</t>
+  </si>
+  <si>
+    <t>Guyer &amp; Regules</t>
+  </si>
+  <si>
+    <t>Lovill</t>
+  </si>
+  <si>
+    <t>Garcia Bodan</t>
+  </si>
+  <si>
+    <t>MHR Legal</t>
+  </si>
+  <si>
+    <t>PNM Adovagos</t>
+  </si>
+  <si>
+    <t>Hope Duggan &amp; Silva</t>
+  </si>
+  <si>
+    <t>Granadeiro Guimarães</t>
+  </si>
+  <si>
+    <t>1min 12</t>
+  </si>
+  <si>
+    <t>Smart &amp; Biggar</t>
+  </si>
+  <si>
+    <t>BCB</t>
+  </si>
+  <si>
+    <t>Lexincorp</t>
+  </si>
+  <si>
+    <t>Machado Associados</t>
+  </si>
+  <si>
+    <t>1min 0</t>
+  </si>
+  <si>
+    <t>Nauta Dutilh</t>
+  </si>
+  <si>
+    <t>Ried Fabres</t>
+  </si>
+  <si>
+    <t>Fogler Rubinoff</t>
+  </si>
+  <si>
+    <t>Travieso Evans Arria And Rengel</t>
+  </si>
+  <si>
+    <t>Claro &amp; Cía</t>
+  </si>
+  <si>
+    <t>Lembeye</t>
+  </si>
+  <si>
+    <t>Delco Law</t>
+  </si>
+  <si>
+    <t>HNA</t>
+  </si>
+  <si>
+    <t>Cassels</t>
+  </si>
+  <si>
+    <t>1min 58</t>
+  </si>
+  <si>
+    <t>Graham Thompson</t>
+  </si>
+  <si>
+    <t>Sangra Moller LLP</t>
+  </si>
+  <si>
+    <t>TAGD</t>
+  </si>
+  <si>
+    <t>Criales Urcullo</t>
+  </si>
+  <si>
+    <t>Ritch Mueller</t>
+  </si>
+  <si>
+    <t>Rodrigo, Elías &amp; Medrano Abogados</t>
+  </si>
+  <si>
+    <t>Patterson Mair Hamilton</t>
+  </si>
+  <si>
+    <t>Kuri Breña</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Jiménez Peña</t>
+  </si>
+  <si>
+    <t>Lacaz Martins, Pereira Neto, Gurevich &amp; Schoueri</t>
+  </si>
+  <si>
+    <t>Bragard</t>
+  </si>
+  <si>
+    <t>Chanis</t>
+  </si>
+  <si>
+    <t>J.D Sellier + Co</t>
+  </si>
+  <si>
+    <t>SIERRA Latam</t>
+  </si>
+  <si>
+    <t>Moreno Baldivieso</t>
+  </si>
+  <si>
+    <t>RMADV Advogados</t>
+  </si>
+  <si>
+    <t>Uhthoff</t>
+  </si>
+  <si>
+    <t>Chediak</t>
+  </si>
+  <si>
+    <t>Nelson Wilians &amp; Advogados</t>
+  </si>
+  <si>
+    <t>De Camps Vasquez Varela</t>
+  </si>
+  <si>
+    <t>McKercher</t>
+  </si>
+  <si>
+    <t>Asafo And Co</t>
+  </si>
+  <si>
+    <t>Palma Law</t>
+  </si>
+  <si>
+    <t>Baraona Marshall</t>
+  </si>
+  <si>
+    <t>Lexvalor Abogados</t>
+  </si>
+  <si>
+    <t>McDougall Gauley</t>
+  </si>
+  <si>
+    <t>Barros And Errazuriz</t>
+  </si>
+  <si>
+    <t>Benites, Vargas &amp; Ugaz</t>
+  </si>
+  <si>
+    <t>Sargent And Krahn</t>
+  </si>
+  <si>
+    <t>1min 20</t>
+  </si>
+  <si>
+    <t>Arthur Cox</t>
+  </si>
+  <si>
+    <t>Bennet Jones</t>
+  </si>
+  <si>
+    <t>Motta Fernandes</t>
+  </si>
+  <si>
+    <t>Di Blasi, Parente &amp; Associados</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>De Hoyos Aviles</t>
+  </si>
+  <si>
+    <t>EC Legal Rubio</t>
+  </si>
+  <si>
+    <t>Rennó Penteado Sampaio Advogados</t>
+  </si>
+  <si>
+    <t>Bermudes</t>
+  </si>
+  <si>
+    <t>Gaia Silva Gaede &amp; Associados</t>
+  </si>
+  <si>
+    <t>Bicalho Navarro</t>
+  </si>
+  <si>
+    <t>Abeledo Gottheil</t>
+  </si>
+  <si>
+    <t>Tavares</t>
+  </si>
+  <si>
+    <t>Wongtschowski Kleiman Advogados</t>
+  </si>
+  <si>
+    <t>MBM</t>
+  </si>
+  <si>
+    <t>Palacios Lleras</t>
+  </si>
+  <si>
+    <t>Montaury Pimenta, Machado And Vieira de Mello</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Chaitons</t>
+  </si>
+  <si>
+    <t>CPB</t>
+  </si>
+  <si>
+    <t>Loopstra Nixon</t>
+  </si>
+  <si>
+    <t>Nader Hayaux And Goebel</t>
+  </si>
+  <si>
+    <t>2min 43</t>
+  </si>
+  <si>
+    <t>Rubio</t>
+  </si>
+  <si>
+    <t>Medina Garnes Abogados</t>
+  </si>
+  <si>
+    <t>FLH</t>
+  </si>
+  <si>
+    <t>Albagli Zaliasnik</t>
+  </si>
+  <si>
+    <t>Fishman Flanz Meland Paquin</t>
+  </si>
+  <si>
+    <t>VILA Abogados</t>
+  </si>
+  <si>
+    <t>Noboa, Peña &amp; Torres</t>
+  </si>
+  <si>
+    <t>Balera, Berbel &amp; Mitne</t>
+  </si>
+  <si>
+    <t>MLL Legal</t>
+  </si>
+  <si>
+    <t>Lund Elmer Sandager</t>
+  </si>
+  <si>
+    <t>1min 5</t>
+  </si>
+  <si>
+    <t>Heuking Kühn Lüer Wojtek</t>
+  </si>
+  <si>
+    <t>Olaniwun Ajayi</t>
+  </si>
+  <si>
+    <t>Badri and Salim El Meouchi Law</t>
+  </si>
+  <si>
+    <t>1min 29</t>
+  </si>
+  <si>
+    <t>CCA</t>
+  </si>
+  <si>
+    <t>NOEWE</t>
+  </si>
+  <si>
+    <t>Lener</t>
+  </si>
+  <si>
+    <t>Macedo Vitorino</t>
+  </si>
+  <si>
+    <t>SPA Ajibade &amp; Co</t>
+  </si>
+  <si>
+    <t>Adsero</t>
+  </si>
+  <si>
+    <t>SIRIUS</t>
+  </si>
+  <si>
+    <t>Naschitz Brandes Amir</t>
+  </si>
+  <si>
+    <t>Gorrissen Federspiel</t>
+  </si>
+  <si>
+    <t>Simont Braun</t>
+  </si>
+  <si>
+    <t>Maples</t>
+  </si>
+  <si>
+    <t>Dinova Rusev &amp; Partners</t>
+  </si>
+  <si>
+    <t>Bureau Plattner</t>
+  </si>
+  <si>
+    <t>ADVANT Beiten</t>
+  </si>
+  <si>
+    <t>AVS Legal</t>
+  </si>
+  <si>
+    <t>Melling Voitishkin And Partners</t>
+  </si>
+  <si>
+    <t>Philip Lee</t>
+  </si>
+  <si>
+    <t>Grimaldi Alliance</t>
+  </si>
+  <si>
+    <t>BRAUNEIS RECHTSANWÄLTE</t>
+  </si>
+  <si>
+    <t>Wikborg Rein</t>
+  </si>
+  <si>
+    <t>Souriadakis Tsibris</t>
+  </si>
+  <si>
+    <t>FCM Limited</t>
+  </si>
+  <si>
+    <t>Lindahl</t>
+  </si>
+  <si>
+    <t>SGP Schneider Geiwitz &amp; Partner</t>
+  </si>
+  <si>
+    <t>Contrast</t>
+  </si>
+  <si>
+    <t>2min 32</t>
+  </si>
+  <si>
+    <t>HCR Legal</t>
+  </si>
+  <si>
+    <t>Fidal</t>
+  </si>
+  <si>
+    <t>Bancila Diaconu si Asociatii</t>
+  </si>
+  <si>
+    <t>Abreu Advogados</t>
+  </si>
+  <si>
+    <t>Sokol, Novák, Trojan, Doleček</t>
+  </si>
+  <si>
+    <t>CBA</t>
+  </si>
+  <si>
+    <t>ALP NG &amp; Co</t>
+  </si>
+  <si>
+    <t>Franklin Law</t>
   </si>
 </sst>
 </file>
@@ -1663,13 +2692,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C139"/>
+  <dimension ref="A1:C321"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="27.6634615384615" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3461538461538" style="1" customWidth="1"/>
-    <col min="3" max="3" width="51.1442307692308" style="1" customWidth="1"/>
-    <col min="4" max="8" width="8.88461538461539" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="27.6634615384615"/>
+    <col min="2" max="2" customWidth="true" style="1" width="33.3461538461538"/>
+    <col min="3" max="3" customWidth="true" style="1" width="51.1442307692308"/>
+    <col min="4" max="8" customWidth="true" width="8.88461538461539"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.2" spans="1:3">
@@ -1683,1522 +2712,3524 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2">
+      <c r="A2" t="s" s="1">
+        <v>428</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="3">
+      <c r="A3" t="s" s="1">
+        <v>518</v>
+      </c>
+      <c r="B3" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="4">
+      <c r="A4" t="s" s="1">
+        <v>527</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="5">
+      <c r="A5" t="s" s="1">
+        <v>537</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="6">
+      <c r="A6" t="s" s="1">
+        <v>544</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
+    <row r="7">
+      <c r="A7" t="s" s="1">
+        <v>308</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C7" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
+    <row r="8">
+      <c r="A8" t="s" s="1">
+        <v>549</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>550</v>
+      </c>
+      <c r="C8" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
+    <row r="9">
+      <c r="A9" t="s" s="1">
+        <v>423</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>424</v>
+      </c>
+      <c r="C9" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
+    <row r="10">
+      <c r="A10" t="s" s="1">
+        <v>283</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>284</v>
+      </c>
+      <c r="C10" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1" t="s">
+    <row r="11">
+      <c r="A11" t="s" s="1">
+        <v>244</v>
+      </c>
+      <c r="B11" t="s" s="1">
+        <v>245</v>
+      </c>
+      <c r="C11" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="1" t="s">
+    <row r="12">
+      <c r="A12" t="s" s="1">
+        <v>523</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>524</v>
+      </c>
+      <c r="C12" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="1" t="s">
+    <row r="13">
+      <c r="A13" t="s" s="1">
+        <v>429</v>
+      </c>
+      <c r="B13" t="s" s="1">
+        <v>430</v>
+      </c>
+      <c r="C13" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="1" t="s">
+    <row r="14">
+      <c r="A14" t="s" s="1">
+        <v>485</v>
+      </c>
+      <c r="B14" t="s" s="1">
+        <v>486</v>
+      </c>
+      <c r="C14" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="1" t="s">
+    <row r="15">
+      <c r="A15" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="B15" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C15" t="s" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
+    <row r="16">
+      <c r="A16" t="s" s="1">
+        <v>374</v>
+      </c>
+      <c r="B16" t="s" s="1">
+        <v>375</v>
+      </c>
+      <c r="C16" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1">
+        <v>485</v>
+      </c>
+      <c r="B17" t="s" s="1">
+        <v>440</v>
+      </c>
+      <c r="C17" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="1">
+        <v>501</v>
+      </c>
+      <c r="B18" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="1">
+        <v>338</v>
+      </c>
+      <c r="B19" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1">
+        <v>381</v>
+      </c>
+      <c r="B20" t="s" s="1">
+        <v>382</v>
+      </c>
+      <c r="C20" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="1">
+        <v>333</v>
+      </c>
+      <c r="B21" t="s" s="1">
+        <v>464</v>
+      </c>
+      <c r="C21" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>273</v>
+      </c>
+      <c r="B22" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="C22" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>460</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>475</v>
+      </c>
+      <c r="B24" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="C24" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="1">
+        <v>405</v>
+      </c>
+      <c r="B25" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="C25" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1">
+        <v>465</v>
+      </c>
+      <c r="B26" t="s" s="1">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="B27" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1">
+        <v>535</v>
+      </c>
+      <c r="B28" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C28" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>539</v>
+      </c>
+      <c r="B29" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
+        <v>435</v>
+      </c>
+      <c r="B30" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C30" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>556</v>
+      </c>
+      <c r="B31" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C31" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1">
+        <v>257</v>
+      </c>
+      <c r="B32" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C32" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1">
+        <v>250</v>
+      </c>
+      <c r="B33" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C33" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="B34" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C34" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1">
+        <v>350</v>
+      </c>
+      <c r="B35" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C35" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1">
+        <v>305</v>
+      </c>
+      <c r="B36" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C36" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="1">
+        <v>392</v>
+      </c>
+      <c r="B37" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C37" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1">
+        <v>335</v>
+      </c>
+      <c r="B38" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1">
+        <v>395</v>
+      </c>
+      <c r="B39" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>513</v>
+      </c>
+      <c r="B40" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C40" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1">
+        <v>349</v>
+      </c>
+      <c r="B41" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C41" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>449</v>
+      </c>
+      <c r="B42" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="1">
+        <v>540</v>
+      </c>
+      <c r="B43" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C43" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="1">
+        <v>399</v>
+      </c>
+      <c r="B44" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C44" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1">
+        <v>336</v>
+      </c>
+      <c r="B45" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C45" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>263</v>
+      </c>
+      <c r="B46" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C46" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1">
+        <v>301</v>
+      </c>
+      <c r="B47" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C47" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
+        <v>331</v>
+      </c>
+      <c r="B48" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C48" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>496</v>
+      </c>
+      <c r="B49" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C49" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
+        <v>487</v>
+      </c>
+      <c r="B50" t="s" s="1">
         <v>24</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="C50" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="1">
+        <v>508</v>
+      </c>
+      <c r="B51" t="s" s="1">
+        <v>509</v>
+      </c>
+      <c r="C51" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="1">
+        <v>367</v>
+      </c>
+      <c r="B52" t="s" s="1">
+        <v>368</v>
+      </c>
+      <c r="C52" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="1">
+        <v>353</v>
+      </c>
+      <c r="B53" t="s" s="1">
+        <v>354</v>
+      </c>
+      <c r="C53" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="1">
+        <v>454</v>
+      </c>
+      <c r="B54" t="s" s="1">
+        <v>455</v>
+      </c>
+      <c r="C54" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="1">
+        <v>542</v>
+      </c>
+      <c r="B55" t="s" s="1">
+        <v>245</v>
+      </c>
+      <c r="C55" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="1">
+        <v>426</v>
+      </c>
+      <c r="B56" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="C56" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="1">
+        <v>433</v>
+      </c>
+      <c r="B57" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C57" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="1">
+        <v>240</v>
+      </c>
+      <c r="B58" t="s" s="1">
+        <v>241</v>
+      </c>
+      <c r="C58" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="1">
+        <v>500</v>
+      </c>
+      <c r="B59" t="s" s="1">
+        <v>241</v>
+      </c>
+      <c r="C59" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="1">
+        <v>502</v>
+      </c>
+      <c r="B60" t="s" s="1">
+        <v>375</v>
+      </c>
+      <c r="C60" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="1">
+        <v>439</v>
+      </c>
+      <c r="B61" t="s" s="1">
+        <v>440</v>
+      </c>
+      <c r="C61" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1">
+        <v>218</v>
+      </c>
+      <c r="B62" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" s="1" t="s">
+      <c r="C62" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="B63" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B43" s="1" t="s">
+      <c r="C63" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="1">
+        <v>547</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>70</v>
+      </c>
+      <c r="C64" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1">
+        <v>403</v>
+      </c>
+      <c r="B65" t="s" s="1">
+        <v>404</v>
+      </c>
+      <c r="C65" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="1">
+        <v>519</v>
+      </c>
+      <c r="B66" t="s" s="1">
+        <v>520</v>
+      </c>
+      <c r="C66" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="1">
+        <v>533</v>
+      </c>
+      <c r="B67" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B46" s="1" t="s">
+      <c r="C67" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="1">
+        <v>444</v>
+      </c>
+      <c r="B68" t="s" s="1">
+        <v>445</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="1">
+        <v>505</v>
+      </c>
+      <c r="B69" t="s" s="1">
+        <v>445</v>
+      </c>
+      <c r="C69" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="B70" t="s" s="1">
         <v>78</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B47" s="1" t="s">
+      <c r="C70" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="1">
+        <v>490</v>
+      </c>
+      <c r="B71" t="s" s="1">
+        <v>491</v>
+      </c>
+      <c r="C71" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="B72" t="s" s="1">
         <v>80</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="C72" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="1">
+        <v>503</v>
+      </c>
+      <c r="B73" t="s" s="1">
+        <v>504</v>
+      </c>
+      <c r="C73" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="1">
+        <v>317</v>
+      </c>
+      <c r="B74" t="s" s="1">
         <v>84</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="C74" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="1">
+        <v>522</v>
+      </c>
+      <c r="B75" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="C75" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="1">
+        <v>229</v>
+      </c>
+      <c r="B76" t="s" s="1">
         <v>86</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B51" s="1" t="s">
+      <c r="C76" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="1">
+        <v>408</v>
+      </c>
+      <c r="B77" t="s" s="1">
         <v>88</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="C77" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="1">
+        <v>427</v>
+      </c>
+      <c r="B78" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="C78" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="1">
+        <v>529</v>
+      </c>
+      <c r="B79" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="C79" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="1">
+        <v>438</v>
+      </c>
+      <c r="B80" t="s" s="1">
         <v>90</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B54" s="1" t="s">
+      <c r="C80" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="1">
+        <v>463</v>
+      </c>
+      <c r="B81" t="s" s="1">
+        <v>464</v>
+      </c>
+      <c r="C81" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="1">
+        <v>255</v>
+      </c>
+      <c r="B82" t="s" s="1">
+        <v>256</v>
+      </c>
+      <c r="C82" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
+        <v>295</v>
+      </c>
+      <c r="B83" t="s" s="1">
         <v>94</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B55" s="1" t="s">
+      <c r="C83" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="1">
+        <v>492</v>
+      </c>
+      <c r="B84" t="s" s="1">
         <v>94</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="C84" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="1">
+        <v>528</v>
+      </c>
+      <c r="B85" t="s" s="1">
         <v>94</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="C85" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="1">
+        <v>499</v>
+      </c>
+      <c r="B86" t="s" s="1">
         <v>98</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B59" s="1" t="s">
+      <c r="C86" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="1">
+        <v>322</v>
+      </c>
+      <c r="B87" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C87" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1">
+        <v>507</v>
+      </c>
+      <c r="B88" t="s" s="1">
         <v>101</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B60" s="1" t="s">
+      <c r="C88" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="B89" t="s" s="1">
         <v>103</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B61" s="1" t="s">
+      <c r="C89" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="1">
+        <v>417</v>
+      </c>
+      <c r="B90" t="s" s="1">
         <v>103</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B62" s="1" t="s">
+      <c r="C90" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="1">
+        <v>532</v>
+      </c>
+      <c r="B91" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="C91" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="1">
+        <v>315</v>
+      </c>
+      <c r="B92" t="s" s="1">
         <v>106</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B64" s="1" t="s">
+      <c r="C92" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="1">
+        <v>468</v>
+      </c>
+      <c r="B93" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="C93" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="1">
+        <v>419</v>
+      </c>
+      <c r="B94" t="s" s="1">
         <v>110</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B65" s="1" t="s">
+      <c r="C94" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="1">
+        <v>480</v>
+      </c>
+      <c r="B95" t="s" s="1">
         <v>110</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B66" s="1" t="s">
+      <c r="C95" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="1">
+        <v>555</v>
+      </c>
+      <c r="B96" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="C96" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="1">
+        <v>416</v>
+      </c>
+      <c r="B97" t="s" s="1">
         <v>113</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B69" s="1" t="s">
+      <c r="C97" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="1">
+        <v>264</v>
+      </c>
+      <c r="B98" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C98" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="1">
+        <v>268</v>
+      </c>
+      <c r="B99" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C99" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="1">
+        <v>436</v>
+      </c>
+      <c r="B100" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C100" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="1">
+        <v>553</v>
+      </c>
+      <c r="B101" t="s" s="1">
         <v>118</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B70" s="1" t="s">
+      <c r="C101" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="B102" t="s" s="1">
         <v>120</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B71" s="1" t="s">
+      <c r="C102" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="1">
+        <v>446</v>
+      </c>
+      <c r="B103" t="s" s="1">
         <v>120</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B72" s="1" t="s">
+      <c r="C103" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="1">
+        <v>289</v>
+      </c>
+      <c r="B104" t="s" s="1">
         <v>123</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B73" s="1" t="s">
+      <c r="C104" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="1">
+        <v>385</v>
+      </c>
+      <c r="B105" t="s" s="1">
         <v>123</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B74" s="1" t="s">
+      <c r="C105" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="B106" t="s" s="1">
         <v>126</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="C106" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="1">
+        <v>493</v>
+      </c>
+      <c r="B107" t="s" s="1">
         <v>126</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B76" s="1" t="s">
+      <c r="C107" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="1">
+        <v>506</v>
+      </c>
+      <c r="B108" t="s" s="1">
         <v>126</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B77" s="1" t="s">
+      <c r="C108" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="1">
+        <v>536</v>
+      </c>
+      <c r="B109" t="s" s="1">
         <v>130</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B80" s="1" t="s">
+      <c r="C109" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="1">
+        <v>482</v>
+      </c>
+      <c r="B110" t="s" s="1">
         <v>134</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B81" s="1" t="s">
+      <c r="C110" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="1">
+        <v>526</v>
+      </c>
+      <c r="B111" t="s" s="1">
         <v>134</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B83" s="1" t="s">
+      <c r="C111" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="1">
+        <v>319</v>
+      </c>
+      <c r="B112" t="s" s="1">
         <v>138</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B84" s="1" t="s">
+      <c r="C112" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="1">
+        <v>418</v>
+      </c>
+      <c r="B113" t="s" s="1">
         <v>138</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B85" s="1" t="s">
+      <c r="C113" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="1">
+        <v>425</v>
+      </c>
+      <c r="B114" t="s" s="1">
         <v>138</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B86" s="1" t="s">
+      <c r="C114" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="1">
+        <v>481</v>
+      </c>
+      <c r="B115" t="s" s="1">
         <v>138</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B87" s="1" t="s">
+      <c r="C115" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="1">
+        <v>511</v>
+      </c>
+      <c r="B116" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C116" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="1">
+        <v>344</v>
+      </c>
+      <c r="B117" t="s" s="1">
         <v>143</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B88" s="1" t="s">
+      <c r="C117" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="1">
+        <v>422</v>
+      </c>
+      <c r="B118" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C118" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="1">
+        <v>557</v>
+      </c>
+      <c r="B119" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C119" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="1">
+        <v>558</v>
+      </c>
+      <c r="B120" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C120" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="B121" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C121" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="1">
+        <v>287</v>
+      </c>
+      <c r="B122" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C122" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="1">
+        <v>346</v>
+      </c>
+      <c r="B123" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C123" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="1">
+        <v>543</v>
+      </c>
+      <c r="B124" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C124" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="1">
+        <v>546</v>
+      </c>
+      <c r="B125" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C125" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="1">
+        <v>373</v>
+      </c>
+      <c r="B126" t="s" s="1">
         <v>145</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B89" s="1" t="s">
+      <c r="C126" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="1">
+        <v>432</v>
+      </c>
+      <c r="B127" t="s" s="1">
         <v>145</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B90" s="1" t="s">
+      <c r="C127" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="1">
+        <v>239</v>
+      </c>
+      <c r="B128" t="s" s="1">
         <v>148</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B91" s="1" t="s">
+      <c r="C128" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="1">
+        <v>325</v>
+      </c>
+      <c r="B129" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C129" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="1">
+        <v>340</v>
+      </c>
+      <c r="B130" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C130" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="1">
+        <v>351</v>
+      </c>
+      <c r="B131" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C131" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="1">
+        <v>369</v>
+      </c>
+      <c r="B132" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C132" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="1">
+        <v>409</v>
+      </c>
+      <c r="B133" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C133" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="1">
+        <v>477</v>
+      </c>
+      <c r="B134" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C134" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="1">
+        <v>222</v>
+      </c>
+      <c r="B135" t="s" s="1">
         <v>150</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B92" s="1" t="s">
+      <c r="C135" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="1">
+        <v>275</v>
+      </c>
+      <c r="B136" t="s" s="1">
         <v>150</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B93" s="1" t="s">
+      <c r="C136" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="1">
+        <v>277</v>
+      </c>
+      <c r="B137" t="s" s="1">
         <v>150</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B94" s="1" t="s">
+      <c r="C137" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="B138" t="s" s="1">
         <v>150</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B95" s="1" t="s">
+      <c r="C138" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="1">
+        <v>332</v>
+      </c>
+      <c r="B139" t="s" s="1">
         <v>150</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B96" s="1" t="s">
+      <c r="C139" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="1">
+        <v>400</v>
+      </c>
+      <c r="B140" t="s" s="1">
         <v>150</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B97" s="1" t="s">
+      <c r="C140" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="1">
+        <v>409</v>
+      </c>
+      <c r="B141" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C141" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="1">
+        <v>441</v>
+      </c>
+      <c r="B142" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C142" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="1">
+        <v>450</v>
+      </c>
+      <c r="B143" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C143" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="1">
+        <v>497</v>
+      </c>
+      <c r="B144" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C144" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="1">
+        <v>516</v>
+      </c>
+      <c r="B145" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C145" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="B146" t="s" s="1">
         <v>156</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B98" s="1" t="s">
+      <c r="C146" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="1">
+        <v>313</v>
+      </c>
+      <c r="B147" t="s" s="1">
         <v>156</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B99" s="1" t="s">
+      <c r="C147" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="1">
+        <v>442</v>
+      </c>
+      <c r="B148" t="s" s="1">
         <v>156</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B100" s="1" t="s">
+      <c r="C148" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="1">
+        <v>453</v>
+      </c>
+      <c r="B149" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C149" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="1">
+        <v>554</v>
+      </c>
+      <c r="B150" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C150" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="1">
+        <v>227</v>
+      </c>
+      <c r="B151" t="s" s="1">
         <v>160</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B101" s="1" t="s">
+      <c r="C151" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="1">
+        <v>352</v>
+      </c>
+      <c r="B152" t="s" s="1">
         <v>160</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B103" s="1" t="s">
+      <c r="C152" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="B153" t="s" s="1">
         <v>164</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B104" s="1" t="s">
+      <c r="C153" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="1">
+        <v>278</v>
+      </c>
+      <c r="B154" t="s" s="1">
         <v>164</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B105" s="1" t="s">
+      <c r="C154" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="1">
+        <v>290</v>
+      </c>
+      <c r="B155" t="s" s="1">
         <v>164</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B106" s="1" t="s">
+      <c r="C155" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="1">
+        <v>321</v>
+      </c>
+      <c r="B156" t="s" s="1">
         <v>164</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B107" s="1" t="s">
+      <c r="C156" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="1">
+        <v>355</v>
+      </c>
+      <c r="B157" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C157" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="1">
+        <v>362</v>
+      </c>
+      <c r="B158" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C158" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="1">
+        <v>452</v>
+      </c>
+      <c r="B159" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C159" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="1">
+        <v>238</v>
+      </c>
+      <c r="B160" t="s" s="1">
         <v>169</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B108" s="1" t="s">
+      <c r="C160" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="1">
+        <v>302</v>
+      </c>
+      <c r="B161" t="s" s="1">
         <v>169</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B109" s="1" t="s">
+      <c r="C161" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="1">
+        <v>334</v>
+      </c>
+      <c r="B162" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C162" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="1">
+        <v>348</v>
+      </c>
+      <c r="B163" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C163" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="1">
+        <v>365</v>
+      </c>
+      <c r="B164" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C164" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="1">
+        <v>371</v>
+      </c>
+      <c r="B165" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C165" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="1">
+        <v>431</v>
+      </c>
+      <c r="B166" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C166" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="1">
+        <v>489</v>
+      </c>
+      <c r="B167" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C167" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="1">
+        <v>495</v>
+      </c>
+      <c r="B168" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C168" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="B169" t="s" s="1">
         <v>172</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B110" s="1" t="s">
+      <c r="C169" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="1">
+        <v>242</v>
+      </c>
+      <c r="B170" t="s" s="1">
         <v>172</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B111" s="1" t="s">
+      <c r="C170" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="B171" t="s" s="1">
         <v>172</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B112" s="1" t="s">
+      <c r="C171" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="1">
+        <v>521</v>
+      </c>
+      <c r="B172" t="s" s="1">
         <v>172</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B114" s="1" t="s">
+      <c r="C172" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="1">
+        <v>274</v>
+      </c>
+      <c r="B173" t="s" s="1">
         <v>178</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B115" s="1" t="s">
+      <c r="C173" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="1">
+        <v>339</v>
+      </c>
+      <c r="B174" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C174" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="1">
+        <v>356</v>
+      </c>
+      <c r="B175" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C175" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="1">
+        <v>357</v>
+      </c>
+      <c r="B176" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C176" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="1">
+        <v>358</v>
+      </c>
+      <c r="B177" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C177" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="1">
+        <v>461</v>
+      </c>
+      <c r="B178" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C178" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="1">
+        <v>484</v>
+      </c>
+      <c r="B179" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C179" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="1">
+        <v>531</v>
+      </c>
+      <c r="B180" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C180" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="B181" t="s" s="1">
         <v>180</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B116" s="1" t="s">
+      <c r="C181" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="1">
+        <v>262</v>
+      </c>
+      <c r="B182" t="s" s="1">
         <v>180</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B117" s="1" t="s">
+      <c r="C182" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="B183" t="s" s="1">
         <v>180</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B118" s="1" t="s">
+      <c r="C183" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="1">
+        <v>366</v>
+      </c>
+      <c r="B184" t="s" s="1">
         <v>180</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B119" s="1" t="s">
+      <c r="C184" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="1">
+        <v>383</v>
+      </c>
+      <c r="B185" t="s" s="1">
         <v>180</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B120" s="1" t="s">
+      <c r="C185" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="1">
+        <v>386</v>
+      </c>
+      <c r="B186" t="s" s="1">
         <v>180</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B121" s="1" t="s">
+      <c r="C186" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="1">
+        <v>421</v>
+      </c>
+      <c r="B187" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C187" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="1">
+        <v>471</v>
+      </c>
+      <c r="B188" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C188" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="1">
+        <v>225</v>
+      </c>
+      <c r="B189" t="s" s="1">
         <v>187</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B122" s="1" t="s">
+      <c r="C189" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="1">
+        <v>232</v>
+      </c>
+      <c r="B190" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C190" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="1">
+        <v>260</v>
+      </c>
+      <c r="B191" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C191" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="1">
+        <v>271</v>
+      </c>
+      <c r="B192" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C192" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="1">
+        <v>291</v>
+      </c>
+      <c r="B193" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C193" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="1">
+        <v>292</v>
+      </c>
+      <c r="B194" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C194" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="1">
+        <v>298</v>
+      </c>
+      <c r="B195" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C195" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="1">
+        <v>343</v>
+      </c>
+      <c r="B196" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C196" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="1">
+        <v>347</v>
+      </c>
+      <c r="B197" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C197" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="1">
+        <v>390</v>
+      </c>
+      <c r="B198" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C198" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="1">
+        <v>406</v>
+      </c>
+      <c r="B199" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C199" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="1">
+        <v>517</v>
+      </c>
+      <c r="B200" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C200" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="1">
+        <v>306</v>
+      </c>
+      <c r="B201" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C201" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="1">
+        <v>372</v>
+      </c>
+      <c r="B202" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C202" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="1">
+        <v>388</v>
+      </c>
+      <c r="B203" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C203" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="1">
+        <v>389</v>
+      </c>
+      <c r="B204" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C204" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="1">
+        <v>434</v>
+      </c>
+      <c r="B205" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C205" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="1">
+        <v>447</v>
+      </c>
+      <c r="B206" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C206" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="1">
+        <v>459</v>
+      </c>
+      <c r="B207" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C207" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="1">
+        <v>476</v>
+      </c>
+      <c r="B208" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C208" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="1">
+        <v>221</v>
+      </c>
+      <c r="B209" t="s" s="1">
         <v>189</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B123" s="1" t="s">
+      <c r="C209" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="1">
+        <v>251</v>
+      </c>
+      <c r="B210" t="s" s="1">
         <v>189</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B124" s="1" t="s">
+      <c r="C210" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="1">
+        <v>279</v>
+      </c>
+      <c r="B211" t="s" s="1">
         <v>189</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B125" s="1" t="s">
+      <c r="C211" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="1">
+        <v>281</v>
+      </c>
+      <c r="B212" t="s" s="1">
         <v>189</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B126" s="1" t="s">
+      <c r="C212" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="1">
+        <v>296</v>
+      </c>
+      <c r="B213" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C213" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="1">
+        <v>371</v>
+      </c>
+      <c r="B214" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C214" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="1">
+        <v>451</v>
+      </c>
+      <c r="B215" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C215" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="1">
+        <v>456</v>
+      </c>
+      <c r="B216" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C216" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="1">
+        <v>470</v>
+      </c>
+      <c r="B217" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C217" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="1">
+        <v>530</v>
+      </c>
+      <c r="B218" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C218" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="1">
+        <v>228</v>
+      </c>
+      <c r="B219" t="s" s="1">
         <v>194</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B127" s="1" t="s">
+      <c r="C219" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="B220" t="s" s="1">
         <v>194</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B128" s="1" t="s">
+      <c r="C220" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="1">
+        <v>294</v>
+      </c>
+      <c r="B221" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C221" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="1">
+        <v>299</v>
+      </c>
+      <c r="B222" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C222" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="1">
+        <v>304</v>
+      </c>
+      <c r="B223" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C223" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="1">
+        <v>320</v>
+      </c>
+      <c r="B224" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C224" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="1">
+        <v>334</v>
+      </c>
+      <c r="B225" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C225" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="1">
+        <v>384</v>
+      </c>
+      <c r="B226" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C226" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="1">
+        <v>458</v>
+      </c>
+      <c r="B227" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C227" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="1">
+        <v>462</v>
+      </c>
+      <c r="B228" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C228" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="1">
+        <v>479</v>
+      </c>
+      <c r="B229" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C229" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="1">
+        <v>510</v>
+      </c>
+      <c r="B230" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C230" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="1">
+        <v>551</v>
+      </c>
+      <c r="B231" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C231" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="1">
+        <v>552</v>
+      </c>
+      <c r="B232" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C232" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="1">
+        <v>223</v>
+      </c>
+      <c r="B233" t="s" s="1">
         <v>197</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B129" s="1" t="s">
+      <c r="C233" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="1">
+        <v>234</v>
+      </c>
+      <c r="B234" t="s" s="1">
         <v>197</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B130" s="1" t="s">
+      <c r="C234" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="1">
+        <v>266</v>
+      </c>
+      <c r="B235" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C235" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="1">
+        <v>378</v>
+      </c>
+      <c r="B236" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C236" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="1">
+        <v>387</v>
+      </c>
+      <c r="B237" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C237" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="1">
+        <v>398</v>
+      </c>
+      <c r="B238" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C238" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="1">
+        <v>401</v>
+      </c>
+      <c r="B239" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C239" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="1">
+        <v>402</v>
+      </c>
+      <c r="B240" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C240" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="1">
+        <v>457</v>
+      </c>
+      <c r="B241" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C241" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="1">
+        <v>488</v>
+      </c>
+      <c r="B242" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C242" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="1">
+        <v>514</v>
+      </c>
+      <c r="B243" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C243" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="1">
+        <v>541</v>
+      </c>
+      <c r="B244" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C244" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="1">
+        <v>224</v>
+      </c>
+      <c r="B245" t="s" s="1">
         <v>200</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B131" s="1" t="s">
+      <c r="C245" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="1">
+        <v>282</v>
+      </c>
+      <c r="B246" t="s" s="1">
         <v>200</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B132" s="1" t="s">
+      <c r="C246" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="1">
+        <v>288</v>
+      </c>
+      <c r="B247" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C247" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="1">
+        <v>318</v>
+      </c>
+      <c r="B248" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C248" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="1">
+        <v>327</v>
+      </c>
+      <c r="B249" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C249" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="1">
+        <v>328</v>
+      </c>
+      <c r="B250" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C250" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="1">
+        <v>341</v>
+      </c>
+      <c r="B251" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C251" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="1">
+        <v>360</v>
+      </c>
+      <c r="B252" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C252" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="1">
+        <v>414</v>
+      </c>
+      <c r="B253" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C253" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="1">
+        <v>448</v>
+      </c>
+      <c r="B254" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C254" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="1">
+        <v>526</v>
+      </c>
+      <c r="B255" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C255" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="1">
+        <v>534</v>
+      </c>
+      <c r="B256" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C256" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="1">
+        <v>216</v>
+      </c>
+      <c r="B257" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C257" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="1">
+        <v>243</v>
+      </c>
+      <c r="B258" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C258" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="1">
+        <v>285</v>
+      </c>
+      <c r="B259" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C259" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="1">
+        <v>286</v>
+      </c>
+      <c r="B260" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C260" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="1">
+        <v>296</v>
+      </c>
+      <c r="B261" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C261" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="1">
+        <v>300</v>
+      </c>
+      <c r="B262" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C262" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="1">
+        <v>303</v>
+      </c>
+      <c r="B263" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C263" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="1">
+        <v>342</v>
+      </c>
+      <c r="B264" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C264" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="1">
+        <v>345</v>
+      </c>
+      <c r="B265" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C265" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="1">
+        <v>393</v>
+      </c>
+      <c r="B266" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C266" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="1">
+        <v>396</v>
+      </c>
+      <c r="B267" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C267" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="1">
+        <v>407</v>
+      </c>
+      <c r="B268" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C268" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="1">
+        <v>437</v>
+      </c>
+      <c r="B269" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C269" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="1">
+        <v>469</v>
+      </c>
+      <c r="B270" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C270" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="1">
+        <v>515</v>
+      </c>
+      <c r="B271" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C271" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="1">
+        <v>548</v>
+      </c>
+      <c r="B272" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C272" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="1">
+        <v>261</v>
+      </c>
+      <c r="B273" t="s" s="1">
         <v>203</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B133" s="1" t="s">
+      <c r="C273" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="1">
+        <v>310</v>
+      </c>
+      <c r="B274" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C274" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="1">
+        <v>337</v>
+      </c>
+      <c r="B275" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C275" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="1">
+        <v>359</v>
+      </c>
+      <c r="B276" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C276" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="1">
+        <v>361</v>
+      </c>
+      <c r="B277" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C277" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="1">
+        <v>370</v>
+      </c>
+      <c r="B278" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C278" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="1">
+        <v>472</v>
+      </c>
+      <c r="B279" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C279" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="1">
+        <v>220</v>
+      </c>
+      <c r="B280" t="s" s="1">
         <v>205</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B134" s="1" t="s">
+      <c r="C280" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="1">
+        <v>236</v>
+      </c>
+      <c r="B281" t="s" s="1">
         <v>205</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B135" s="1" t="s">
+      <c r="C281" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="1">
+        <v>326</v>
+      </c>
+      <c r="B282" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C282" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="1">
+        <v>333</v>
+      </c>
+      <c r="B283" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C283" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="1">
+        <v>376</v>
+      </c>
+      <c r="B284" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C284" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="1">
+        <v>380</v>
+      </c>
+      <c r="B285" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C285" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="1">
+        <v>413</v>
+      </c>
+      <c r="B286" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C286" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="1">
+        <v>448</v>
+      </c>
+      <c r="B287" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C287" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="1">
+        <v>466</v>
+      </c>
+      <c r="B288" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C288" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="1">
+        <v>467</v>
+      </c>
+      <c r="B289" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C289" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="1">
+        <v>474</v>
+      </c>
+      <c r="B290" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C290" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="1">
+        <v>545</v>
+      </c>
+      <c r="B291" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C291" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="1">
+        <v>270</v>
+      </c>
+      <c r="B292" t="s" s="1">
         <v>208</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B136" s="1" t="s">
+      <c r="C292" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="1">
+        <v>297</v>
+      </c>
+      <c r="B293" t="s" s="1">
         <v>208</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B137" s="1" t="s">
+      <c r="C293" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="B294" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C294" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="1">
+        <v>324</v>
+      </c>
+      <c r="B295" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C295" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="1">
+        <v>379</v>
+      </c>
+      <c r="B296" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C296" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="1">
+        <v>391</v>
+      </c>
+      <c r="B297" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C297" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="1">
+        <v>394</v>
+      </c>
+      <c r="B298" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C298" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="1">
+        <v>410</v>
+      </c>
+      <c r="B299" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C299" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="1">
+        <v>411</v>
+      </c>
+      <c r="B300" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C300" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="1">
+        <v>412</v>
+      </c>
+      <c r="B301" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C301" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="1">
+        <v>420</v>
+      </c>
+      <c r="B302" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C302" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="1">
+        <v>483</v>
+      </c>
+      <c r="B303" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C303" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="1">
+        <v>494</v>
+      </c>
+      <c r="B304" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C304" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="1">
+        <v>512</v>
+      </c>
+      <c r="B305" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C305" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="1">
+        <v>525</v>
+      </c>
+      <c r="B306" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C306" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="1">
+        <v>226</v>
+      </c>
+      <c r="B307" t="s" s="1">
         <v>211</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B138" s="1" t="s">
+      <c r="C307" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="1">
+        <v>252</v>
+      </c>
+      <c r="B308" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C308" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="1">
+        <v>311</v>
+      </c>
+      <c r="B309" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C309" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="1">
+        <v>330</v>
+      </c>
+      <c r="B310" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C310" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="1">
+        <v>377</v>
+      </c>
+      <c r="B311" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C311" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="1">
+        <v>397</v>
+      </c>
+      <c r="B312" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C312" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="1">
+        <v>415</v>
+      </c>
+      <c r="B313" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C313" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="1">
+        <v>498</v>
+      </c>
+      <c r="B314" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C314" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="1">
+        <v>473</v>
+      </c>
+      <c r="B315" t="s" s="1">
         <v>213</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>5</v>
+      <c r="C315" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="1">
+        <v>269</v>
+      </c>
+      <c r="B316" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="C316" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="B317" t="s" s="1">
+        <v>248</v>
+      </c>
+      <c r="C317" t="s" s="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="1">
+        <v>538</v>
+      </c>
+      <c r="B318" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="C318" t="s" s="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="1">
+        <v>478</v>
+      </c>
+      <c r="B319" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C319" t="s" s="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="1">
+        <v>443</v>
+      </c>
+      <c r="B320" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C320" t="s" s="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="1">
+        <v>230</v>
+      </c>
+      <c r="B321" t="s" s="1">
+        <v>231</v>
+      </c>
+      <c r="C321" t="s" s="1">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -3216,8 +6247,8 @@
   <dimension ref="D2:F35"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="4" max="4" width="36.0769230769231" customWidth="1"/>
-    <col min="5" max="6" width="15.875" customWidth="1"/>
+    <col min="4" max="4" customWidth="true" width="36.0769230769231"/>
+    <col min="5" max="6" customWidth="true" width="15.875"/>
   </cols>
   <sheetData>
     <row r="2" spans="4:6">

--- a/core/src/main/resources/baseFiles/excel/Reports.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Reports.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4221" uniqueCount="599">
   <si>
     <t>Firm</t>
   </si>
@@ -1705,6 +1705,126 @@
   </si>
   <si>
     <t>Franklin Law</t>
+  </si>
+  <si>
+    <t>2min 28</t>
+  </si>
+  <si>
+    <t>1min 8</t>
+  </si>
+  <si>
+    <t>2min 17</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Alta Batalla</t>
+  </si>
+  <si>
+    <t>1min 56</t>
+  </si>
+  <si>
+    <t>1min 17</t>
+  </si>
+  <si>
+    <t>1min 32</t>
+  </si>
+  <si>
+    <t>2min 35</t>
+  </si>
+  <si>
+    <t>2min 0</t>
+  </si>
+  <si>
+    <t>Alessandri</t>
+  </si>
+  <si>
+    <t>ARIFA</t>
+  </si>
+  <si>
+    <t>1min 21</t>
+  </si>
+  <si>
+    <t>1min 48</t>
+  </si>
+  <si>
+    <t>GPA Advogados</t>
+  </si>
+  <si>
+    <t>ErsoyBilgehan</t>
+  </si>
+  <si>
+    <t>Mishcon de Reya</t>
+  </si>
+  <si>
+    <t>Drzewiecki Tomaszek</t>
+  </si>
+  <si>
+    <t>Darrois</t>
+  </si>
+  <si>
+    <t>B2R Law</t>
+  </si>
+  <si>
+    <t>Moalem Weitemeyer</t>
+  </si>
+  <si>
+    <t>Hoffmann Liebs</t>
+  </si>
+  <si>
+    <t>Kromann Reumert</t>
+  </si>
+  <si>
+    <t>Holmes</t>
+  </si>
+  <si>
+    <t>Theart Mey</t>
+  </si>
+  <si>
+    <t>Hügel</t>
+  </si>
+  <si>
+    <t>JB Law</t>
+  </si>
+  <si>
+    <t>Juris</t>
+  </si>
+  <si>
+    <t>Perchstone &amp; Graeys</t>
+  </si>
+  <si>
+    <t>Nysingh advocaten-notarissen N.V.</t>
+  </si>
+  <si>
+    <t>HARTE-BAVENDAMM</t>
+  </si>
+  <si>
+    <t>Stek</t>
+  </si>
+  <si>
+    <t>Desfilis</t>
+  </si>
+  <si>
+    <t>Ojukwu Faotu &amp; Yusuf</t>
+  </si>
+  <si>
+    <t>Konecna &amp; Zacha</t>
+  </si>
+  <si>
+    <t>Zamfirescu Racoti Predoiu</t>
+  </si>
+  <si>
+    <t>SLKB</t>
+  </si>
+  <si>
+    <t>Boodle Hatfield</t>
+  </si>
+  <si>
+    <t>Mccann Fitz Gerald</t>
+  </si>
+  <si>
+    <t>Chrysses Demetriades &amp; Co</t>
   </si>
 </sst>
 </file>
@@ -2692,7 +2812,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C321"/>
+  <dimension ref="A1:C315"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.6634615384615"/>
@@ -2725,7 +2845,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="1">
-        <v>518</v>
+        <v>582</v>
       </c>
       <c r="B3" t="s" s="1">
         <v>24</v>
@@ -2736,10 +2856,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>527</v>
+        <v>574</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>24</v>
+        <v>550</v>
       </c>
       <c r="C4" t="s" s="1">
         <v>5</v>
@@ -2747,10 +2867,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>537</v>
+        <v>336</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s" s="1">
         <v>5</v>
@@ -2758,10 +2878,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="1">
-        <v>544</v>
+        <v>423</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>24</v>
+        <v>559</v>
       </c>
       <c r="C6" t="s" s="1">
         <v>5</v>
@@ -2769,10 +2889,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="C7" t="s" s="1">
         <v>5</v>
@@ -2780,10 +2900,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="1">
-        <v>549</v>
+        <v>244</v>
       </c>
       <c r="B8" t="s" s="1">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="C8" t="s" s="1">
         <v>5</v>
@@ -2791,10 +2911,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="1">
-        <v>423</v>
+        <v>485</v>
       </c>
       <c r="B9" t="s" s="1">
-        <v>424</v>
+        <v>571</v>
       </c>
       <c r="C9" t="s" s="1">
         <v>5</v>
@@ -2802,10 +2922,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="1">
-        <v>283</v>
+        <v>374</v>
       </c>
       <c r="B10" t="s" s="1">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s" s="1">
         <v>5</v>
@@ -2813,10 +2933,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="1">
-        <v>244</v>
+        <v>429</v>
       </c>
       <c r="B11" t="s" s="1">
-        <v>245</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s" s="1">
         <v>5</v>
@@ -2824,10 +2944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="1">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="B12" t="s" s="1">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s" s="1">
         <v>5</v>
@@ -2835,10 +2955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="1">
-        <v>429</v>
+        <v>253</v>
       </c>
       <c r="B13" t="s" s="1">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s" s="1">
         <v>5</v>
@@ -2846,10 +2966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="1">
-        <v>485</v>
+        <v>381</v>
       </c>
       <c r="B14" t="s" s="1">
-        <v>486</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s" s="1">
         <v>5</v>
@@ -2857,10 +2977,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="1">
-        <v>253</v>
+        <v>305</v>
       </c>
       <c r="B15" t="s" s="1">
-        <v>254</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s" s="1">
         <v>5</v>
@@ -2868,10 +2988,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="1">
-        <v>374</v>
+        <v>460</v>
       </c>
       <c r="B16" t="s" s="1">
-        <v>375</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s" s="1">
         <v>5</v>
@@ -2879,10 +2999,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="1">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="B17" t="s" s="1">
-        <v>440</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s" s="1">
         <v>5</v>
@@ -2890,10 +3010,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="1">
-        <v>501</v>
+        <v>273</v>
       </c>
       <c r="B18" t="s" s="1">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s" s="1">
         <v>5</v>
@@ -2901,10 +3021,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="1">
-        <v>338</v>
+        <v>465</v>
       </c>
       <c r="B19" t="s" s="1">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s" s="1">
         <v>5</v>
@@ -2912,10 +3032,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="1">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="B20" t="s" s="1">
-        <v>382</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s" s="1">
         <v>5</v>
@@ -2923,10 +3043,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="1">
-        <v>333</v>
+        <v>276</v>
       </c>
       <c r="B21" t="s" s="1">
-        <v>464</v>
+        <v>130</v>
       </c>
       <c r="C21" t="s" s="1">
         <v>5</v>
@@ -2934,10 +3054,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="1">
-        <v>273</v>
+        <v>435</v>
       </c>
       <c r="B22" t="s" s="1">
-        <v>110</v>
+        <v>259</v>
       </c>
       <c r="C22" t="s" s="1">
         <v>5</v>
@@ -2945,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="1">
-        <v>460</v>
+        <v>585</v>
       </c>
       <c r="B23" t="s" s="1">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C23" t="s" s="1">
         <v>5</v>
@@ -2956,10 +3076,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="1">
-        <v>475</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s" s="1">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s" s="1">
         <v>5</v>
@@ -2967,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="1">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="B25" t="s" s="1">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="C25" t="s" s="1">
         <v>5</v>
@@ -2978,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="1">
-        <v>465</v>
+        <v>591</v>
       </c>
       <c r="B26" t="s" s="1">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s" s="1">
         <v>5</v>
@@ -2989,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="1">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="B27" t="s" s="1">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s" s="1">
         <v>5</v>
@@ -3000,10 +3120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="1">
-        <v>535</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="1">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="C28" t="s" s="1">
         <v>5</v>
@@ -3011,10 +3131,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="1">
-        <v>539</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="1">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="C29" t="s" s="1">
         <v>5</v>
@@ -3022,10 +3142,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="1">
-        <v>435</v>
+        <v>392</v>
       </c>
       <c r="B30" t="s" s="1">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="C30" t="s" s="1">
         <v>5</v>
@@ -3033,10 +3153,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="1">
-        <v>556</v>
+        <v>349</v>
       </c>
       <c r="B31" t="s" s="1">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="C31" t="s" s="1">
         <v>5</v>
@@ -3044,10 +3164,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="1">
-        <v>257</v>
+        <v>350</v>
       </c>
       <c r="B32" t="s" s="1">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="C32" t="s" s="1">
         <v>5</v>
@@ -3055,10 +3175,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="1">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="B33" t="s" s="1">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C33" t="s" s="1">
         <v>5</v>
@@ -3066,10 +3186,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="1">
-        <v>267</v>
+        <v>577</v>
       </c>
       <c r="B34" t="s" s="1">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C34" t="s" s="1">
         <v>5</v>
@@ -3077,10 +3197,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="1">
-        <v>350</v>
+        <v>399</v>
       </c>
       <c r="B35" t="s" s="1">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s" s="1">
         <v>5</v>
@@ -3088,10 +3208,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="1">
-        <v>305</v>
+        <v>449</v>
       </c>
       <c r="B36" t="s" s="1">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C36" t="s" s="1">
         <v>5</v>
@@ -3099,10 +3219,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="1">
-        <v>392</v>
+        <v>513</v>
       </c>
       <c r="B37" t="s" s="1">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C37" t="s" s="1">
         <v>5</v>
@@ -3110,10 +3230,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="1">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="1">
-        <v>307</v>
+        <v>205</v>
       </c>
       <c r="C38" t="s" s="1">
         <v>5</v>
@@ -3121,10 +3241,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="1">
-        <v>395</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="1">
-        <v>307</v>
+        <v>208</v>
       </c>
       <c r="C39" t="s" s="1">
         <v>5</v>
@@ -3132,10 +3252,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="1">
-        <v>513</v>
+        <v>263</v>
       </c>
       <c r="B40" t="s" s="1">
-        <v>307</v>
+        <v>208</v>
       </c>
       <c r="C40" t="s" s="1">
         <v>5</v>
@@ -3143,10 +3263,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="1">
-        <v>349</v>
+        <v>496</v>
       </c>
       <c r="B41" t="s" s="1">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C41" t="s" s="1">
         <v>5</v>
@@ -3154,98 +3274,98 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="1">
-        <v>449</v>
+        <v>487</v>
       </c>
       <c r="B42" t="s" s="1">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s" s="1">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="1">
-        <v>540</v>
+        <v>508</v>
       </c>
       <c r="B43" t="s" s="1">
-        <v>194</v>
+        <v>567</v>
       </c>
       <c r="C43" t="s" s="1">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="1">
-        <v>399</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="1">
-        <v>217</v>
+        <v>559</v>
       </c>
       <c r="C44" t="s" s="1">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="1">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="1">
-        <v>203</v>
+        <v>561</v>
       </c>
       <c r="C45" t="s" s="1">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="1">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B46" t="s" s="1">
-        <v>205</v>
+        <v>568</v>
       </c>
       <c r="C46" t="s" s="1">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="1">
-        <v>301</v>
+        <v>454</v>
       </c>
       <c r="B47" t="s" s="1">
-        <v>205</v>
+        <v>455</v>
       </c>
       <c r="C47" t="s" s="1">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="1">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="1">
-        <v>205</v>
+        <v>564</v>
       </c>
       <c r="C48" t="s" s="1">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="1">
-        <v>496</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="1">
-        <v>211</v>
+        <v>524</v>
       </c>
       <c r="C49" t="s" s="1">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="1">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B50" t="s" s="1">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s" s="1">
         <v>215</v>
@@ -3253,10 +3373,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="1">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B51" t="s" s="1">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="C51" t="s" s="1">
         <v>215</v>
@@ -3264,10 +3384,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="1">
-        <v>367</v>
+        <v>433</v>
       </c>
       <c r="B52" t="s" s="1">
-        <v>368</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s" s="1">
         <v>215</v>
@@ -3275,10 +3395,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="1">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s" s="1">
-        <v>354</v>
+        <v>565</v>
       </c>
       <c r="C53" t="s" s="1">
         <v>215</v>
@@ -3286,10 +3406,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="1">
-        <v>454</v>
+        <v>547</v>
       </c>
       <c r="B54" t="s" s="1">
-        <v>455</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s" s="1">
         <v>215</v>
@@ -3297,10 +3417,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="1">
-        <v>542</v>
+        <v>500</v>
       </c>
       <c r="B55" t="s" s="1">
-        <v>245</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s" s="1">
         <v>215</v>
@@ -3308,10 +3428,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="1">
-        <v>426</v>
+        <v>363</v>
       </c>
       <c r="B56" t="s" s="1">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s" s="1">
         <v>215</v>
@@ -3319,10 +3439,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="1">
-        <v>433</v>
+        <v>219</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>254</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s" s="1">
         <v>215</v>
@@ -3330,10 +3450,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="1">
-        <v>240</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>241</v>
+        <v>560</v>
       </c>
       <c r="C58" t="s" s="1">
         <v>215</v>
@@ -3341,10 +3461,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="1">
-        <v>500</v>
+        <v>218</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>241</v>
+        <v>560</v>
       </c>
       <c r="C59" t="s" s="1">
         <v>215</v>
@@ -3355,7 +3475,7 @@
         <v>502</v>
       </c>
       <c r="B60" t="s" s="1">
-        <v>375</v>
+        <v>560</v>
       </c>
       <c r="C60" t="s" s="1">
         <v>215</v>
@@ -3363,10 +3483,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="1">
-        <v>439</v>
+        <v>502</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C61" t="s" s="1">
         <v>215</v>
@@ -3374,10 +3494,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="1">
-        <v>218</v>
+        <v>505</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>66</v>
+        <v>491</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>215</v>
@@ -3385,10 +3505,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="1">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>70</v>
+        <v>491</v>
       </c>
       <c r="C63" t="s" s="1">
         <v>215</v>
@@ -3396,10 +3516,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="1">
-        <v>547</v>
+        <v>229</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C64" t="s" s="1">
         <v>215</v>
@@ -3407,10 +3527,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="1">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>404</v>
+        <v>562</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>215</v>
@@ -3418,10 +3538,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="1">
-        <v>519</v>
+        <v>233</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>520</v>
+        <v>562</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>215</v>
@@ -3429,10 +3549,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="1">
-        <v>533</v>
+        <v>239</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s" s="1">
         <v>215</v>
@@ -3440,10 +3560,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="1">
-        <v>444</v>
+        <v>340</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>445</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s" s="1">
         <v>215</v>
@@ -3451,10 +3571,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="1">
-        <v>505</v>
+        <v>295</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>445</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>215</v>
@@ -3462,10 +3582,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="1">
-        <v>364</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>215</v>
@@ -3473,10 +3593,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="1">
-        <v>490</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>491</v>
+        <v>90</v>
       </c>
       <c r="C71" t="s" s="1">
         <v>215</v>
@@ -3484,10 +3604,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="1">
-        <v>233</v>
+        <v>339</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C72" t="s" s="1">
         <v>215</v>
@@ -3495,10 +3615,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="1">
-        <v>503</v>
+        <v>570</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>504</v>
+        <v>464</v>
       </c>
       <c r="C73" t="s" s="1">
         <v>215</v>
@@ -3506,10 +3626,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="1">
-        <v>317</v>
+        <v>511</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C74" t="s" s="1">
         <v>215</v>
@@ -3517,10 +3637,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="1">
-        <v>522</v>
+        <v>427</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>84</v>
+        <v>256</v>
       </c>
       <c r="C75" t="s" s="1">
         <v>215</v>
@@ -3528,10 +3648,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="1">
-        <v>229</v>
+        <v>417</v>
       </c>
       <c r="B76" t="s" s="1">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="C76" t="s" s="1">
         <v>215</v>
@@ -3539,10 +3659,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="1">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="B77" t="s" s="1">
-        <v>88</v>
+        <v>256</v>
       </c>
       <c r="C77" t="s" s="1">
         <v>215</v>
@@ -3550,10 +3670,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="1">
-        <v>427</v>
+        <v>240</v>
       </c>
       <c r="B78" t="s" s="1">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C78" t="s" s="1">
         <v>215</v>
@@ -3561,10 +3681,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="1">
-        <v>529</v>
+        <v>490</v>
       </c>
       <c r="B79" t="s" s="1">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C79" t="s" s="1">
         <v>215</v>
@@ -3572,10 +3692,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="1">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="B80" t="s" s="1">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="C80" t="s" s="1">
         <v>215</v>
@@ -3583,10 +3703,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="1">
-        <v>463</v>
+        <v>380</v>
       </c>
       <c r="B81" t="s" s="1">
-        <v>464</v>
+        <v>323</v>
       </c>
       <c r="C81" t="s" s="1">
         <v>215</v>
@@ -3594,10 +3714,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="1">
-        <v>255</v>
+        <v>499</v>
       </c>
       <c r="B82" t="s" s="1">
-        <v>256</v>
+        <v>323</v>
       </c>
       <c r="C82" t="s" s="1">
         <v>215</v>
@@ -3605,10 +3725,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="1">
-        <v>295</v>
+        <v>479</v>
       </c>
       <c r="B83" t="s" s="1">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C83" t="s" s="1">
         <v>215</v>
@@ -3616,10 +3736,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="1">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s" s="1">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C84" t="s" s="1">
         <v>215</v>
@@ -3627,10 +3747,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="1">
-        <v>528</v>
+        <v>594</v>
       </c>
       <c r="B85" t="s" s="1">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C85" t="s" s="1">
         <v>215</v>
@@ -3638,10 +3758,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="1">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="B86" t="s" s="1">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C86" t="s" s="1">
         <v>215</v>
@@ -3649,10 +3769,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="1">
-        <v>322</v>
+        <v>588</v>
       </c>
       <c r="B87" t="s" s="1">
-        <v>323</v>
+        <v>106</v>
       </c>
       <c r="C87" t="s" s="1">
         <v>215</v>
@@ -3660,10 +3780,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="1">
-        <v>507</v>
+        <v>596</v>
       </c>
       <c r="B88" t="s" s="1">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C88" t="s" s="1">
         <v>215</v>
@@ -3671,10 +3791,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="1">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="1">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C89" t="s" s="1">
         <v>215</v>
@@ -3682,10 +3802,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="1">
-        <v>417</v>
+        <v>274</v>
       </c>
       <c r="B90" t="s" s="1">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C90" t="s" s="1">
         <v>215</v>
@@ -3693,10 +3813,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="1">
-        <v>532</v>
+        <v>444</v>
       </c>
       <c r="B91" t="s" s="1">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C91" t="s" s="1">
         <v>215</v>
@@ -3704,10 +3824,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="1">
-        <v>315</v>
+        <v>216</v>
       </c>
       <c r="B92" t="s" s="1">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C92" t="s" s="1">
         <v>215</v>
@@ -3715,10 +3835,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="1">
-        <v>468</v>
+        <v>597</v>
       </c>
       <c r="B93" t="s" s="1">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C93" t="s" s="1">
         <v>215</v>
@@ -3726,10 +3846,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="1">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B94" t="s" s="1">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C94" t="s" s="1">
         <v>215</v>
@@ -3737,10 +3857,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="1">
-        <v>480</v>
+        <v>221</v>
       </c>
       <c r="B95" t="s" s="1">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C95" t="s" s="1">
         <v>215</v>
@@ -3748,10 +3868,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="1">
-        <v>555</v>
+        <v>506</v>
       </c>
       <c r="B96" t="s" s="1">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="C96" t="s" s="1">
         <v>215</v>
@@ -3759,10 +3879,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="1">
-        <v>416</v>
+        <v>235</v>
       </c>
       <c r="B97" t="s" s="1">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C97" t="s" s="1">
         <v>215</v>
@@ -3770,10 +3890,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="1">
-        <v>264</v>
+        <v>587</v>
       </c>
       <c r="B98" t="s" s="1">
-        <v>265</v>
+        <v>120</v>
       </c>
       <c r="C98" t="s" s="1">
         <v>215</v>
@@ -3781,10 +3901,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="1">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="B99" t="s" s="1">
-        <v>265</v>
+        <v>123</v>
       </c>
       <c r="C99" t="s" s="1">
         <v>215</v>
@@ -3792,10 +3912,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="1">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="B100" t="s" s="1">
-        <v>265</v>
+        <v>123</v>
       </c>
       <c r="C100" t="s" s="1">
         <v>215</v>
@@ -3803,10 +3923,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="1">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="B101" t="s" s="1">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C101" t="s" s="1">
         <v>215</v>
@@ -3814,10 +3934,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="1">
-        <v>235</v>
+        <v>385</v>
       </c>
       <c r="B102" t="s" s="1">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C102" t="s" s="1">
         <v>215</v>
@@ -3825,10 +3945,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="1">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="B103" t="s" s="1">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C103" t="s" s="1">
         <v>215</v>
@@ -3836,10 +3956,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="1">
-        <v>289</v>
+        <v>446</v>
       </c>
       <c r="B104" t="s" s="1">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C104" t="s" s="1">
         <v>215</v>
@@ -3847,10 +3967,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="1">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="B105" t="s" s="1">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C105" t="s" s="1">
         <v>215</v>
@@ -3858,7 +3978,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="1">
-        <v>329</v>
+        <v>581</v>
       </c>
       <c r="B106" t="s" s="1">
         <v>126</v>
@@ -3869,10 +3989,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="1">
-        <v>493</v>
+        <v>329</v>
       </c>
       <c r="B107" t="s" s="1">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C107" t="s" s="1">
         <v>215</v>
@@ -3880,10 +4000,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="1">
-        <v>506</v>
+        <v>576</v>
       </c>
       <c r="B108" t="s" s="1">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C108" t="s" s="1">
         <v>215</v>
@@ -3891,7 +4011,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="1">
-        <v>536</v>
+        <v>578</v>
       </c>
       <c r="B109" t="s" s="1">
         <v>130</v>
@@ -3902,7 +4022,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="1">
-        <v>482</v>
+        <v>319</v>
       </c>
       <c r="B110" t="s" s="1">
         <v>134</v>
@@ -3913,7 +4033,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="1">
-        <v>526</v>
+        <v>589</v>
       </c>
       <c r="B111" t="s" s="1">
         <v>134</v>
@@ -3924,7 +4044,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="1">
-        <v>319</v>
+        <v>289</v>
       </c>
       <c r="B112" t="s" s="1">
         <v>138</v>
@@ -3935,7 +4055,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="1">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B113" t="s" s="1">
         <v>138</v>
@@ -3946,7 +4066,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="1">
-        <v>425</v>
+        <v>482</v>
       </c>
       <c r="B114" t="s" s="1">
         <v>138</v>
@@ -3957,7 +4077,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="1">
-        <v>481</v>
+        <v>400</v>
       </c>
       <c r="B115" t="s" s="1">
         <v>138</v>
@@ -3968,7 +4088,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="1">
-        <v>511</v>
+        <v>598</v>
       </c>
       <c r="B116" t="s" s="1">
         <v>138</v>
@@ -3979,7 +4099,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="1">
-        <v>344</v>
+        <v>516</v>
       </c>
       <c r="B117" t="s" s="1">
         <v>143</v>
@@ -3990,7 +4110,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="1">
-        <v>422</v>
+        <v>344</v>
       </c>
       <c r="B118" t="s" s="1">
         <v>143</v>
@@ -4001,7 +4121,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="1">
-        <v>557</v>
+        <v>441</v>
       </c>
       <c r="B119" t="s" s="1">
         <v>143</v>
@@ -4012,7 +4132,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="1">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="B120" t="s" s="1">
         <v>143</v>
@@ -4023,7 +4143,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="1">
-        <v>258</v>
+        <v>425</v>
       </c>
       <c r="B121" t="s" s="1">
         <v>259</v>
@@ -4034,7 +4154,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="1">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="B122" t="s" s="1">
         <v>259</v>
@@ -4045,7 +4165,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="1">
-        <v>346</v>
+        <v>268</v>
       </c>
       <c r="B123" t="s" s="1">
         <v>259</v>
@@ -4056,7 +4176,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="1">
-        <v>543</v>
+        <v>481</v>
       </c>
       <c r="B124" t="s" s="1">
         <v>259</v>
@@ -4067,10 +4187,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="1">
-        <v>546</v>
+        <v>373</v>
       </c>
       <c r="B125" t="s" s="1">
-        <v>259</v>
+        <v>145</v>
       </c>
       <c r="C125" t="s" s="1">
         <v>215</v>
@@ -4078,7 +4198,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="1">
-        <v>373</v>
+        <v>287</v>
       </c>
       <c r="B126" t="s" s="1">
         <v>145</v>
@@ -4089,7 +4209,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="1">
-        <v>432</v>
+        <v>356</v>
       </c>
       <c r="B127" t="s" s="1">
         <v>145</v>
@@ -4100,10 +4220,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="1">
-        <v>239</v>
+        <v>334</v>
       </c>
       <c r="B128" t="s" s="1">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C128" t="s" s="1">
         <v>215</v>
@@ -4111,7 +4231,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="1">
-        <v>325</v>
+        <v>239</v>
       </c>
       <c r="B129" t="s" s="1">
         <v>148</v>
@@ -4122,7 +4242,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="1">
-        <v>340</v>
+        <v>432</v>
       </c>
       <c r="B130" t="s" s="1">
         <v>148</v>
@@ -4133,7 +4253,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="1">
-        <v>351</v>
+        <v>271</v>
       </c>
       <c r="B131" t="s" s="1">
         <v>148</v>
@@ -4144,7 +4264,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="1">
-        <v>369</v>
+        <v>453</v>
       </c>
       <c r="B132" t="s" s="1">
         <v>148</v>
@@ -4155,7 +4275,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="1">
-        <v>409</v>
+        <v>258</v>
       </c>
       <c r="B133" t="s" s="1">
         <v>148</v>
@@ -4166,7 +4286,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="1">
-        <v>477</v>
+        <v>237</v>
       </c>
       <c r="B134" t="s" s="1">
         <v>148</v>
@@ -4177,10 +4297,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="1">
-        <v>222</v>
+        <v>463</v>
       </c>
       <c r="B135" t="s" s="1">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C135" t="s" s="1">
         <v>215</v>
@@ -4188,10 +4308,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="1">
-        <v>275</v>
+        <v>351</v>
       </c>
       <c r="B136" t="s" s="1">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C136" t="s" s="1">
         <v>215</v>
@@ -4199,10 +4319,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="1">
-        <v>277</v>
+        <v>363</v>
       </c>
       <c r="B137" t="s" s="1">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C137" t="s" s="1">
         <v>215</v>
@@ -4210,10 +4330,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="1">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="B138" t="s" s="1">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C138" t="s" s="1">
         <v>215</v>
@@ -4221,10 +4341,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="1">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B139" t="s" s="1">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C139" t="s" s="1">
         <v>215</v>
@@ -4232,7 +4352,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="1">
-        <v>400</v>
+        <v>497</v>
       </c>
       <c r="B140" t="s" s="1">
         <v>150</v>
@@ -4243,7 +4363,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="1">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="B141" t="s" s="1">
         <v>150</v>
@@ -4254,7 +4374,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="1">
-        <v>441</v>
+        <v>332</v>
       </c>
       <c r="B142" t="s" s="1">
         <v>150</v>
@@ -4265,7 +4385,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="1">
-        <v>450</v>
+        <v>275</v>
       </c>
       <c r="B143" t="s" s="1">
         <v>150</v>
@@ -4276,7 +4396,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="1">
-        <v>497</v>
+        <v>583</v>
       </c>
       <c r="B144" t="s" s="1">
         <v>150</v>
@@ -4287,10 +4407,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="1">
-        <v>516</v>
+        <v>477</v>
       </c>
       <c r="B145" t="s" s="1">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C145" t="s" s="1">
         <v>215</v>
@@ -4298,7 +4418,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="1">
-        <v>258</v>
+        <v>386</v>
       </c>
       <c r="B146" t="s" s="1">
         <v>156</v>
@@ -4309,7 +4429,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="1">
-        <v>313</v>
+        <v>450</v>
       </c>
       <c r="B147" t="s" s="1">
         <v>156</v>
@@ -4320,7 +4440,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="1">
-        <v>442</v>
+        <v>313</v>
       </c>
       <c r="B148" t="s" s="1">
         <v>156</v>
@@ -4331,7 +4451,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="1">
-        <v>453</v>
+        <v>321</v>
       </c>
       <c r="B149" t="s" s="1">
         <v>156</v>
@@ -4342,7 +4462,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="1">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="B150" t="s" s="1">
         <v>156</v>
@@ -4353,7 +4473,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="1">
-        <v>227</v>
+        <v>422</v>
       </c>
       <c r="B151" t="s" s="1">
         <v>160</v>
@@ -4364,7 +4484,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="1">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="B152" t="s" s="1">
         <v>160</v>
@@ -4375,10 +4495,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="1">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="B153" t="s" s="1">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C153" t="s" s="1">
         <v>215</v>
@@ -4386,10 +4506,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="1">
-        <v>278</v>
+        <v>593</v>
       </c>
       <c r="B154" t="s" s="1">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C154" t="s" s="1">
         <v>215</v>
@@ -4397,7 +4517,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="1">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B155" t="s" s="1">
         <v>164</v>
@@ -4408,7 +4528,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="1">
-        <v>321</v>
+        <v>418</v>
       </c>
       <c r="B156" t="s" s="1">
         <v>164</v>
@@ -4419,7 +4539,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="1">
-        <v>355</v>
+        <v>503</v>
       </c>
       <c r="B157" t="s" s="1">
         <v>164</v>
@@ -4430,7 +4550,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="1">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B158" t="s" s="1">
         <v>164</v>
@@ -4441,10 +4561,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="1">
-        <v>452</v>
+        <v>348</v>
       </c>
       <c r="B159" t="s" s="1">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C159" t="s" s="1">
         <v>215</v>
@@ -4452,7 +4572,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="1">
-        <v>238</v>
+        <v>364</v>
       </c>
       <c r="B160" t="s" s="1">
         <v>169</v>
@@ -4463,7 +4583,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="1">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="B161" t="s" s="1">
         <v>169</v>
@@ -4474,7 +4594,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="1">
-        <v>334</v>
+        <v>431</v>
       </c>
       <c r="B162" t="s" s="1">
         <v>169</v>
@@ -4485,7 +4605,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="1">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="B163" t="s" s="1">
         <v>169</v>
@@ -4496,7 +4616,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="1">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B164" t="s" s="1">
         <v>169</v>
@@ -4507,7 +4627,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="1">
-        <v>371</v>
+        <v>447</v>
       </c>
       <c r="B165" t="s" s="1">
         <v>169</v>
@@ -4518,10 +4638,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="1">
-        <v>431</v>
+        <v>278</v>
       </c>
       <c r="B166" t="s" s="1">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C166" t="s" s="1">
         <v>215</v>
@@ -4529,10 +4649,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="1">
-        <v>489</v>
+        <v>280</v>
       </c>
       <c r="B167" t="s" s="1">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C167" t="s" s="1">
         <v>215</v>
@@ -4540,10 +4660,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="1">
-        <v>495</v>
+        <v>376</v>
       </c>
       <c r="B168" t="s" s="1">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C168" t="s" s="1">
         <v>215</v>
@@ -4551,7 +4671,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="1">
-        <v>237</v>
+        <v>406</v>
       </c>
       <c r="B169" t="s" s="1">
         <v>172</v>
@@ -4562,10 +4682,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="1">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="B170" t="s" s="1">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C170" t="s" s="1">
         <v>215</v>
@@ -4573,10 +4693,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="1">
-        <v>312</v>
+        <v>421</v>
       </c>
       <c r="B171" t="s" s="1">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C171" t="s" s="1">
         <v>215</v>
@@ -4584,10 +4704,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="1">
-        <v>521</v>
+        <v>290</v>
       </c>
       <c r="B172" t="s" s="1">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C172" t="s" s="1">
         <v>215</v>
@@ -4595,7 +4715,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="1">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="B173" t="s" s="1">
         <v>178</v>
@@ -4606,7 +4726,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="1">
-        <v>339</v>
+        <v>292</v>
       </c>
       <c r="B174" t="s" s="1">
         <v>178</v>
@@ -4617,7 +4737,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="1">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="B175" t="s" s="1">
         <v>178</v>
@@ -4628,7 +4748,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="1">
-        <v>357</v>
+        <v>471</v>
       </c>
       <c r="B176" t="s" s="1">
         <v>178</v>
@@ -4639,7 +4759,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="1">
-        <v>358</v>
+        <v>272</v>
       </c>
       <c r="B177" t="s" s="1">
         <v>178</v>
@@ -4650,7 +4770,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="1">
-        <v>461</v>
+        <v>586</v>
       </c>
       <c r="B178" t="s" s="1">
         <v>178</v>
@@ -4661,10 +4781,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="1">
-        <v>484</v>
+        <v>281</v>
       </c>
       <c r="B179" t="s" s="1">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C179" t="s" s="1">
         <v>215</v>
@@ -4672,10 +4792,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="1">
-        <v>531</v>
+        <v>232</v>
       </c>
       <c r="B180" t="s" s="1">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C180" t="s" s="1">
         <v>215</v>
@@ -4683,7 +4803,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="1">
-        <v>246</v>
+        <v>484</v>
       </c>
       <c r="B181" t="s" s="1">
         <v>180</v>
@@ -4694,7 +4814,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="1">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="B182" t="s" s="1">
         <v>180</v>
@@ -4705,7 +4825,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="1">
-        <v>363</v>
+        <v>409</v>
       </c>
       <c r="B183" t="s" s="1">
         <v>180</v>
@@ -4716,7 +4836,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="1">
-        <v>366</v>
+        <v>459</v>
       </c>
       <c r="B184" t="s" s="1">
         <v>180</v>
@@ -4727,7 +4847,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="1">
-        <v>383</v>
+        <v>451</v>
       </c>
       <c r="B185" t="s" s="1">
         <v>180</v>
@@ -4738,7 +4858,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="1">
-        <v>386</v>
+        <v>442</v>
       </c>
       <c r="B186" t="s" s="1">
         <v>180</v>
@@ -4749,10 +4869,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="1">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="B187" t="s" s="1">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C187" t="s" s="1">
         <v>215</v>
@@ -4760,10 +4880,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="1">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="B188" t="s" s="1">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C188" t="s" s="1">
         <v>215</v>
@@ -4771,7 +4891,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="1">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="B189" t="s" s="1">
         <v>187</v>
@@ -4782,7 +4902,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="1">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B190" t="s" s="1">
         <v>187</v>
@@ -4793,7 +4913,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="1">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="B191" t="s" s="1">
         <v>187</v>
@@ -4804,7 +4924,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="1">
-        <v>271</v>
+        <v>362</v>
       </c>
       <c r="B192" t="s" s="1">
         <v>187</v>
@@ -4815,7 +4935,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="1">
-        <v>291</v>
+        <v>414</v>
       </c>
       <c r="B193" t="s" s="1">
         <v>187</v>
@@ -4826,10 +4946,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="1">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="B194" t="s" s="1">
-        <v>187</v>
+        <v>307</v>
       </c>
       <c r="C194" t="s" s="1">
         <v>215</v>
@@ -4837,10 +4957,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="1">
-        <v>298</v>
+        <v>495</v>
       </c>
       <c r="B195" t="s" s="1">
-        <v>187</v>
+        <v>307</v>
       </c>
       <c r="C195" t="s" s="1">
         <v>215</v>
@@ -4848,10 +4968,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="1">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="B196" t="s" s="1">
-        <v>187</v>
+        <v>307</v>
       </c>
       <c r="C196" t="s" s="1">
         <v>215</v>
@@ -4859,10 +4979,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="1">
-        <v>347</v>
+        <v>462</v>
       </c>
       <c r="B197" t="s" s="1">
-        <v>187</v>
+        <v>307</v>
       </c>
       <c r="C197" t="s" s="1">
         <v>215</v>
@@ -4870,10 +4990,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="1">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="B198" t="s" s="1">
-        <v>187</v>
+        <v>307</v>
       </c>
       <c r="C198" t="s" s="1">
         <v>215</v>
@@ -4881,10 +5001,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="1">
-        <v>406</v>
+        <v>489</v>
       </c>
       <c r="B199" t="s" s="1">
-        <v>187</v>
+        <v>307</v>
       </c>
       <c r="C199" t="s" s="1">
         <v>215</v>
@@ -4892,10 +5012,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="1">
-        <v>517</v>
+        <v>347</v>
       </c>
       <c r="B200" t="s" s="1">
-        <v>187</v>
+        <v>307</v>
       </c>
       <c r="C200" t="s" s="1">
         <v>215</v>
@@ -4903,7 +5023,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="1">
-        <v>306</v>
+        <v>452</v>
       </c>
       <c r="B201" t="s" s="1">
         <v>307</v>
@@ -4914,10 +5034,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="1">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="B202" t="s" s="1">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="C202" t="s" s="1">
         <v>215</v>
@@ -4925,10 +5045,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="1">
-        <v>388</v>
+        <v>220</v>
       </c>
       <c r="B203" t="s" s="1">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="C203" t="s" s="1">
         <v>215</v>
@@ -4936,10 +5056,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="1">
-        <v>389</v>
+        <v>434</v>
       </c>
       <c r="B204" t="s" s="1">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="C204" t="s" s="1">
         <v>215</v>
@@ -4947,10 +5067,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="1">
-        <v>434</v>
+        <v>291</v>
       </c>
       <c r="B205" t="s" s="1">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="C205" t="s" s="1">
         <v>215</v>
@@ -4958,10 +5078,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="1">
-        <v>447</v>
+        <v>569</v>
       </c>
       <c r="B206" t="s" s="1">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="C206" t="s" s="1">
         <v>215</v>
@@ -4969,10 +5089,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="1">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B207" t="s" s="1">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="C207" t="s" s="1">
         <v>215</v>
@@ -4980,10 +5100,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="1">
-        <v>476</v>
+        <v>260</v>
       </c>
       <c r="B208" t="s" s="1">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="C208" t="s" s="1">
         <v>215</v>
@@ -4991,7 +5111,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="1">
-        <v>221</v>
+        <v>366</v>
       </c>
       <c r="B209" t="s" s="1">
         <v>189</v>
@@ -5002,7 +5122,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="1">
-        <v>251</v>
+        <v>476</v>
       </c>
       <c r="B210" t="s" s="1">
         <v>189</v>
@@ -5013,7 +5133,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="1">
-        <v>279</v>
+        <v>552</v>
       </c>
       <c r="B211" t="s" s="1">
         <v>189</v>
@@ -5024,7 +5144,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="1">
-        <v>281</v>
+        <v>595</v>
       </c>
       <c r="B212" t="s" s="1">
         <v>189</v>
@@ -5035,10 +5155,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="1">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B213" t="s" s="1">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C213" t="s" s="1">
         <v>215</v>
@@ -5046,10 +5166,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="1">
-        <v>371</v>
+        <v>563</v>
       </c>
       <c r="B214" t="s" s="1">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C214" t="s" s="1">
         <v>215</v>
@@ -5057,10 +5177,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="1">
-        <v>451</v>
+        <v>371</v>
       </c>
       <c r="B215" t="s" s="1">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C215" t="s" s="1">
         <v>215</v>
@@ -5068,10 +5188,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="1">
-        <v>456</v>
+        <v>402</v>
       </c>
       <c r="B216" t="s" s="1">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C216" t="s" s="1">
         <v>215</v>
@@ -5079,10 +5199,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="1">
-        <v>470</v>
+        <v>384</v>
       </c>
       <c r="B217" t="s" s="1">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C217" t="s" s="1">
         <v>215</v>
@@ -5090,10 +5210,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="1">
-        <v>530</v>
+        <v>257</v>
       </c>
       <c r="B218" t="s" s="1">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C218" t="s" s="1">
         <v>215</v>
@@ -5101,7 +5221,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="1">
-        <v>228</v>
+        <v>492</v>
       </c>
       <c r="B219" t="s" s="1">
         <v>194</v>
@@ -5112,7 +5232,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="1">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="B220" t="s" s="1">
         <v>194</v>
@@ -5123,7 +5243,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="1">
-        <v>294</v>
+        <v>242</v>
       </c>
       <c r="B221" t="s" s="1">
         <v>194</v>
@@ -5134,7 +5254,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="1">
-        <v>299</v>
+        <v>467</v>
       </c>
       <c r="B222" t="s" s="1">
         <v>194</v>
@@ -5145,7 +5265,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="1">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="B223" t="s" s="1">
         <v>194</v>
@@ -5156,7 +5276,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="1">
-        <v>320</v>
+        <v>266</v>
       </c>
       <c r="B224" t="s" s="1">
         <v>194</v>
@@ -5167,7 +5287,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="1">
-        <v>334</v>
+        <v>517</v>
       </c>
       <c r="B225" t="s" s="1">
         <v>194</v>
@@ -5178,7 +5298,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="1">
-        <v>384</v>
+        <v>580</v>
       </c>
       <c r="B226" t="s" s="1">
         <v>194</v>
@@ -5189,10 +5309,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="1">
-        <v>458</v>
+        <v>328</v>
       </c>
       <c r="B227" t="s" s="1">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C227" t="s" s="1">
         <v>215</v>
@@ -5200,10 +5320,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="1">
-        <v>462</v>
+        <v>401</v>
       </c>
       <c r="B228" t="s" s="1">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C228" t="s" s="1">
         <v>215</v>
@@ -5211,10 +5331,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="1">
-        <v>479</v>
+        <v>439</v>
       </c>
       <c r="B229" t="s" s="1">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C229" t="s" s="1">
         <v>215</v>
@@ -5222,10 +5342,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="1">
-        <v>510</v>
+        <v>228</v>
       </c>
       <c r="B230" t="s" s="1">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C230" t="s" s="1">
         <v>215</v>
@@ -5233,10 +5353,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="1">
-        <v>551</v>
+        <v>251</v>
       </c>
       <c r="B231" t="s" s="1">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C231" t="s" s="1">
         <v>215</v>
@@ -5244,10 +5364,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="1">
-        <v>552</v>
+        <v>378</v>
       </c>
       <c r="B232" t="s" s="1">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C232" t="s" s="1">
         <v>215</v>
@@ -5255,7 +5375,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="1">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="B233" t="s" s="1">
         <v>197</v>
@@ -5266,7 +5386,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="1">
-        <v>234</v>
+        <v>469</v>
       </c>
       <c r="B234" t="s" s="1">
         <v>197</v>
@@ -5277,10 +5397,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="1">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="B235" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C235" t="s" s="1">
         <v>215</v>
@@ -5288,10 +5408,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="1">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="B236" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C236" t="s" s="1">
         <v>215</v>
@@ -5299,10 +5419,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="1">
-        <v>387</v>
+        <v>252</v>
       </c>
       <c r="B237" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C237" t="s" s="1">
         <v>215</v>
@@ -5310,10 +5430,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="1">
-        <v>398</v>
+        <v>300</v>
       </c>
       <c r="B238" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C238" t="s" s="1">
         <v>215</v>
@@ -5321,10 +5441,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="1">
-        <v>401</v>
+        <v>507</v>
       </c>
       <c r="B239" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C239" t="s" s="1">
         <v>215</v>
@@ -5332,10 +5452,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="1">
-        <v>402</v>
+        <v>234</v>
       </c>
       <c r="B240" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C240" t="s" s="1">
         <v>215</v>
@@ -5343,10 +5463,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="1">
-        <v>457</v>
+        <v>413</v>
       </c>
       <c r="B241" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C241" t="s" s="1">
         <v>215</v>
@@ -5354,10 +5474,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="1">
-        <v>488</v>
+        <v>225</v>
       </c>
       <c r="B242" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C242" t="s" s="1">
         <v>215</v>
@@ -5365,10 +5485,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="1">
-        <v>514</v>
+        <v>387</v>
       </c>
       <c r="B243" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C243" t="s" s="1">
         <v>215</v>
@@ -5376,10 +5496,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="1">
-        <v>541</v>
+        <v>343</v>
       </c>
       <c r="B244" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C244" t="s" s="1">
         <v>215</v>
@@ -5387,7 +5507,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="1">
-        <v>224</v>
+        <v>420</v>
       </c>
       <c r="B245" t="s" s="1">
         <v>200</v>
@@ -5398,7 +5518,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="1">
-        <v>282</v>
+        <v>396</v>
       </c>
       <c r="B246" t="s" s="1">
         <v>200</v>
@@ -5409,7 +5529,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="1">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B247" t="s" s="1">
         <v>200</v>
@@ -5420,7 +5540,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="1">
-        <v>318</v>
+        <v>224</v>
       </c>
       <c r="B248" t="s" s="1">
         <v>200</v>
@@ -5431,7 +5551,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="1">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="B249" t="s" s="1">
         <v>200</v>
@@ -5442,7 +5562,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="1">
-        <v>328</v>
+        <v>575</v>
       </c>
       <c r="B250" t="s" s="1">
         <v>200</v>
@@ -5453,10 +5573,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="1">
-        <v>341</v>
+        <v>407</v>
       </c>
       <c r="B251" t="s" s="1">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C251" t="s" s="1">
         <v>215</v>
@@ -5464,10 +5584,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="1">
-        <v>360</v>
+        <v>472</v>
       </c>
       <c r="B252" t="s" s="1">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C252" t="s" s="1">
         <v>215</v>
@@ -5475,10 +5595,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="1">
-        <v>414</v>
+        <v>359</v>
       </c>
       <c r="B253" t="s" s="1">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C253" t="s" s="1">
         <v>215</v>
@@ -5486,10 +5606,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="1">
-        <v>448</v>
+        <v>282</v>
       </c>
       <c r="B254" t="s" s="1">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C254" t="s" s="1">
         <v>215</v>
@@ -5497,10 +5617,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="1">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="B255" t="s" s="1">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C255" t="s" s="1">
         <v>215</v>
@@ -5508,10 +5628,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="1">
-        <v>534</v>
+        <v>473</v>
       </c>
       <c r="B256" t="s" s="1">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C256" t="s" s="1">
         <v>215</v>
@@ -5519,7 +5639,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="1">
-        <v>216</v>
+        <v>372</v>
       </c>
       <c r="B257" t="s" s="1">
         <v>217</v>
@@ -5530,7 +5650,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="1">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="B258" t="s" s="1">
         <v>217</v>
@@ -5541,7 +5661,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="1">
-        <v>285</v>
+        <v>468</v>
       </c>
       <c r="B259" t="s" s="1">
         <v>217</v>
@@ -5552,7 +5672,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="1">
-        <v>286</v>
+        <v>515</v>
       </c>
       <c r="B260" t="s" s="1">
         <v>217</v>
@@ -5563,7 +5683,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="1">
-        <v>296</v>
+        <v>223</v>
       </c>
       <c r="B261" t="s" s="1">
         <v>217</v>
@@ -5574,7 +5694,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="1">
-        <v>300</v>
+        <v>573</v>
       </c>
       <c r="B262" t="s" s="1">
         <v>217</v>
@@ -5585,10 +5705,10 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="1">
-        <v>303</v>
+        <v>458</v>
       </c>
       <c r="B263" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C263" t="s" s="1">
         <v>215</v>
@@ -5596,10 +5716,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="1">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="B264" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C264" t="s" s="1">
         <v>215</v>
@@ -5607,10 +5727,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="1">
-        <v>345</v>
+        <v>261</v>
       </c>
       <c r="B265" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C265" t="s" s="1">
         <v>215</v>
@@ -5618,10 +5738,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="1">
-        <v>393</v>
+        <v>286</v>
       </c>
       <c r="B266" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C266" t="s" s="1">
         <v>215</v>
@@ -5629,10 +5749,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="1">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="B267" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C267" t="s" s="1">
         <v>215</v>
@@ -5640,10 +5760,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="1">
-        <v>407</v>
+        <v>285</v>
       </c>
       <c r="B268" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C268" t="s" s="1">
         <v>215</v>
@@ -5651,10 +5771,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="1">
-        <v>437</v>
+        <v>345</v>
       </c>
       <c r="B269" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C269" t="s" s="1">
         <v>215</v>
@@ -5662,10 +5782,10 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="1">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B270" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C270" t="s" s="1">
         <v>215</v>
@@ -5673,10 +5793,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="1">
-        <v>515</v>
+        <v>590</v>
       </c>
       <c r="B271" t="s" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C271" t="s" s="1">
         <v>215</v>
@@ -5684,10 +5804,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="1">
-        <v>548</v>
+        <v>297</v>
       </c>
       <c r="B272" t="s" s="1">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C272" t="s" s="1">
         <v>215</v>
@@ -5695,10 +5815,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="1">
-        <v>261</v>
+        <v>494</v>
       </c>
       <c r="B273" t="s" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C273" t="s" s="1">
         <v>215</v>
@@ -5706,10 +5826,10 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="1">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B274" t="s" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C274" t="s" s="1">
         <v>215</v>
@@ -5717,10 +5837,10 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="1">
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="B275" t="s" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C275" t="s" s="1">
         <v>215</v>
@@ -5728,10 +5848,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="1">
-        <v>359</v>
+        <v>303</v>
       </c>
       <c r="B276" t="s" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C276" t="s" s="1">
         <v>215</v>
@@ -5739,10 +5859,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="1">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="B277" t="s" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C277" t="s" s="1">
         <v>215</v>
@@ -5750,10 +5870,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="1">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="B278" t="s" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C278" t="s" s="1">
         <v>215</v>
@@ -5761,10 +5881,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="1">
-        <v>472</v>
+        <v>337</v>
       </c>
       <c r="B279" t="s" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C279" t="s" s="1">
         <v>215</v>
@@ -5772,7 +5892,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="1">
-        <v>220</v>
+        <v>466</v>
       </c>
       <c r="B280" t="s" s="1">
         <v>205</v>
@@ -5783,7 +5903,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="1">
-        <v>236</v>
+        <v>448</v>
       </c>
       <c r="B281" t="s" s="1">
         <v>205</v>
@@ -5794,7 +5914,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="1">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="B282" t="s" s="1">
         <v>205</v>
@@ -5805,7 +5925,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="1">
-        <v>333</v>
+        <v>294</v>
       </c>
       <c r="B283" t="s" s="1">
         <v>205</v>
@@ -5816,7 +5936,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="1">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B284" t="s" s="1">
         <v>205</v>
@@ -5827,7 +5947,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="1">
-        <v>380</v>
+        <v>474</v>
       </c>
       <c r="B285" t="s" s="1">
         <v>205</v>
@@ -5838,7 +5958,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="1">
-        <v>413</v>
+        <v>333</v>
       </c>
       <c r="B286" t="s" s="1">
         <v>205</v>
@@ -5849,7 +5969,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="1">
-        <v>448</v>
+        <v>370</v>
       </c>
       <c r="B287" t="s" s="1">
         <v>205</v>
@@ -5860,7 +5980,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="1">
-        <v>466</v>
+        <v>394</v>
       </c>
       <c r="B288" t="s" s="1">
         <v>205</v>
@@ -5871,7 +5991,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="1">
-        <v>467</v>
+        <v>555</v>
       </c>
       <c r="B289" t="s" s="1">
         <v>205</v>
@@ -5882,7 +6002,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="1">
-        <v>474</v>
+        <v>592</v>
       </c>
       <c r="B290" t="s" s="1">
         <v>205</v>
@@ -5893,10 +6013,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="1">
-        <v>545</v>
+        <v>318</v>
       </c>
       <c r="B291" t="s" s="1">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C291" t="s" s="1">
         <v>215</v>
@@ -5904,7 +6024,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="1">
-        <v>270</v>
+        <v>397</v>
       </c>
       <c r="B292" t="s" s="1">
         <v>208</v>
@@ -5915,7 +6035,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="1">
-        <v>297</v>
+        <v>483</v>
       </c>
       <c r="B293" t="s" s="1">
         <v>208</v>
@@ -5926,7 +6046,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="1">
-        <v>316</v>
+        <v>226</v>
       </c>
       <c r="B294" t="s" s="1">
         <v>208</v>
@@ -5937,7 +6057,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="1">
-        <v>324</v>
+        <v>412</v>
       </c>
       <c r="B295" t="s" s="1">
         <v>208</v>
@@ -5948,7 +6068,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="1">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="B296" t="s" s="1">
         <v>208</v>
@@ -5959,7 +6079,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="1">
-        <v>391</v>
+        <v>512</v>
       </c>
       <c r="B297" t="s" s="1">
         <v>208</v>
@@ -5970,7 +6090,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="1">
-        <v>394</v>
+        <v>270</v>
       </c>
       <c r="B298" t="s" s="1">
         <v>208</v>
@@ -5981,7 +6101,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="1">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="B299" t="s" s="1">
         <v>208</v>
@@ -5992,7 +6112,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="1">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="B300" t="s" s="1">
         <v>208</v>
@@ -6003,7 +6123,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="1">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="B301" t="s" s="1">
         <v>208</v>
@@ -6014,7 +6134,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="1">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B302" t="s" s="1">
         <v>208</v>
@@ -6025,7 +6145,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="1">
-        <v>483</v>
+        <v>324</v>
       </c>
       <c r="B303" t="s" s="1">
         <v>208</v>
@@ -6036,10 +6156,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="1">
-        <v>494</v>
+        <v>316</v>
       </c>
       <c r="B304" t="s" s="1">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C304" t="s" s="1">
         <v>215</v>
@@ -6047,10 +6167,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="1">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="B305" t="s" s="1">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C305" t="s" s="1">
         <v>215</v>
@@ -6058,10 +6178,10 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="1">
-        <v>525</v>
+        <v>393</v>
       </c>
       <c r="B306" t="s" s="1">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C306" t="s" s="1">
         <v>215</v>
@@ -6069,7 +6189,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="1">
-        <v>226</v>
+        <v>377</v>
       </c>
       <c r="B307" t="s" s="1">
         <v>211</v>
@@ -6080,7 +6200,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="1">
-        <v>252</v>
+        <v>330</v>
       </c>
       <c r="B308" t="s" s="1">
         <v>211</v>
@@ -6091,7 +6211,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="1">
-        <v>311</v>
+        <v>410</v>
       </c>
       <c r="B309" t="s" s="1">
         <v>211</v>
@@ -6102,10 +6222,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="1">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="B310" t="s" s="1">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C310" t="s" s="1">
         <v>215</v>
@@ -6113,10 +6233,10 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="1">
-        <v>377</v>
+        <v>269</v>
       </c>
       <c r="B311" t="s" s="1">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C311" t="s" s="1">
         <v>215</v>
@@ -6124,111 +6244,45 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="1">
-        <v>397</v>
+        <v>247</v>
       </c>
       <c r="B312" t="s" s="1">
-        <v>211</v>
+        <v>572</v>
       </c>
       <c r="C312" t="s" s="1">
-        <v>215</v>
+        <v>249</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s" s="1">
-        <v>415</v>
+        <v>478</v>
       </c>
       <c r="B313" t="s" s="1">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="C313" t="s" s="1">
-        <v>215</v>
+        <v>249</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s" s="1">
-        <v>498</v>
+        <v>443</v>
       </c>
       <c r="B314" t="s" s="1">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="C314" t="s" s="1">
-        <v>215</v>
+        <v>249</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s" s="1">
-        <v>473</v>
+        <v>230</v>
       </c>
       <c r="B315" t="s" s="1">
-        <v>213</v>
+        <v>565</v>
       </c>
       <c r="C315" t="s" s="1">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="s" s="1">
-        <v>269</v>
-      </c>
-      <c r="B316" t="s" s="1">
-        <v>249</v>
-      </c>
-      <c r="C316" t="s" s="1">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="s" s="1">
-        <v>247</v>
-      </c>
-      <c r="B317" t="s" s="1">
-        <v>248</v>
-      </c>
-      <c r="C317" t="s" s="1">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="s" s="1">
-        <v>538</v>
-      </c>
-      <c r="B318" t="s" s="1">
-        <v>88</v>
-      </c>
-      <c r="C318" t="s" s="1">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="s" s="1">
-        <v>478</v>
-      </c>
-      <c r="B319" t="s" s="1">
-        <v>148</v>
-      </c>
-      <c r="C319" t="s" s="1">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="s" s="1">
-        <v>443</v>
-      </c>
-      <c r="B320" t="s" s="1">
-        <v>164</v>
-      </c>
-      <c r="C320" t="s" s="1">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="s" s="1">
-        <v>230</v>
-      </c>
-      <c r="B321" t="s" s="1">
-        <v>231</v>
-      </c>
-      <c r="C321" t="s" s="1">
         <v>213</v>
       </c>
     </row>

--- a/core/src/main/resources/baseFiles/excel/Reports.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Reports.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4221" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6597" uniqueCount="955">
   <si>
     <t>Firm</t>
   </si>
@@ -1825,6 +1825,1074 @@
   </si>
   <si>
     <t>Chrysses Demetriades &amp; Co</t>
+  </si>
+  <si>
+    <t>Alfaro</t>
+  </si>
+  <si>
+    <t>Bruchou &amp; Funes de Rioja</t>
+  </si>
+  <si>
+    <t>PBP</t>
+  </si>
+  <si>
+    <t>TozziniFreire</t>
+  </si>
+  <si>
+    <t>L O Baptista</t>
+  </si>
+  <si>
+    <t>VSV</t>
+  </si>
+  <si>
+    <t>Licks</t>
+  </si>
+  <si>
+    <t>CRF Rojas</t>
+  </si>
+  <si>
+    <t>HDS</t>
+  </si>
+  <si>
+    <t>Facio &amp; Cañas</t>
+  </si>
+  <si>
+    <t>Levy &amp; Salomão</t>
+  </si>
+  <si>
+    <t>Hulbert Volio</t>
+  </si>
+  <si>
+    <t>López Ribadeneira Mora</t>
+  </si>
+  <si>
+    <t>Gusmão &amp; Labrunie</t>
+  </si>
+  <si>
+    <t>Goodrich Riquelme</t>
+  </si>
+  <si>
+    <t>Aguilar Castillo Love</t>
+  </si>
+  <si>
+    <t>Beretta Godoy</t>
+  </si>
+  <si>
+    <t>Baker Tilly</t>
+  </si>
+  <si>
+    <t>DHC</t>
+  </si>
+  <si>
+    <t>Bullard, Falla, Ezcurra</t>
+  </si>
+  <si>
+    <t>Santos-Elizondo</t>
+  </si>
+  <si>
+    <t>1min 25</t>
+  </si>
+  <si>
+    <t>AMYA</t>
+  </si>
+  <si>
+    <t>Russin, Vecchi &amp; Heredia Bonetti</t>
+  </si>
+  <si>
+    <t>Cascione</t>
+  </si>
+  <si>
+    <t>Rebaza, Alcázar &amp; De Las Casas</t>
+  </si>
+  <si>
+    <t>Pino Elizalde</t>
+  </si>
+  <si>
+    <t>Lexvalor</t>
+  </si>
+  <si>
+    <t>Mendoza</t>
+  </si>
+  <si>
+    <t>Montes, Olivos, Eyzaguirre &amp; Arostegui</t>
+  </si>
+  <si>
+    <t>Noetinger &amp; Armando</t>
+  </si>
+  <si>
+    <t>Rolim Goulart</t>
+  </si>
+  <si>
+    <t>Ibarra, del Paso y Gallego</t>
+  </si>
+  <si>
+    <t>Guerra González y Asociados</t>
+  </si>
+  <si>
+    <t>Sainz</t>
+  </si>
+  <si>
+    <t>Corral Rosales</t>
+  </si>
+  <si>
+    <t>Lloreda Camacho &amp; Co</t>
+  </si>
+  <si>
+    <t>Severgnini, Robiola, Grinberg &amp; Tombeur</t>
+  </si>
+  <si>
+    <t>Cervieri Monsuarez</t>
+  </si>
+  <si>
+    <t>G Breuer</t>
+  </si>
+  <si>
+    <t>Durán &amp; Osorio</t>
+  </si>
+  <si>
+    <t>Pellerano &amp; Herrera</t>
+  </si>
+  <si>
+    <t>Azevedo Sette</t>
+  </si>
+  <si>
+    <t>Araújo e Policastro</t>
+  </si>
+  <si>
+    <t>Dias Carneiro</t>
+  </si>
+  <si>
+    <t>RCTZZ</t>
+  </si>
+  <si>
+    <t>Anaya Diaz Ibanez</t>
+  </si>
+  <si>
+    <t>Jauregui &amp; Del Valle</t>
+  </si>
+  <si>
+    <t>1min 2</t>
+  </si>
+  <si>
+    <t>Lewin &amp; Wills</t>
+  </si>
+  <si>
+    <t>Pellerano Nadal</t>
+  </si>
+  <si>
+    <t>Brons &amp; Salas</t>
+  </si>
+  <si>
+    <t>Delaney Partners</t>
+  </si>
+  <si>
+    <t>Castro Leiva Rendón</t>
+  </si>
+  <si>
+    <t>Cacheaux, Cavazos &amp; Newton</t>
+  </si>
+  <si>
+    <t>Von Wobeser</t>
+  </si>
+  <si>
+    <t>Tanoira Cassagne</t>
+  </si>
+  <si>
+    <t>KLA</t>
+  </si>
+  <si>
+    <t>Henlin Gibson Henlin</t>
+  </si>
+  <si>
+    <t>Marval</t>
+  </si>
+  <si>
+    <t>Nicholson &amp; Cano</t>
+  </si>
+  <si>
+    <t>Dannemann Siemsen</t>
+  </si>
+  <si>
+    <t>Falconi Puig</t>
+  </si>
+  <si>
+    <t>Vidigal Neto Advogados</t>
+  </si>
+  <si>
+    <t>Fernández Secco</t>
+  </si>
+  <si>
+    <t>FBPH Law</t>
+  </si>
+  <si>
+    <t>Lollato Lopes Rangel Ribeiro Advogados</t>
+  </si>
+  <si>
+    <t>BDS Asesores</t>
+  </si>
+  <si>
+    <t>Freitas Leite</t>
+  </si>
+  <si>
+    <t>Estudio Bunge</t>
+  </si>
+  <si>
+    <t>BARENTSKRANS</t>
+  </si>
+  <si>
+    <t>Kochański &amp; Partners</t>
+  </si>
+  <si>
+    <t>Odigo</t>
+  </si>
+  <si>
+    <t>Tuca Zbarcea</t>
+  </si>
+  <si>
+    <t>Finreg 360</t>
+  </si>
+  <si>
+    <t>Kanter</t>
+  </si>
+  <si>
+    <t>Atlas Advokater</t>
+  </si>
+  <si>
+    <t>DMS Legal</t>
+  </si>
+  <si>
+    <t>BARDEHLE PAGENBERG</t>
+  </si>
+  <si>
+    <t>Nunziante Magrone</t>
+  </si>
+  <si>
+    <t>CLEERDIN &amp; HAMER</t>
+  </si>
+  <si>
+    <t>Roca Junyent</t>
+  </si>
+  <si>
+    <t>PM&amp;P</t>
+  </si>
+  <si>
+    <t>Zulficar &amp; Partners</t>
+  </si>
+  <si>
+    <t>Prinz &amp; Partner</t>
+  </si>
+  <si>
+    <t>Kienhuis Legal</t>
+  </si>
+  <si>
+    <t>Ibrachy &amp; Dermarkar</t>
+  </si>
+  <si>
+    <t>AGP Advokater</t>
+  </si>
+  <si>
+    <t>Lakatos Köves &amp; Partners</t>
+  </si>
+  <si>
+    <t>Clemens Law</t>
+  </si>
+  <si>
+    <t>Kondrat</t>
+  </si>
+  <si>
+    <t>Arnold &amp; Siedsma</t>
+  </si>
+  <si>
+    <t>DALDEWOLF</t>
+  </si>
+  <si>
+    <t>Aera</t>
+  </si>
+  <si>
+    <t>Lennox</t>
+  </si>
+  <si>
+    <t>Valfor</t>
+  </si>
+  <si>
+    <t>AS Papadimitriou &amp; Partners</t>
+  </si>
+  <si>
+    <t>Robinson Bertram</t>
+  </si>
+  <si>
+    <t>POROBIJA &amp; ŠPOLJARIĆ</t>
+  </si>
+  <si>
+    <t>Agio Legal</t>
+  </si>
+  <si>
+    <t>Grigorescu Ştefănică</t>
+  </si>
+  <si>
+    <t>BLC Robert &amp; Associates Ltd</t>
+  </si>
+  <si>
+    <t>ACT LEGAL</t>
+  </si>
+  <si>
+    <t>isarpatent München</t>
+  </si>
+  <si>
+    <t>Engling Stritter &amp; Partners</t>
+  </si>
+  <si>
+    <t>Ganado Advocates</t>
+  </si>
+  <si>
+    <t>Patrikios Pavlou &amp; Associates</t>
+  </si>
+  <si>
+    <t>Niederhuber &amp; Partner</t>
+  </si>
+  <si>
+    <t>Dimitrov Petrov &amp; Co</t>
+  </si>
+  <si>
+    <t>Hayes</t>
+  </si>
+  <si>
+    <t>1min 19</t>
+  </si>
+  <si>
+    <t>Liedekerke</t>
+  </si>
+  <si>
+    <t>KLC Law</t>
+  </si>
+  <si>
+    <t>Plesner</t>
+  </si>
+  <si>
+    <t>PricaAndPartners</t>
+  </si>
+  <si>
+    <t>Eversheds Sutherland</t>
+  </si>
+  <si>
+    <t>Rutgers &amp; Posch</t>
+  </si>
+  <si>
+    <t>Vainanidis, Economou &amp; Associates Law Firm</t>
+  </si>
+  <si>
+    <t>Politis &amp; Partners</t>
+  </si>
+  <si>
+    <t>Buss Murton Law</t>
+  </si>
+  <si>
+    <t>Popov, Arnaudov &amp; Partners</t>
+  </si>
+  <si>
+    <t>Scotto Partners</t>
+  </si>
+  <si>
+    <t>TEGOS</t>
+  </si>
+  <si>
+    <t>Elmann</t>
+  </si>
+  <si>
+    <t>Zepos &amp; Yannopoulos</t>
+  </si>
+  <si>
+    <t>GvW Graf von Westphalen</t>
+  </si>
+  <si>
+    <t>Strelia</t>
+  </si>
+  <si>
+    <t>Kyriakides Georgopoulos</t>
+  </si>
+  <si>
+    <t>NESTOR</t>
+  </si>
+  <si>
+    <t>Kaimakliotis</t>
+  </si>
+  <si>
+    <t>Papapolitis &amp; Papapolitis</t>
+  </si>
+  <si>
+    <t>Uría Menéndez</t>
+  </si>
+  <si>
+    <t>De Pardieu</t>
+  </si>
+  <si>
+    <t>Vinge</t>
+  </si>
+  <si>
+    <t>Andersen Tax &amp; Legal Iberia</t>
+  </si>
+  <si>
+    <t>Berggren</t>
+  </si>
+  <si>
+    <t>Ioannides Demetriou LLC</t>
+  </si>
+  <si>
+    <t>NGL Legal</t>
+  </si>
+  <si>
+    <t>Kew Law</t>
+  </si>
+  <si>
+    <t>MSB Solicitors</t>
+  </si>
+  <si>
+    <t>Maikowski &amp; Ninnemann</t>
+  </si>
+  <si>
+    <t>Aumento Law Firm</t>
+  </si>
+  <si>
+    <t>Broseta</t>
+  </si>
+  <si>
+    <t>KBVL Law</t>
+  </si>
+  <si>
+    <t>Adriaanse van der Weel</t>
+  </si>
+  <si>
+    <t>Langseth Advokat</t>
+  </si>
+  <si>
+    <t>VDA Partners</t>
+  </si>
+  <si>
+    <t>Georgiades &amp; Pelides</t>
+  </si>
+  <si>
+    <t>Esche</t>
+  </si>
+  <si>
+    <t>WILLEMSPARK</t>
+  </si>
+  <si>
+    <t>TKP</t>
+  </si>
+  <si>
+    <t>Ukiri Lijadu</t>
+  </si>
+  <si>
+    <t>PlasBossinade</t>
+  </si>
+  <si>
+    <t>Tabacks</t>
+  </si>
+  <si>
+    <t>LexQuire</t>
+  </si>
+  <si>
+    <t>Lacourte Raquin Tatar</t>
+  </si>
+  <si>
+    <t>Cerrahoğlu</t>
+  </si>
+  <si>
+    <t>Orsingher</t>
+  </si>
+  <si>
+    <t>Brinkmann &amp; Partner</t>
+  </si>
+  <si>
+    <t>MOLITOR</t>
+  </si>
+  <si>
+    <t>Dittmar And Indrenius</t>
+  </si>
+  <si>
+    <t>FBL Advogados</t>
+  </si>
+  <si>
+    <t>DORDA</t>
+  </si>
+  <si>
+    <t>KCG Partners</t>
+  </si>
+  <si>
+    <t>Richardson Lissack</t>
+  </si>
+  <si>
+    <t>Rödl &amp; Partner</t>
+  </si>
+  <si>
+    <t>Potamitis Vekris</t>
+  </si>
+  <si>
+    <t>Krogerus</t>
+  </si>
+  <si>
+    <t>Nielsen Nørager</t>
+  </si>
+  <si>
+    <t>Kennedy Van der Laan</t>
+  </si>
+  <si>
+    <t>NPP Legal</t>
+  </si>
+  <si>
+    <t>Chevalier &amp; Sciales</t>
+  </si>
+  <si>
+    <t>Legalis</t>
+  </si>
+  <si>
+    <t>FIVERS</t>
+  </si>
+  <si>
+    <t>MMD Advokati</t>
+  </si>
+  <si>
+    <t>Otis</t>
+  </si>
+  <si>
+    <t>Logos</t>
+  </si>
+  <si>
+    <t>Gárdos Mosonyi Tomori</t>
+  </si>
+  <si>
+    <t>One Essex Court</t>
+  </si>
+  <si>
+    <t>Knezović &amp; Associates</t>
+  </si>
+  <si>
+    <t>Norens</t>
+  </si>
+  <si>
+    <t>Jackson Etti &amp; Edu</t>
+  </si>
+  <si>
+    <t>Ashong Benjamin</t>
+  </si>
+  <si>
+    <t>Betten &amp; Resch</t>
+  </si>
+  <si>
+    <t>2min 14</t>
+  </si>
+  <si>
+    <t>MMAKS</t>
+  </si>
+  <si>
+    <t>Keystone Law</t>
+  </si>
+  <si>
+    <t>Oraro &amp; Company</t>
+  </si>
+  <si>
+    <t>Abrahams &amp; Gross Incorporated</t>
+  </si>
+  <si>
+    <t>DKCO</t>
+  </si>
+  <si>
+    <t>Astrea</t>
+  </si>
+  <si>
+    <t>BDK Advokati</t>
+  </si>
+  <si>
+    <t>Tope Adebayo LP</t>
+  </si>
+  <si>
+    <t>Bulboaca &amp; Asociaţii</t>
+  </si>
+  <si>
+    <t>Knijff</t>
+  </si>
+  <si>
+    <t>Vanberkel</t>
+  </si>
+  <si>
+    <t>Kantor &amp; Immerman</t>
+  </si>
+  <si>
+    <t>Georgiev Todorov &amp; Co</t>
+  </si>
+  <si>
+    <t>Hoffmann Eitle</t>
+  </si>
+  <si>
+    <t>Ekelmans</t>
+  </si>
+  <si>
+    <t>2min 57</t>
+  </si>
+  <si>
+    <t>GÖRG</t>
+  </si>
+  <si>
+    <t>1min 41</t>
+  </si>
+  <si>
+    <t>Advel</t>
+  </si>
+  <si>
+    <t>Sampson Coward LLP</t>
+  </si>
+  <si>
+    <t>Gernandt &amp; Danielsson</t>
+  </si>
+  <si>
+    <t>Burges Salmon</t>
+  </si>
+  <si>
+    <t>Wierzbowski &amp; Partners</t>
+  </si>
+  <si>
+    <t>Gill, Godlonton &amp; Gerrans</t>
+  </si>
+  <si>
+    <t>Davis Polk And Wardwell</t>
+  </si>
+  <si>
+    <t>Titov</t>
+  </si>
+  <si>
+    <t>Mulenga Mundashi Legal Practitioners</t>
+  </si>
+  <si>
+    <t>Heussen</t>
+  </si>
+  <si>
+    <t>Stehlin &amp; Associés</t>
+  </si>
+  <si>
+    <t>Oppenhoff</t>
+  </si>
+  <si>
+    <t>CWA Associates</t>
+  </si>
+  <si>
+    <t>Provença de Carvalho</t>
+  </si>
+  <si>
+    <t>Matouk Bassiouny</t>
+  </si>
+  <si>
+    <t>Elverdam</t>
+  </si>
+  <si>
+    <t>Fellner Wratzfeld &amp; Partner</t>
+  </si>
+  <si>
+    <t>Skils Law</t>
+  </si>
+  <si>
+    <t>MVVP advocaten</t>
+  </si>
+  <si>
+    <t>Kallio Law</t>
+  </si>
+  <si>
+    <t>Interlaw</t>
+  </si>
+  <si>
+    <t>Sibinčič Novak &amp; Partners</t>
+  </si>
+  <si>
+    <t>Muşat &amp; Asociaţii</t>
+  </si>
+  <si>
+    <t>Rassers Advocaten</t>
+  </si>
+  <si>
+    <t>J-K Gadzama LLP</t>
+  </si>
+  <si>
+    <t>Czabański Gałuszyński</t>
+  </si>
+  <si>
+    <t>RPC Legal</t>
+  </si>
+  <si>
+    <t>Šelih &amp; Partnerji</t>
+  </si>
+  <si>
+    <t>Spreksel advocaten</t>
+  </si>
+  <si>
+    <t>HJW</t>
+  </si>
+  <si>
+    <t>Bonn &amp; Schmitt</t>
+  </si>
+  <si>
+    <t>1min 39</t>
+  </si>
+  <si>
+    <t>KWKR Law</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Ecovis ProventusLaw</t>
+  </si>
+  <si>
+    <t>CCS Legal</t>
+  </si>
+  <si>
+    <t>Sérvulo &amp; Associados</t>
+  </si>
+  <si>
+    <t>Cases &amp; Lacambra</t>
+  </si>
+  <si>
+    <t>Udo Udoma &amp; Belo-Osagie</t>
+  </si>
+  <si>
+    <t>1min 42</t>
+  </si>
+  <si>
+    <t>Schramm Öhler</t>
+  </si>
+  <si>
+    <t>Amorys</t>
+  </si>
+  <si>
+    <t>Živković Samardžić</t>
+  </si>
+  <si>
+    <t>1min 46</t>
+  </si>
+  <si>
+    <t>D&amp;B David si Baias</t>
+  </si>
+  <si>
+    <t>BARGER PREKOP</t>
+  </si>
+  <si>
+    <t>LMS</t>
+  </si>
+  <si>
+    <t>GPK</t>
+  </si>
+  <si>
+    <t>JWP</t>
+  </si>
+  <si>
+    <t>1min 55</t>
+  </si>
+  <si>
+    <t>Green Horse Legal</t>
+  </si>
+  <si>
+    <t>Brown Rudnick</t>
+  </si>
+  <si>
+    <t>LSW Law</t>
+  </si>
+  <si>
+    <t>Suárez de Vivero</t>
+  </si>
+  <si>
+    <t>Schalast &amp; Partner</t>
+  </si>
+  <si>
+    <t>Nicolas Kanellopoulos Law</t>
+  </si>
+  <si>
+    <t>Salus Legal</t>
+  </si>
+  <si>
+    <t>Meyer Köring</t>
+  </si>
+  <si>
+    <t>Niederer Kraft Frey</t>
+  </si>
+  <si>
+    <t>Ilej &amp; Partners</t>
+  </si>
+  <si>
+    <t>Schneeweiss Weixelbaum Rechtsanwälte</t>
+  </si>
+  <si>
+    <t>Gleiss Lutz</t>
+  </si>
+  <si>
+    <t>Racine</t>
+  </si>
+  <si>
+    <t>1min 26</t>
+  </si>
+  <si>
+    <t>Kolster</t>
+  </si>
+  <si>
+    <t>Quinz</t>
+  </si>
+  <si>
+    <t>Frontier</t>
+  </si>
+  <si>
+    <t>Małecki Legal</t>
+  </si>
+  <si>
+    <t>Straatman Koster</t>
+  </si>
+  <si>
+    <t>Ramberg Advokater</t>
+  </si>
+  <si>
+    <t>SPVS</t>
+  </si>
+  <si>
+    <t>PLMJ</t>
+  </si>
+  <si>
+    <t>Ružička &amp; Partners</t>
+  </si>
+  <si>
+    <t>Aman &amp; Partners</t>
+  </si>
+  <si>
+    <t>HEKKELMAN</t>
+  </si>
+  <si>
+    <t>Oppenheim</t>
+  </si>
+  <si>
+    <t>RB Law</t>
+  </si>
+  <si>
+    <t>MENA City Lawyers</t>
+  </si>
+  <si>
+    <t>Webber Wentzel</t>
+  </si>
+  <si>
+    <t>Zampa Partners</t>
+  </si>
+  <si>
+    <t>Elias Neocleous &amp; Co LLC</t>
+  </si>
+  <si>
+    <t>GLNS</t>
+  </si>
+  <si>
+    <t>GMW lawyers</t>
+  </si>
+  <si>
+    <t>Rosenut Solicitors</t>
+  </si>
+  <si>
+    <t>LMCR</t>
+  </si>
+  <si>
+    <t>2min 5</t>
+  </si>
+  <si>
+    <t>Bennani &amp; Associes</t>
+  </si>
+  <si>
+    <t>Banwo &amp; Ighodalo</t>
+  </si>
+  <si>
+    <t>CAINS</t>
+  </si>
+  <si>
+    <t>VB Advocates</t>
+  </si>
+  <si>
+    <t>Endors</t>
+  </si>
+  <si>
+    <t>Granrut</t>
+  </si>
+  <si>
+    <t>DVDK Law</t>
+  </si>
+  <si>
+    <t>Wise 3</t>
+  </si>
+  <si>
+    <t>Vossius And Partner</t>
+  </si>
+  <si>
+    <t>Senica &amp; Partners</t>
+  </si>
+  <si>
+    <t>E+H Rechtsanwälte</t>
+  </si>
+  <si>
+    <t>Roschier</t>
+  </si>
+  <si>
+    <t>1min 10</t>
+  </si>
+  <si>
+    <t>Joffe &amp; Associés</t>
+  </si>
+  <si>
+    <t>Pepeljugoski Law</t>
+  </si>
+  <si>
+    <t>Den Hollander Advocaten</t>
+  </si>
+  <si>
+    <t>RDS Partners</t>
+  </si>
+  <si>
+    <t>Fylgia</t>
+  </si>
+  <si>
+    <t>Flichy Grangé</t>
+  </si>
+  <si>
+    <t>Shalakany</t>
+  </si>
+  <si>
+    <t>Blandy &amp; Blandy</t>
+  </si>
+  <si>
+    <t>Pestalozzi</t>
+  </si>
+  <si>
+    <t>hww hermann wienberg wilhelm</t>
+  </si>
+  <si>
+    <t>De Gaulle Fleurance</t>
+  </si>
+  <si>
+    <t>Stone King</t>
+  </si>
+  <si>
+    <t>ABL Partners LP</t>
+  </si>
+  <si>
+    <t>Araoz &amp; Rueda</t>
+  </si>
+  <si>
+    <t>Bowmans</t>
+  </si>
+  <si>
+    <t>SKW Schwarz</t>
+  </si>
+  <si>
+    <t>AKL</t>
+  </si>
+  <si>
+    <t>Peli Partners</t>
+  </si>
+  <si>
+    <t>POELLATH</t>
+  </si>
+  <si>
+    <t>1min 30</t>
+  </si>
+  <si>
+    <t>ENS Africa</t>
+  </si>
+  <si>
+    <t>Hannes Snellman</t>
+  </si>
+  <si>
+    <t>VO Patents &amp; Trademarks</t>
+  </si>
+  <si>
+    <t>Hedman</t>
+  </si>
+  <si>
+    <t>AMERELLER</t>
+  </si>
+  <si>
+    <t>Zirngibl</t>
+  </si>
+  <si>
+    <t>De Clercq</t>
+  </si>
+  <si>
+    <t>Lenz &amp; Staehelin</t>
+  </si>
+  <si>
+    <t>CRCCD</t>
+  </si>
+  <si>
+    <t>Pedersoli</t>
+  </si>
+  <si>
+    <t>Haslinger Nagele</t>
+  </si>
+  <si>
+    <t>2min 24</t>
+  </si>
+  <si>
+    <t>M&amp;P Legal</t>
+  </si>
+  <si>
+    <t>Ogletree Deakins</t>
+  </si>
+  <si>
+    <t>Moore Legal Kovács</t>
+  </si>
+  <si>
+    <t>Poulschmith</t>
+  </si>
+  <si>
+    <t>Lemstra Van der Korst</t>
+  </si>
+  <si>
+    <t>Held Berdnik Astner &amp; Partner</t>
+  </si>
+  <si>
+    <t>Lindemann Schwennicke &amp; Partner</t>
+  </si>
+  <si>
+    <t>ALN</t>
+  </si>
+  <si>
+    <t>Bech-Bruun</t>
+  </si>
+  <si>
+    <t>RWP Rechtsanwälte</t>
+  </si>
+  <si>
+    <t>Chazai Wamba</t>
+  </si>
+  <si>
+    <t>Eubelius</t>
+  </si>
+  <si>
+    <t>Wijn &amp; Stael</t>
+  </si>
+  <si>
+    <t>DZP Law</t>
+  </si>
+  <si>
+    <t>Wintertaling</t>
+  </si>
+  <si>
+    <t>Senekal Simmonds</t>
+  </si>
+  <si>
+    <t>Ferreira Pinto Cardigos</t>
+  </si>
+  <si>
+    <t>KO Associates</t>
+  </si>
+  <si>
+    <t>Blenheim</t>
+  </si>
+  <si>
+    <t>Vision Consulting</t>
+  </si>
+  <si>
+    <t>LEXENCE</t>
+  </si>
+  <si>
+    <t>Byrne Wallace</t>
   </si>
 </sst>
 </file>
@@ -2812,7 +3880,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C397"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.6634615384615"/>
@@ -2830,6 +3898,4362 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="1">
+        <v>308</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="1">
+        <v>428</v>
+      </c>
+      <c r="B3" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="1">
+        <v>616</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="1">
+        <v>650</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="1">
+        <v>760</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="1">
+        <v>582</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="1">
+        <v>518</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="1">
+        <v>912</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="1">
+        <v>929</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="1">
+        <v>946</v>
+      </c>
+      <c r="B11" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="1">
+        <v>537</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C12" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="1">
+        <v>736</v>
+      </c>
+      <c r="B13" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C13" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="1">
+        <v>549</v>
+      </c>
+      <c r="B14" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C14" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="1">
+        <v>875</v>
+      </c>
+      <c r="B15" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C15" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="1">
+        <v>882</v>
+      </c>
+      <c r="B16" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C16" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1">
+        <v>423</v>
+      </c>
+      <c r="B17" t="s" s="1">
+        <v>550</v>
+      </c>
+      <c r="C17" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="1">
+        <v>931</v>
+      </c>
+      <c r="B18" t="s" s="1">
+        <v>932</v>
+      </c>
+      <c r="C18" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="1">
+        <v>782</v>
+      </c>
+      <c r="B19" t="s" s="1">
+        <v>783</v>
+      </c>
+      <c r="C19" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1">
+        <v>689</v>
+      </c>
+      <c r="B20" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="1">
+        <v>283</v>
+      </c>
+      <c r="B21" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>283</v>
+      </c>
+      <c r="B22" t="s" s="1">
+        <v>284</v>
+      </c>
+      <c r="C22" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>619</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>620</v>
+      </c>
+      <c r="C23" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>244</v>
+      </c>
+      <c r="B24" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="1">
+        <v>899</v>
+      </c>
+      <c r="B25" t="s" s="1">
+        <v>900</v>
+      </c>
+      <c r="C25" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1">
+        <v>910</v>
+      </c>
+      <c r="B26" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="1">
+        <v>646</v>
+      </c>
+      <c r="B27" t="s" s="1">
+        <v>647</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1">
+        <v>904</v>
+      </c>
+      <c r="B28" t="s" s="1">
+        <v>835</v>
+      </c>
+      <c r="C28" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>786</v>
+      </c>
+      <c r="B29" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
+        <v>684</v>
+      </c>
+      <c r="B30" t="s" s="1">
+        <v>562</v>
+      </c>
+      <c r="C30" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>381</v>
+      </c>
+      <c r="B31" t="s" s="1">
+        <v>382</v>
+      </c>
+      <c r="C31" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1">
+        <v>735</v>
+      </c>
+      <c r="B32" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1">
+        <v>843</v>
+      </c>
+      <c r="B33" t="s" s="1">
+        <v>256</v>
+      </c>
+      <c r="C33" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1">
+        <v>681</v>
+      </c>
+      <c r="B34" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C34" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1">
+        <v>810</v>
+      </c>
+      <c r="B35" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="C35" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1">
+        <v>273</v>
+      </c>
+      <c r="B36" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="C36" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="1">
+        <v>808</v>
+      </c>
+      <c r="B37" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="C37" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1">
+        <v>944</v>
+      </c>
+      <c r="B38" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1">
+        <v>460</v>
+      </c>
+      <c r="B39" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>475</v>
+      </c>
+      <c r="B40" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="C40" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1">
+        <v>820</v>
+      </c>
+      <c r="B41" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="C41" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>532</v>
+      </c>
+      <c r="B42" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="C42" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="1">
+        <v>821</v>
+      </c>
+      <c r="B43" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="C43" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="1">
+        <v>681</v>
+      </c>
+      <c r="B44" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C44" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1">
+        <v>914</v>
+      </c>
+      <c r="B45" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C45" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>814</v>
+      </c>
+      <c r="B46" t="s" s="1">
+        <v>120</v>
+      </c>
+      <c r="C46" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1">
+        <v>892</v>
+      </c>
+      <c r="B47" t="s" s="1">
+        <v>120</v>
+      </c>
+      <c r="C47" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
+        <v>861</v>
+      </c>
+      <c r="B48" t="s" s="1">
+        <v>123</v>
+      </c>
+      <c r="C48" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>769</v>
+      </c>
+      <c r="B49" t="s" s="1">
+        <v>126</v>
+      </c>
+      <c r="C49" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
+        <v>276</v>
+      </c>
+      <c r="B50" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C50" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="1">
+        <v>630</v>
+      </c>
+      <c r="B51" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C51" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="1">
+        <v>711</v>
+      </c>
+      <c r="B52" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C52" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="1">
+        <v>696</v>
+      </c>
+      <c r="B53" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="1">
+        <v>893</v>
+      </c>
+      <c r="B54" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C54" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="1">
+        <v>700</v>
+      </c>
+      <c r="B55" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="1">
+        <v>809</v>
+      </c>
+      <c r="B56" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="1">
+        <v>847</v>
+      </c>
+      <c r="B57" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C57" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="1">
+        <v>746</v>
+      </c>
+      <c r="B58" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C58" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="1">
+        <v>787</v>
+      </c>
+      <c r="B59" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C59" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="1">
+        <v>755</v>
+      </c>
+      <c r="B60" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C60" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="1">
+        <v>435</v>
+      </c>
+      <c r="B61" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C61" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1">
+        <v>902</v>
+      </c>
+      <c r="B62" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C62" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="1">
+        <v>585</v>
+      </c>
+      <c r="B63" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C63" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="1">
+        <v>732</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C64" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1">
+        <v>762</v>
+      </c>
+      <c r="B65" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C65" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="1">
+        <v>898</v>
+      </c>
+      <c r="B66" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C66" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="B67" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C67" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="1">
+        <v>741</v>
+      </c>
+      <c r="B68" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="1">
+        <v>744</v>
+      </c>
+      <c r="B69" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C69" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>828</v>
+      </c>
+      <c r="B70" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C70" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="1">
+        <v>952</v>
+      </c>
+      <c r="B71" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C71" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="1">
+        <v>250</v>
+      </c>
+      <c r="B72" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="C72" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="1">
+        <v>879</v>
+      </c>
+      <c r="B73" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="C73" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="B74" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C74" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="1">
+        <v>336</v>
+      </c>
+      <c r="B75" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C75" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="1">
+        <v>728</v>
+      </c>
+      <c r="B76" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C76" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="1">
+        <v>663</v>
+      </c>
+      <c r="B77" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C77" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="1">
+        <v>669</v>
+      </c>
+      <c r="B78" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C78" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="1">
+        <v>770</v>
+      </c>
+      <c r="B79" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C79" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="1">
+        <v>891</v>
+      </c>
+      <c r="B80" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C80" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="1">
+        <v>392</v>
+      </c>
+      <c r="B81" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C81" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="1">
+        <v>335</v>
+      </c>
+      <c r="B82" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C82" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
+        <v>718</v>
+      </c>
+      <c r="B83" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C83" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="1">
+        <v>395</v>
+      </c>
+      <c r="B84" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C84" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="1">
+        <v>350</v>
+      </c>
+      <c r="B85" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C85" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="1">
+        <v>574</v>
+      </c>
+      <c r="B86" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C86" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="1">
+        <v>551</v>
+      </c>
+      <c r="B87" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C87" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1">
+        <v>935</v>
+      </c>
+      <c r="B88" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C88" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="1">
+        <v>948</v>
+      </c>
+      <c r="B89" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C89" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="1">
+        <v>784</v>
+      </c>
+      <c r="B90" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C90" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="1">
+        <v>925</v>
+      </c>
+      <c r="B91" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C91" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="1">
+        <v>826</v>
+      </c>
+      <c r="B92" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C92" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="1">
+        <v>705</v>
+      </c>
+      <c r="B93" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C93" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="1">
+        <v>817</v>
+      </c>
+      <c r="B94" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C94" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="1">
+        <v>331</v>
+      </c>
+      <c r="B95" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C95" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="1">
+        <v>263</v>
+      </c>
+      <c r="B96" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C96" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="1">
+        <v>301</v>
+      </c>
+      <c r="B97" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C97" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="1">
+        <v>858</v>
+      </c>
+      <c r="B98" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C98" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="1">
+        <v>202</v>
+      </c>
+      <c r="B99" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C99" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="1">
+        <v>690</v>
+      </c>
+      <c r="B100" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C100" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="1">
+        <v>713</v>
+      </c>
+      <c r="B101" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C101" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="1">
+        <v>788</v>
+      </c>
+      <c r="B102" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C102" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="1">
+        <v>496</v>
+      </c>
+      <c r="B103" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C103" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="1">
+        <v>657</v>
+      </c>
+      <c r="B104" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C104" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="1">
+        <v>895</v>
+      </c>
+      <c r="B105" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C105" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="1">
+        <v>639</v>
+      </c>
+      <c r="B106" t="s" s="1">
+        <v>213</v>
+      </c>
+      <c r="C106" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="1">
+        <v>936</v>
+      </c>
+      <c r="B107" t="s" s="1">
+        <v>213</v>
+      </c>
+      <c r="C107" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="1">
+        <v>487</v>
+      </c>
+      <c r="B108" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="1">
+        <v>868</v>
+      </c>
+      <c r="B109" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C109" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="1">
+        <v>723</v>
+      </c>
+      <c r="B110" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="C110" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="1">
+        <v>798</v>
+      </c>
+      <c r="B111" t="s" s="1">
+        <v>799</v>
+      </c>
+      <c r="C111" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="1">
+        <v>886</v>
+      </c>
+      <c r="B112" t="s" s="1">
+        <v>887</v>
+      </c>
+      <c r="C112" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="1">
+        <v>623</v>
+      </c>
+      <c r="B113" t="s" s="1">
+        <v>568</v>
+      </c>
+      <c r="C113" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="1">
+        <v>747</v>
+      </c>
+      <c r="B114" t="s" s="1">
+        <v>568</v>
+      </c>
+      <c r="C114" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="1">
+        <v>850</v>
+      </c>
+      <c r="B115" t="s" s="1">
+        <v>851</v>
+      </c>
+      <c r="C115" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="1">
+        <v>850</v>
+      </c>
+      <c r="B116" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="C116" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="1">
+        <v>907</v>
+      </c>
+      <c r="B117" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="C117" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="1">
+        <v>844</v>
+      </c>
+      <c r="B118" t="s" s="1">
+        <v>845</v>
+      </c>
+      <c r="C118" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="1">
+        <v>840</v>
+      </c>
+      <c r="B119" t="s" s="1">
+        <v>841</v>
+      </c>
+      <c r="C119" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="1">
+        <v>800</v>
+      </c>
+      <c r="B120" t="s" s="1">
+        <v>801</v>
+      </c>
+      <c r="C120" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="1">
+        <v>832</v>
+      </c>
+      <c r="B121" t="s" s="1">
+        <v>833</v>
+      </c>
+      <c r="C121" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="1">
+        <v>919</v>
+      </c>
+      <c r="B122" t="s" s="1">
+        <v>920</v>
+      </c>
+      <c r="C122" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="1">
+        <v>864</v>
+      </c>
+      <c r="B123" t="s" s="1">
+        <v>865</v>
+      </c>
+      <c r="C123" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="1">
+        <v>780</v>
+      </c>
+      <c r="B124" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="C124" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="1">
+        <v>916</v>
+      </c>
+      <c r="B125" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="C125" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="1">
+        <v>768</v>
+      </c>
+      <c r="B126" t="s" s="1">
+        <v>571</v>
+      </c>
+      <c r="C126" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="1">
+        <v>896</v>
+      </c>
+      <c r="B127" t="s" s="1">
+        <v>486</v>
+      </c>
+      <c r="C127" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="1">
+        <v>708</v>
+      </c>
+      <c r="B128" t="s" s="1">
+        <v>709</v>
+      </c>
+      <c r="C128" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="1">
+        <v>905</v>
+      </c>
+      <c r="B129" t="s" s="1">
+        <v>62</v>
+      </c>
+      <c r="C129" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="1">
+        <v>687</v>
+      </c>
+      <c r="B130" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="C130" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="1">
+        <v>710</v>
+      </c>
+      <c r="B131" t="s" s="1">
+        <v>241</v>
+      </c>
+      <c r="C131" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="1">
+        <v>789</v>
+      </c>
+      <c r="B132" t="s" s="1">
+        <v>440</v>
+      </c>
+      <c r="C132" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="1">
+        <v>672</v>
+      </c>
+      <c r="B133" t="s" s="1">
+        <v>68</v>
+      </c>
+      <c r="C133" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="1">
+        <v>666</v>
+      </c>
+      <c r="B134" t="s" s="1">
+        <v>404</v>
+      </c>
+      <c r="C134" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="1">
+        <v>890</v>
+      </c>
+      <c r="B135" t="s" s="1">
+        <v>647</v>
+      </c>
+      <c r="C135" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="1">
+        <v>651</v>
+      </c>
+      <c r="B136" t="s" s="1">
+        <v>76</v>
+      </c>
+      <c r="C136" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="1">
+        <v>834</v>
+      </c>
+      <c r="B137" t="s" s="1">
+        <v>835</v>
+      </c>
+      <c r="C137" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="1">
+        <v>816</v>
+      </c>
+      <c r="B138" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="C138" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="1">
+        <v>628</v>
+      </c>
+      <c r="B139" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C139" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="1">
+        <v>938</v>
+      </c>
+      <c r="B140" t="s" s="1">
+        <v>504</v>
+      </c>
+      <c r="C140" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="1">
+        <v>612</v>
+      </c>
+      <c r="B141" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="C141" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="1">
+        <v>726</v>
+      </c>
+      <c r="B142" t="s" s="1">
+        <v>562</v>
+      </c>
+      <c r="C142" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="1">
+        <v>838</v>
+      </c>
+      <c r="B143" t="s" s="1">
+        <v>562</v>
+      </c>
+      <c r="C143" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="1">
+        <v>812</v>
+      </c>
+      <c r="B144" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C144" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="1">
+        <v>529</v>
+      </c>
+      <c r="B145" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="C145" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="1">
+        <v>738</v>
+      </c>
+      <c r="B146" t="s" s="1">
+        <v>382</v>
+      </c>
+      <c r="C146" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="1">
+        <v>758</v>
+      </c>
+      <c r="B147" t="s" s="1">
+        <v>382</v>
+      </c>
+      <c r="C147" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="1">
+        <v>522</v>
+      </c>
+      <c r="B148" t="s" s="1">
+        <v>382</v>
+      </c>
+      <c r="C148" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="1">
+        <v>707</v>
+      </c>
+      <c r="B149" t="s" s="1">
+        <v>464</v>
+      </c>
+      <c r="C149" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="1">
+        <v>888</v>
+      </c>
+      <c r="B150" t="s" s="1">
+        <v>464</v>
+      </c>
+      <c r="C150" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="1">
+        <v>780</v>
+      </c>
+      <c r="B151" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C151" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="1">
+        <v>951</v>
+      </c>
+      <c r="B152" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C152" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="1">
+        <v>682</v>
+      </c>
+      <c r="B153" t="s" s="1">
+        <v>256</v>
+      </c>
+      <c r="C153" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="1">
+        <v>725</v>
+      </c>
+      <c r="B154" t="s" s="1">
+        <v>256</v>
+      </c>
+      <c r="C154" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="1">
+        <v>829</v>
+      </c>
+      <c r="B155" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="C155" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="1">
+        <v>727</v>
+      </c>
+      <c r="B156" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="C156" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="1">
+        <v>790</v>
+      </c>
+      <c r="B157" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="C157" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="1">
+        <v>607</v>
+      </c>
+      <c r="B158" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C158" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="1">
+        <v>637</v>
+      </c>
+      <c r="B159" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C159" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="1">
+        <v>638</v>
+      </c>
+      <c r="B160" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C160" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="1">
+        <v>795</v>
+      </c>
+      <c r="B161" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C161" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="1">
+        <v>870</v>
+      </c>
+      <c r="B162" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C162" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="1">
+        <v>906</v>
+      </c>
+      <c r="B163" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="C163" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="1">
+        <v>644</v>
+      </c>
+      <c r="B164" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="C164" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="1">
+        <v>654</v>
+      </c>
+      <c r="B165" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="C165" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="1">
+        <v>839</v>
+      </c>
+      <c r="B166" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="C166" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="1">
+        <v>953</v>
+      </c>
+      <c r="B167" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="C167" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="1">
+        <v>859</v>
+      </c>
+      <c r="B168" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="C168" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="1">
+        <v>822</v>
+      </c>
+      <c r="B169" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="C169" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="1">
+        <v>921</v>
+      </c>
+      <c r="B170" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="C170" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="1">
+        <v>941</v>
+      </c>
+      <c r="B171" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="C171" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="1">
+        <v>642</v>
+      </c>
+      <c r="B172" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="C172" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="1">
+        <v>685</v>
+      </c>
+      <c r="B173" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="C173" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="1">
+        <v>776</v>
+      </c>
+      <c r="B174" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="C174" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="1">
+        <v>804</v>
+      </c>
+      <c r="B175" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="C175" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="1">
+        <v>664</v>
+      </c>
+      <c r="B176" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C176" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="1">
+        <v>796</v>
+      </c>
+      <c r="B177" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C177" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="1">
+        <v>950</v>
+      </c>
+      <c r="B178" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C178" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="1">
+        <v>730</v>
+      </c>
+      <c r="B179" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C179" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="1">
+        <v>918</v>
+      </c>
+      <c r="B180" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C180" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="1">
+        <v>860</v>
+      </c>
+      <c r="B181" t="s" s="1">
+        <v>120</v>
+      </c>
+      <c r="C181" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="1">
+        <v>884</v>
+      </c>
+      <c r="B182" t="s" s="1">
+        <v>120</v>
+      </c>
+      <c r="C182" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="1">
+        <v>917</v>
+      </c>
+      <c r="B183" t="s" s="1">
+        <v>123</v>
+      </c>
+      <c r="C183" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="1">
+        <v>942</v>
+      </c>
+      <c r="B184" t="s" s="1">
+        <v>123</v>
+      </c>
+      <c r="C184" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="1">
+        <v>623</v>
+      </c>
+      <c r="B185" t="s" s="1">
+        <v>126</v>
+      </c>
+      <c r="C185" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="1">
+        <v>671</v>
+      </c>
+      <c r="B186" t="s" s="1">
+        <v>126</v>
+      </c>
+      <c r="C186" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="1">
+        <v>774</v>
+      </c>
+      <c r="B187" t="s" s="1">
+        <v>126</v>
+      </c>
+      <c r="C187" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="1">
+        <v>848</v>
+      </c>
+      <c r="B188" t="s" s="1">
+        <v>126</v>
+      </c>
+      <c r="C188" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="1">
+        <v>679</v>
+      </c>
+      <c r="B189" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C189" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="1">
+        <v>695</v>
+      </c>
+      <c r="B190" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C190" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="1">
+        <v>766</v>
+      </c>
+      <c r="B191" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C191" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="1">
+        <v>897</v>
+      </c>
+      <c r="B192" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C192" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="1">
+        <v>601</v>
+      </c>
+      <c r="B193" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C193" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="1">
+        <v>712</v>
+      </c>
+      <c r="B194" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C194" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="1">
+        <v>764</v>
+      </c>
+      <c r="B195" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C195" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="1">
+        <v>866</v>
+      </c>
+      <c r="B196" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C196" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="1">
+        <v>867</v>
+      </c>
+      <c r="B197" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C197" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="1">
+        <v>617</v>
+      </c>
+      <c r="B198" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C198" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="1">
+        <v>546</v>
+      </c>
+      <c r="B199" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C199" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="1">
+        <v>825</v>
+      </c>
+      <c r="B200" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C200" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="1">
+        <v>880</v>
+      </c>
+      <c r="B201" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C201" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="1">
+        <v>919</v>
+      </c>
+      <c r="B202" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C202" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="1">
+        <v>927</v>
+      </c>
+      <c r="B203" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C203" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="1">
+        <v>613</v>
+      </c>
+      <c r="B204" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C204" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="1">
+        <v>703</v>
+      </c>
+      <c r="B205" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C205" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="1">
+        <v>729</v>
+      </c>
+      <c r="B206" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C206" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="1">
+        <v>558</v>
+      </c>
+      <c r="B207" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C207" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="1">
+        <v>742</v>
+      </c>
+      <c r="B208" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C208" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="1">
+        <v>754</v>
+      </c>
+      <c r="B209" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C209" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="1">
+        <v>781</v>
+      </c>
+      <c r="B210" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C210" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="1">
+        <v>614</v>
+      </c>
+      <c r="B211" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C211" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="1">
+        <v>640</v>
+      </c>
+      <c r="B212" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C212" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="1">
+        <v>803</v>
+      </c>
+      <c r="B213" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C213" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="1">
+        <v>930</v>
+      </c>
+      <c r="B214" t="s" s="1">
+        <v>259</v>
+      </c>
+      <c r="C214" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="1">
+        <v>622</v>
+      </c>
+      <c r="B215" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C215" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="1">
+        <v>740</v>
+      </c>
+      <c r="B216" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C216" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="1">
+        <v>745</v>
+      </c>
+      <c r="B217" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C217" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="1">
+        <v>554</v>
+      </c>
+      <c r="B218" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C218" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="1">
+        <v>827</v>
+      </c>
+      <c r="B219" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C219" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="1">
+        <v>852</v>
+      </c>
+      <c r="B220" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C220" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="1">
+        <v>889</v>
+      </c>
+      <c r="B221" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C221" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="1">
+        <v>913</v>
+      </c>
+      <c r="B222" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="C222" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="1">
+        <v>719</v>
+      </c>
+      <c r="B223" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C223" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="1">
+        <v>756</v>
+      </c>
+      <c r="B224" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C224" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="1">
+        <v>837</v>
+      </c>
+      <c r="B225" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C225" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="1">
+        <v>945</v>
+      </c>
+      <c r="B226" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C226" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="1">
+        <v>949</v>
+      </c>
+      <c r="B227" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C227" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="1">
+        <v>954</v>
+      </c>
+      <c r="B228" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C228" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="1">
+        <v>625</v>
+      </c>
+      <c r="B229" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C229" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="1">
+        <v>702</v>
+      </c>
+      <c r="B230" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C230" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="1">
+        <v>778</v>
+      </c>
+      <c r="B231" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C231" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="1">
+        <v>849</v>
+      </c>
+      <c r="B232" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C232" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="1">
+        <v>857</v>
+      </c>
+      <c r="B233" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C233" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="1">
+        <v>536</v>
+      </c>
+      <c r="B234" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C234" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="1">
+        <v>940</v>
+      </c>
+      <c r="B235" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C235" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="1">
+        <v>626</v>
+      </c>
+      <c r="B236" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C236" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="1">
+        <v>660</v>
+      </c>
+      <c r="B237" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C237" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="1">
+        <v>674</v>
+      </c>
+      <c r="B238" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C238" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="1">
+        <v>747</v>
+      </c>
+      <c r="B239" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C239" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="1">
+        <v>874</v>
+      </c>
+      <c r="B240" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C240" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="1">
+        <v>602</v>
+      </c>
+      <c r="B241" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C241" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="1">
+        <v>603</v>
+      </c>
+      <c r="B242" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C242" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="1">
+        <v>632</v>
+      </c>
+      <c r="B243" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C243" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="1">
+        <v>635</v>
+      </c>
+      <c r="B244" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C244" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="1">
+        <v>676</v>
+      </c>
+      <c r="B245" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C245" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="1">
+        <v>716</v>
+      </c>
+      <c r="B246" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C246" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="1">
+        <v>731</v>
+      </c>
+      <c r="B247" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C247" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="1">
+        <v>521</v>
+      </c>
+      <c r="B248" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C248" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="1">
+        <v>846</v>
+      </c>
+      <c r="B249" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C249" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="1">
+        <v>697</v>
+      </c>
+      <c r="B250" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C250" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="1">
+        <v>739</v>
+      </c>
+      <c r="B251" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C251" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="1">
+        <v>773</v>
+      </c>
+      <c r="B252" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C252" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="1">
+        <v>797</v>
+      </c>
+      <c r="B253" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C253" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="1">
+        <v>807</v>
+      </c>
+      <c r="B254" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C254" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="1">
+        <v>813</v>
+      </c>
+      <c r="B255" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C255" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="1">
+        <v>876</v>
+      </c>
+      <c r="B256" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C256" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="1">
+        <v>608</v>
+      </c>
+      <c r="B257" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C257" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="1">
+        <v>678</v>
+      </c>
+      <c r="B258" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C258" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="1">
+        <v>686</v>
+      </c>
+      <c r="B259" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C259" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="1">
+        <v>704</v>
+      </c>
+      <c r="B260" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C260" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="1">
+        <v>749</v>
+      </c>
+      <c r="B261" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C261" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="1">
+        <v>856</v>
+      </c>
+      <c r="B262" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C262" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="1">
+        <v>937</v>
+      </c>
+      <c r="B263" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C263" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="1">
+        <v>600</v>
+      </c>
+      <c r="B264" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="C264" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="1">
+        <v>765</v>
+      </c>
+      <c r="B265" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="C265" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="1">
+        <v>785</v>
+      </c>
+      <c r="B266" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="C266" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="1">
+        <v>811</v>
+      </c>
+      <c r="B267" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="C267" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="1">
+        <v>824</v>
+      </c>
+      <c r="B268" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="C268" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="1">
+        <v>877</v>
+      </c>
+      <c r="B269" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="C269" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="1">
+        <v>668</v>
+      </c>
+      <c r="B270" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C270" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="1">
+        <v>791</v>
+      </c>
+      <c r="B271" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C271" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="1">
+        <v>794</v>
+      </c>
+      <c r="B272" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C272" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="1">
+        <v>815</v>
+      </c>
+      <c r="B273" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C273" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="1">
+        <v>836</v>
+      </c>
+      <c r="B274" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C274" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="1">
+        <v>943</v>
+      </c>
+      <c r="B275" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="C275" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="1">
+        <v>605</v>
+      </c>
+      <c r="B276" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C276" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="1">
+        <v>615</v>
+      </c>
+      <c r="B277" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C277" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="1">
+        <v>618</v>
+      </c>
+      <c r="B278" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C278" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="1">
+        <v>636</v>
+      </c>
+      <c r="B279" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C279" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="1">
+        <v>645</v>
+      </c>
+      <c r="B280" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C280" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="1">
+        <v>706</v>
+      </c>
+      <c r="B281" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C281" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="1">
+        <v>715</v>
+      </c>
+      <c r="B282" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C282" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="1">
+        <v>721</v>
+      </c>
+      <c r="B283" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C283" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="1">
+        <v>734</v>
+      </c>
+      <c r="B284" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C284" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="1">
+        <v>759</v>
+      </c>
+      <c r="B285" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C285" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="1">
+        <v>767</v>
+      </c>
+      <c r="B286" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C286" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="1">
+        <v>805</v>
+      </c>
+      <c r="B287" t="s" s="1">
+        <v>180</v>
+      </c>
+      <c r="C287" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="1">
+        <v>634</v>
+      </c>
+      <c r="B288" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C288" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="1">
+        <v>757</v>
+      </c>
+      <c r="B289" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C289" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="1">
+        <v>779</v>
+      </c>
+      <c r="B290" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C290" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="1">
+        <v>195</v>
+      </c>
+      <c r="B291" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C291" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="1">
+        <v>806</v>
+      </c>
+      <c r="B292" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C292" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="1">
+        <v>926</v>
+      </c>
+      <c r="B293" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C293" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="1">
+        <v>954</v>
+      </c>
+      <c r="B294" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C294" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="1">
+        <v>606</v>
+      </c>
+      <c r="B295" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C295" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="1">
+        <v>649</v>
+      </c>
+      <c r="B296" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C296" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="1">
+        <v>653</v>
+      </c>
+      <c r="B297" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C297" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="1">
+        <v>658</v>
+      </c>
+      <c r="B298" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C298" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="1">
+        <v>750</v>
+      </c>
+      <c r="B299" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C299" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="1">
+        <v>792</v>
+      </c>
+      <c r="B300" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C300" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="1">
+        <v>854</v>
+      </c>
+      <c r="B301" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C301" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="1">
+        <v>869</v>
+      </c>
+      <c r="B302" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C302" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="1">
+        <v>933</v>
+      </c>
+      <c r="B303" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="C303" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="1">
+        <v>624</v>
+      </c>
+      <c r="B304" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C304" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="1">
+        <v>652</v>
+      </c>
+      <c r="B305" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C305" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="1">
+        <v>680</v>
+      </c>
+      <c r="B306" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C306" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="1">
+        <v>688</v>
+      </c>
+      <c r="B307" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C307" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="1">
+        <v>691</v>
+      </c>
+      <c r="B308" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C308" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="1">
+        <v>717</v>
+      </c>
+      <c r="B309" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C309" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="1">
+        <v>720</v>
+      </c>
+      <c r="B310" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C310" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="1">
+        <v>911</v>
+      </c>
+      <c r="B311" t="s" s="1">
+        <v>189</v>
+      </c>
+      <c r="C311" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="1">
+        <v>604</v>
+      </c>
+      <c r="B312" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C312" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="1">
+        <v>648</v>
+      </c>
+      <c r="B313" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C313" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="1">
+        <v>692</v>
+      </c>
+      <c r="B314" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C314" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="1">
+        <v>722</v>
+      </c>
+      <c r="B315" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C315" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="1">
+        <v>737</v>
+      </c>
+      <c r="B316" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C316" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="1">
+        <v>777</v>
+      </c>
+      <c r="B317" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C317" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="1">
+        <v>815</v>
+      </c>
+      <c r="B318" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C318" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="1">
+        <v>818</v>
+      </c>
+      <c r="B319" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C319" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="1">
+        <v>823</v>
+      </c>
+      <c r="B320" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C320" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="1">
+        <v>894</v>
+      </c>
+      <c r="B321" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C321" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="1">
+        <v>901</v>
+      </c>
+      <c r="B322" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C322" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="1">
+        <v>915</v>
+      </c>
+      <c r="B323" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C323" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="1">
+        <v>924</v>
+      </c>
+      <c r="B324" t="s" s="1">
+        <v>194</v>
+      </c>
+      <c r="C324" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="1">
+        <v>599</v>
+      </c>
+      <c r="B325" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C325" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="1">
+        <v>670</v>
+      </c>
+      <c r="B326" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C326" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="1">
+        <v>724</v>
+      </c>
+      <c r="B327" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C327" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="1">
+        <v>743</v>
+      </c>
+      <c r="B328" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C328" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="1">
+        <v>748</v>
+      </c>
+      <c r="B329" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C329" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="1">
+        <v>761</v>
+      </c>
+      <c r="B330" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C330" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="1">
+        <v>763</v>
+      </c>
+      <c r="B331" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C331" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="1">
+        <v>530</v>
+      </c>
+      <c r="B332" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C332" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="1">
+        <v>802</v>
+      </c>
+      <c r="B333" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C333" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="1">
+        <v>878</v>
+      </c>
+      <c r="B334" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C334" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="1">
+        <v>885</v>
+      </c>
+      <c r="B335" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C335" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="1">
+        <v>922</v>
+      </c>
+      <c r="B336" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C336" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="1">
+        <v>934</v>
+      </c>
+      <c r="B337" t="s" s="1">
+        <v>197</v>
+      </c>
+      <c r="C337" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="1">
+        <v>609</v>
+      </c>
+      <c r="B338" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C338" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="1">
+        <v>699</v>
+      </c>
+      <c r="B339" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C339" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="1">
+        <v>733</v>
+      </c>
+      <c r="B340" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C340" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="1">
+        <v>819</v>
+      </c>
+      <c r="B341" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C341" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="1">
+        <v>853</v>
+      </c>
+      <c r="B342" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="C342" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="1">
+        <v>610</v>
+      </c>
+      <c r="B343" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C343" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="1">
+        <v>633</v>
+      </c>
+      <c r="B344" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C344" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="1">
+        <v>662</v>
+      </c>
+      <c r="B345" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C345" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="1">
+        <v>665</v>
+      </c>
+      <c r="B346" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C346" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="1">
+        <v>693</v>
+      </c>
+      <c r="B347" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C347" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s" s="1">
+        <v>694</v>
+      </c>
+      <c r="B348" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C348" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="1">
+        <v>752</v>
+      </c>
+      <c r="B349" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C349" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s" s="1">
+        <v>753</v>
+      </c>
+      <c r="B350" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C350" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s" s="1">
+        <v>830</v>
+      </c>
+      <c r="B351" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C351" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s" s="1">
+        <v>534</v>
+      </c>
+      <c r="B352" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C352" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="1">
+        <v>855</v>
+      </c>
+      <c r="B353" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C353" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="1">
+        <v>871</v>
+      </c>
+      <c r="B354" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C354" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s" s="1">
+        <v>873</v>
+      </c>
+      <c r="B355" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C355" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s" s="1">
+        <v>908</v>
+      </c>
+      <c r="B356" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C356" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s" s="1">
+        <v>939</v>
+      </c>
+      <c r="B357" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C357" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s" s="1">
+        <v>947</v>
+      </c>
+      <c r="B358" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C358" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="1">
+        <v>641</v>
+      </c>
+      <c r="B359" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C359" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="1">
+        <v>643</v>
+      </c>
+      <c r="B360" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C360" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="1">
+        <v>673</v>
+      </c>
+      <c r="B361" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C361" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="1">
+        <v>775</v>
+      </c>
+      <c r="B362" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C362" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="1">
+        <v>885</v>
+      </c>
+      <c r="B363" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C363" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="1">
+        <v>909</v>
+      </c>
+      <c r="B364" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="C364" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="1">
+        <v>611</v>
+      </c>
+      <c r="B365" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C365" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s" s="1">
+        <v>621</v>
+      </c>
+      <c r="B366" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C366" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s" s="1">
+        <v>631</v>
+      </c>
+      <c r="B367" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C367" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s" s="1">
+        <v>655</v>
+      </c>
+      <c r="B368" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C368" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s" s="1">
+        <v>656</v>
+      </c>
+      <c r="B369" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C369" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s" s="1">
+        <v>661</v>
+      </c>
+      <c r="B370" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C370" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="1">
+        <v>751</v>
+      </c>
+      <c r="B371" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C371" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="1">
+        <v>772</v>
+      </c>
+      <c r="B372" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C372" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="1">
+        <v>793</v>
+      </c>
+      <c r="B373" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C373" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="1">
+        <v>862</v>
+      </c>
+      <c r="B374" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C374" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="1">
+        <v>863</v>
+      </c>
+      <c r="B375" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C375" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="1">
+        <v>881</v>
+      </c>
+      <c r="B376" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C376" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="1">
+        <v>883</v>
+      </c>
+      <c r="B377" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="C377" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="1">
+        <v>629</v>
+      </c>
+      <c r="B378" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C378" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="1">
+        <v>667</v>
+      </c>
+      <c r="B379" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C379" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="1">
+        <v>675</v>
+      </c>
+      <c r="B380" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C380" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="1">
+        <v>683</v>
+      </c>
+      <c r="B381" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C381" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="1">
+        <v>698</v>
+      </c>
+      <c r="B382" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C382" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="1">
+        <v>545</v>
+      </c>
+      <c r="B383" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C383" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="1">
+        <v>771</v>
+      </c>
+      <c r="B384" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C384" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="1">
+        <v>525</v>
+      </c>
+      <c r="B385" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C385" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="1">
+        <v>831</v>
+      </c>
+      <c r="B386" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C386" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="1">
+        <v>842</v>
+      </c>
+      <c r="B387" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C387" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="1">
+        <v>872</v>
+      </c>
+      <c r="B388" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C388" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="1">
+        <v>903</v>
+      </c>
+      <c r="B389" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C389" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="1">
+        <v>928</v>
+      </c>
+      <c r="B390" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="C390" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="1">
+        <v>627</v>
+      </c>
+      <c r="B391" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C391" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="1">
+        <v>659</v>
+      </c>
+      <c r="B392" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="C392" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="1">
+        <v>677</v>
+      </c>
+      <c r="B393" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C393" t="s" s="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="1">
+        <v>923</v>
+      </c>
+      <c r="B394" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="C394" t="s" s="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="1">
+        <v>714</v>
+      </c>
+      <c r="B395" t="s" s="1">
+        <v>568</v>
+      </c>
+      <c r="C395" t="s" s="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="1">
+        <v>701</v>
+      </c>
+      <c r="B396" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="C396" t="s" s="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="1">
+        <v>714</v>
+      </c>
+      <c r="B397" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C397" t="s" s="1">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
